--- a/docs/301_鍵盤設計規格_方音符號輸入_台語音標編碼.xlsx
+++ b/docs/301_鍵盤設計規格_方音符號輸入_台語音標編碼.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AlanJui\work\rime-tlpa\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F5719C5-A92C-47CB-8FAF-0D1A60E0CD40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45E1D4C6-116B-4751-8A9C-78F2CC84B365}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6300" yWindow="-5940" windowWidth="16440" windowHeight="28320" firstSheet="7" activeTab="7" xr2:uid="{6D6F034E-466E-416C-B3CC-1F7937B8DE3D}"/>
+    <workbookView xWindow="67080" yWindow="-120" windowWidth="16440" windowHeight="28320" activeTab="1" xr2:uid="{6D6F034E-466E-416C-B3CC-1F7937B8DE3D}"/>
   </bookViews>
   <sheets>
     <sheet name="xlit對映工具" sheetId="1" r:id="rId1"/>
@@ -4151,6 +4151,20 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="115" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="116" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="117" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="118" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="119" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="108" fillId="29" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="108" fillId="29" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="108" fillId="29" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="107" fillId="30" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -4178,20 +4192,6 @@
     <xf numFmtId="0" fontId="107" fillId="30" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="108" fillId="29" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="108" fillId="29" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="108" fillId="29" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="115" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="116" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="117" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="118" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="119" fillId="0" borderId="0" xfId="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -11517,8 +11517,8 @@
     </row>
     <row r="13" spans="1:86" outlineLevel="1">
       <c r="B13" s="1" t="str">
-        <f xml:space="preserve"> _xlfn.CONCAT("    - xlit|", D4:BH4, "|", D5:BH5, "|")</f>
-        <v xml:space="preserve">    - xlit|bPmtTnlkgKŋhzjcsZJCSaiuweOəMNGRFQVIUY@AWHdfqrvxy1732584&amp;L|!qa2wsxeEdNcyYhnrRfv8ujK,ikmp/btgz9lM0;Oo*UJ&lt;I(L:5346][7-|</v>
+        <f xml:space="preserve"> _xlfn.CONCAT("    - xlit|", C4:BH4, "|", C5:BH5, "|")</f>
+        <v xml:space="preserve">    - xlit|pbPmtTnlkgKŋhzjcsZJCSaiuweOəMNGRFQVIUY@AWHdfqrvxy1732584&amp;L|1!qa2wsxeEdNcyYhnrRfv8ujK,ikmp/btgz9lM0;Oo*UJ&lt;I(L:5346][7-|</v>
       </c>
       <c r="BL13" s="246">
         <v>12</v>
@@ -11676,7 +11676,7 @@
       </c>
       <c r="B16" s="1">
         <f xml:space="preserve"> SEARCH("|", $B$13, B15+1)</f>
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="BL16" s="246">
         <v>15</v>
@@ -11730,7 +11730,7 @@
       </c>
       <c r="B17" s="1">
         <f xml:space="preserve"> SEARCH("|", $B$13, B16+1)</f>
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="BL17" s="246">
         <v>16</v>
@@ -11895,11 +11895,11 @@
       </c>
       <c r="B19" s="1">
         <f xml:space="preserve"> LEN(C19)</f>
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C19" s="1" t="str">
         <f xml:space="preserve"> MID($B$13,B15+1, (B16-B15-1))</f>
-        <v>bPmtTnlkgKŋhzjcsZJCSaiuweOəMNGRFQVIUY@AWHdfqrvxy1732584&amp;L</v>
+        <v>pbPmtTnlkgKŋhzjcsZJCSaiuweOəMNGRFQVIUY@AWHdfqrvxy1732584&amp;L</v>
       </c>
       <c r="D19" s="1"/>
       <c r="E19" s="1"/>
@@ -12014,11 +12014,11 @@
       </c>
       <c r="B20" s="1">
         <f xml:space="preserve"> LEN(C20)</f>
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C20" s="1" t="str">
         <f xml:space="preserve"> MID($B$13,B16+1, (B17-B16-1))</f>
-        <v>!qa2wsxeEdNcyYhnrRfv8ujK,ikmp/btgz9lM0;Oo*UJ&lt;I(L:5346][7-</v>
+        <v>1!qa2wsxeEdNcyYhnrRfv8ujK,ikmp/btgz9lM0;Oo*UJ&lt;I(L:5346][7-</v>
       </c>
       <c r="D20" s="1"/>
       <c r="E20" s="1"/>
@@ -12536,235 +12536,235 @@
       <c r="B23" s="1"/>
       <c r="C23" s="5" t="str">
         <f xml:space="preserve"> MID($C$19,C$22,1)</f>
-        <v>b</v>
+        <v>p</v>
       </c>
       <c r="D23" s="5" t="str">
         <f t="shared" ref="D23:BJ23" si="2" xml:space="preserve"> MID($C$19,D$22,1)</f>
-        <v>P</v>
+        <v>b</v>
       </c>
       <c r="E23" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>m</v>
+        <v>P</v>
       </c>
       <c r="F23" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>t</v>
+        <v>m</v>
       </c>
       <c r="G23" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>T</v>
+        <v>t</v>
       </c>
       <c r="H23" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>n</v>
+        <v>T</v>
       </c>
       <c r="I23" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>l</v>
+        <v>n</v>
       </c>
       <c r="J23" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>k</v>
+        <v>l</v>
       </c>
       <c r="K23" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>g</v>
+        <v>k</v>
       </c>
       <c r="L23" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>K</v>
+        <v>g</v>
       </c>
       <c r="M23" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>ŋ</v>
+        <v>K</v>
       </c>
       <c r="N23" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>h</v>
+        <v>ŋ</v>
       </c>
       <c r="O23" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>z</v>
+        <v>h</v>
       </c>
       <c r="P23" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>j</v>
+        <v>z</v>
       </c>
       <c r="Q23" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>c</v>
+        <v>j</v>
       </c>
       <c r="R23" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>s</v>
+        <v>c</v>
       </c>
       <c r="S23" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>Z</v>
+        <v>s</v>
       </c>
       <c r="T23" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>J</v>
+        <v>Z</v>
       </c>
       <c r="U23" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>C</v>
+        <v>J</v>
       </c>
       <c r="V23" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>S</v>
+        <v>C</v>
       </c>
       <c r="W23" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>a</v>
+        <v>S</v>
       </c>
       <c r="X23" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>i</v>
+        <v>a</v>
       </c>
       <c r="Y23" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>u</v>
+        <v>i</v>
       </c>
       <c r="Z23" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>w</v>
+        <v>u</v>
       </c>
       <c r="AA23" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>e</v>
+        <v>w</v>
       </c>
       <c r="AB23" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>O</v>
+        <v>e</v>
       </c>
       <c r="AC23" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>ə</v>
+        <v>O</v>
       </c>
       <c r="AD23" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>M</v>
+        <v>ə</v>
       </c>
       <c r="AE23" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>N</v>
+        <v>M</v>
       </c>
       <c r="AF23" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>G</v>
+        <v>N</v>
       </c>
       <c r="AG23" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>R</v>
+        <v>G</v>
       </c>
       <c r="AH23" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>F</v>
+        <v>R</v>
       </c>
       <c r="AI23" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>Q</v>
+        <v>F</v>
       </c>
       <c r="AJ23" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>V</v>
+        <v>Q</v>
       </c>
       <c r="AK23" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>I</v>
+        <v>V</v>
       </c>
       <c r="AL23" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>U</v>
+        <v>I</v>
       </c>
       <c r="AM23" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>Y</v>
+        <v>U</v>
       </c>
       <c r="AN23" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>@</v>
+        <v>Y</v>
       </c>
       <c r="AO23" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>A</v>
+        <v>@</v>
       </c>
       <c r="AP23" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>W</v>
+        <v>A</v>
       </c>
       <c r="AQ23" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>H</v>
+        <v>W</v>
       </c>
       <c r="AR23" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>d</v>
+        <v>H</v>
       </c>
       <c r="AS23" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>f</v>
+        <v>d</v>
       </c>
       <c r="AT23" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>q</v>
+        <v>f</v>
       </c>
       <c r="AU23" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>r</v>
+        <v>q</v>
       </c>
       <c r="AV23" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>v</v>
+        <v>r</v>
       </c>
       <c r="AW23" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>x</v>
+        <v>v</v>
       </c>
       <c r="AX23" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>y</v>
+        <v>x</v>
       </c>
       <c r="AY23" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>y</v>
       </c>
       <c r="AZ23" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="BA23" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="BB23" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BC23" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="BD23" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="BE23" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="BF23" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>&amp;</v>
+        <v>4</v>
       </c>
       <c r="BG23" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>L</v>
+        <v>&amp;</v>
       </c>
       <c r="BH23" s="5" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>L</v>
       </c>
       <c r="BI23" s="5" t="str">
         <f t="shared" si="2"/>
@@ -12829,235 +12829,235 @@
       <c r="B24" s="1"/>
       <c r="C24" s="6" t="str">
         <f xml:space="preserve"> MID($C$20,C$22,1)</f>
-        <v>!</v>
+        <v>1</v>
       </c>
       <c r="D24" s="6" t="str">
         <f t="shared" ref="D24:BJ24" si="3" xml:space="preserve"> MID($C$20,D$22,1)</f>
-        <v>q</v>
+        <v>!</v>
       </c>
       <c r="E24" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>a</v>
+        <v>q</v>
       </c>
       <c r="F24" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>a</v>
       </c>
       <c r="G24" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>w</v>
+        <v>2</v>
       </c>
       <c r="H24" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>s</v>
+        <v>w</v>
       </c>
       <c r="I24" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>x</v>
+        <v>s</v>
       </c>
       <c r="J24" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>e</v>
+        <v>x</v>
       </c>
       <c r="K24" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>E</v>
+        <v>e</v>
       </c>
       <c r="L24" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>d</v>
+        <v>E</v>
       </c>
       <c r="M24" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>N</v>
+        <v>d</v>
       </c>
       <c r="N24" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>c</v>
+        <v>N</v>
       </c>
       <c r="O24" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>y</v>
+        <v>c</v>
       </c>
       <c r="P24" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>Y</v>
+        <v>y</v>
       </c>
       <c r="Q24" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>h</v>
+        <v>Y</v>
       </c>
       <c r="R24" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>n</v>
+        <v>h</v>
       </c>
       <c r="S24" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>r</v>
+        <v>n</v>
       </c>
       <c r="T24" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>R</v>
+        <v>r</v>
       </c>
       <c r="U24" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>f</v>
+        <v>R</v>
       </c>
       <c r="V24" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>v</v>
+        <v>f</v>
       </c>
       <c r="W24" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>8</v>
+        <v>v</v>
       </c>
       <c r="X24" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>u</v>
+        <v>8</v>
       </c>
       <c r="Y24" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>j</v>
+        <v>u</v>
       </c>
       <c r="Z24" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>K</v>
+        <v>j</v>
       </c>
       <c r="AA24" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>,</v>
+        <v>K</v>
       </c>
       <c r="AB24" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>i</v>
+        <v>,</v>
       </c>
       <c r="AC24" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>k</v>
+        <v>i</v>
       </c>
       <c r="AD24" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>m</v>
+        <v>k</v>
       </c>
       <c r="AE24" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>p</v>
+        <v>m</v>
       </c>
       <c r="AF24" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>/</v>
+        <v>p</v>
       </c>
       <c r="AG24" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>b</v>
+        <v>/</v>
       </c>
       <c r="AH24" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>t</v>
+        <v>b</v>
       </c>
       <c r="AI24" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>g</v>
+        <v>t</v>
       </c>
       <c r="AJ24" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>z</v>
+        <v>g</v>
       </c>
       <c r="AK24" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>9</v>
+        <v>z</v>
       </c>
       <c r="AL24" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>l</v>
+        <v>9</v>
       </c>
       <c r="AM24" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>M</v>
+        <v>l</v>
       </c>
       <c r="AN24" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>M</v>
       </c>
       <c r="AO24" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>;</v>
+        <v>0</v>
       </c>
       <c r="AP24" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>O</v>
+        <v>;</v>
       </c>
       <c r="AQ24" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>o</v>
+        <v>O</v>
       </c>
       <c r="AR24" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>*</v>
+        <v>o</v>
       </c>
       <c r="AS24" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>U</v>
+        <v>*</v>
       </c>
       <c r="AT24" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>J</v>
+        <v>U</v>
       </c>
       <c r="AU24" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>&lt;</v>
+        <v>J</v>
       </c>
       <c r="AV24" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>I</v>
+        <v>&lt;</v>
       </c>
       <c r="AW24" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>(</v>
+        <v>I</v>
       </c>
       <c r="AX24" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>L</v>
+        <v>(</v>
       </c>
       <c r="AY24" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>:</v>
+        <v>L</v>
       </c>
       <c r="AZ24" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>5</v>
+        <v>:</v>
       </c>
       <c r="BA24" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="BB24" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BC24" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="BD24" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>]</v>
+        <v>6</v>
       </c>
       <c r="BE24" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>[</v>
+        <v>]</v>
       </c>
       <c r="BF24" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>7</v>
+        <v>[</v>
       </c>
       <c r="BG24" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>-</v>
+        <v>7</v>
       </c>
       <c r="BH24" s="6" t="str">
         <f t="shared" si="3"/>
-        <v/>
+        <v>-</v>
       </c>
       <c r="BI24" s="6" t="str">
         <f t="shared" si="3"/>
@@ -13393,8 +13393,8 @@
     <row r="28" spans="1:87" s="245" customFormat="1" outlineLevel="1">
       <c r="A28" s="1"/>
       <c r="B28" s="1" t="str">
-        <f xml:space="preserve"> _xlfn.CONCAT("    - xlit|", D5:BH5, "|", D6:BH6, "|")</f>
-        <v xml:space="preserve">    - xlit|!qa2wsxeEdNcyYhnrRfv8ujK,ikmp/btgz9lM0;Oo*UJ&lt;I(L:5346][7-|ㆠㄆㄇㄉㄊㄋㄌㄍㆣㄎㄫㄏㄗㆡㄘㄙㄐㆢㄑㄒㄚㄧㄨㆨㆤㆦㄜㆬㄣㆭㆴㆵㆻㆷㄞㄠㆰㄢㄤㆱㆲㆩㆪㆫㆥㆧㆮㆯ一七三二五八四入゜|</v>
+        <f xml:space="preserve"> _xlfn.CONCAT("    - xlit|", C5:BH5, "|", C6:BH6, "|")</f>
+        <v xml:space="preserve">    - xlit|1!qa2wsxeEdNcyYhnrRfv8ujK,ikmp/btgz9lM0;Oo*UJ&lt;I(L:5346][7-|ㄅㆠㄆㄇㄉㄊㄋㄌㄍㆣㄎㄫㄏㄗㆡㄘㄙㄐㆢㄑㄒㄚㄧㄨㆨㆤㆦㄜㆬㄣㆭㆴㆵㆻㆷㄞㄠㆰㄢㄤㆱㆲㆩㆪㆫㆥㆧㆮㆯ一七三二五八四入゜|</v>
       </c>
       <c r="C28" s="1"/>
       <c r="D28" s="1"/>
@@ -13692,7 +13692,7 @@
       </c>
       <c r="B31" s="1">
         <f xml:space="preserve"> SEARCH("|", $B$28, B30+1)</f>
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C31" s="1"/>
       <c r="D31" s="1"/>
@@ -13778,7 +13778,7 @@
       </c>
       <c r="B32" s="1">
         <f xml:space="preserve"> SEARCH("|", $B$28, B31+1)</f>
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C32" s="1"/>
       <c r="D32" s="1"/>
@@ -13945,11 +13945,11 @@
       </c>
       <c r="B34" s="1">
         <f xml:space="preserve"> LEN(C34)</f>
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C34" s="1" t="str">
         <f xml:space="preserve"> MID($B$28,B30+1, (B31-B30-1))</f>
-        <v>!qa2wsxeEdNcyYhnrRfv8ujK,ikmp/btgz9lM0;Oo*UJ&lt;I(L:5346][7-</v>
+        <v>1!qa2wsxeEdNcyYhnrRfv8ujK,ikmp/btgz9lM0;Oo*UJ&lt;I(L:5346][7-</v>
       </c>
       <c r="D34" s="1"/>
       <c r="E34" s="1"/>
@@ -14034,11 +14034,11 @@
       </c>
       <c r="B35" s="1">
         <f xml:space="preserve"> LEN(C35)</f>
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C35" s="1" t="str">
         <f xml:space="preserve"> MID($B$28,B31+1, (B32-B31-1))</f>
-        <v>ㆠㄆㄇㄉㄊㄋㄌㄍㆣㄎㄫㄏㄗㆡㄘㄙㄐㆢㄑㄒㄚㄧㄨㆨㆤㆦㄜㆬㄣㆭㆴㆵㆻㆷㄞㄠㆰㄢㄤㆱㆲㆩㆪㆫㆥㆧㆮㆯ一七三二五八四入゜</v>
+        <v>ㄅㆠㄆㄇㄉㄊㄋㄌㄍㆣㄎㄫㄏㄗㆡㄘㄙㄐㆢㄑㄒㄚㄧㄨㆨㆤㆦㄜㆬㄣㆭㆴㆵㆻㆷㄞㄠㆰㄢㄤㆱㆲㆩㆪㆫㆥㆧㆮㆯ一七三二五八四入゜</v>
       </c>
       <c r="D35" s="1"/>
       <c r="E35" s="1"/>
@@ -14466,235 +14466,235 @@
       <c r="B38" s="1"/>
       <c r="C38" s="5" t="str">
         <f>C23</f>
-        <v>b</v>
+        <v>p</v>
       </c>
       <c r="D38" s="5" t="str">
         <f t="shared" ref="D38:BH38" si="5">D23</f>
-        <v>P</v>
+        <v>b</v>
       </c>
       <c r="E38" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>m</v>
+        <v>P</v>
       </c>
       <c r="F38" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>t</v>
+        <v>m</v>
       </c>
       <c r="G38" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>T</v>
+        <v>t</v>
       </c>
       <c r="H38" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>n</v>
+        <v>T</v>
       </c>
       <c r="I38" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>l</v>
+        <v>n</v>
       </c>
       <c r="J38" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>k</v>
+        <v>l</v>
       </c>
       <c r="K38" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>g</v>
+        <v>k</v>
       </c>
       <c r="L38" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>K</v>
+        <v>g</v>
       </c>
       <c r="M38" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>ŋ</v>
+        <v>K</v>
       </c>
       <c r="N38" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>h</v>
+        <v>ŋ</v>
       </c>
       <c r="O38" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>z</v>
+        <v>h</v>
       </c>
       <c r="P38" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>j</v>
+        <v>z</v>
       </c>
       <c r="Q38" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>c</v>
+        <v>j</v>
       </c>
       <c r="R38" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>s</v>
+        <v>c</v>
       </c>
       <c r="S38" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>Z</v>
+        <v>s</v>
       </c>
       <c r="T38" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>J</v>
+        <v>Z</v>
       </c>
       <c r="U38" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>C</v>
+        <v>J</v>
       </c>
       <c r="V38" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>S</v>
+        <v>C</v>
       </c>
       <c r="W38" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>a</v>
+        <v>S</v>
       </c>
       <c r="X38" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>i</v>
+        <v>a</v>
       </c>
       <c r="Y38" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>u</v>
+        <v>i</v>
       </c>
       <c r="Z38" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>w</v>
+        <v>u</v>
       </c>
       <c r="AA38" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>e</v>
+        <v>w</v>
       </c>
       <c r="AB38" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>O</v>
+        <v>e</v>
       </c>
       <c r="AC38" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>ə</v>
+        <v>O</v>
       </c>
       <c r="AD38" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>M</v>
+        <v>ə</v>
       </c>
       <c r="AE38" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>N</v>
+        <v>M</v>
       </c>
       <c r="AF38" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>G</v>
+        <v>N</v>
       </c>
       <c r="AG38" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>R</v>
+        <v>G</v>
       </c>
       <c r="AH38" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>F</v>
+        <v>R</v>
       </c>
       <c r="AI38" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>Q</v>
+        <v>F</v>
       </c>
       <c r="AJ38" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>V</v>
+        <v>Q</v>
       </c>
       <c r="AK38" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>I</v>
+        <v>V</v>
       </c>
       <c r="AL38" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>U</v>
+        <v>I</v>
       </c>
       <c r="AM38" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>Y</v>
+        <v>U</v>
       </c>
       <c r="AN38" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>@</v>
+        <v>Y</v>
       </c>
       <c r="AO38" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>A</v>
+        <v>@</v>
       </c>
       <c r="AP38" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>W</v>
+        <v>A</v>
       </c>
       <c r="AQ38" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>H</v>
+        <v>W</v>
       </c>
       <c r="AR38" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>d</v>
+        <v>H</v>
       </c>
       <c r="AS38" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>f</v>
+        <v>d</v>
       </c>
       <c r="AT38" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>q</v>
+        <v>f</v>
       </c>
       <c r="AU38" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>r</v>
+        <v>q</v>
       </c>
       <c r="AV38" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>v</v>
+        <v>r</v>
       </c>
       <c r="AW38" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>x</v>
+        <v>v</v>
       </c>
       <c r="AX38" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>y</v>
+        <v>x</v>
       </c>
       <c r="AY38" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>1</v>
+        <v>y</v>
       </c>
       <c r="AZ38" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="BA38" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="BB38" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BC38" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="BD38" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="BE38" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="BF38" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>&amp;</v>
+        <v>4</v>
       </c>
       <c r="BG38" s="5" t="str">
         <f t="shared" si="5"/>
-        <v>L</v>
+        <v>&amp;</v>
       </c>
       <c r="BH38" s="5" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>L</v>
       </c>
       <c r="BI38" s="5" t="str">
         <f xml:space="preserve"> _xlfn.XLOOKUP(BI39, $C$24:$BJ$24,$C$23:$BJ$23, "")</f>
@@ -14729,235 +14729,235 @@
       <c r="B39" s="1"/>
       <c r="C39" s="6" t="str">
         <f t="shared" ref="C39:BJ39" si="6" xml:space="preserve"> MID($C$34,C$37,1)</f>
-        <v>!</v>
+        <v>1</v>
       </c>
       <c r="D39" s="6" t="str">
         <f t="shared" si="6"/>
-        <v>q</v>
+        <v>!</v>
       </c>
       <c r="E39" s="6" t="str">
         <f t="shared" si="6"/>
-        <v>a</v>
+        <v>q</v>
       </c>
       <c r="F39" s="6" t="str">
         <f t="shared" si="6"/>
-        <v>2</v>
+        <v>a</v>
       </c>
       <c r="G39" s="6" t="str">
         <f t="shared" si="6"/>
-        <v>w</v>
+        <v>2</v>
       </c>
       <c r="H39" s="6" t="str">
         <f t="shared" si="6"/>
-        <v>s</v>
+        <v>w</v>
       </c>
       <c r="I39" s="6" t="str">
         <f t="shared" si="6"/>
-        <v>x</v>
+        <v>s</v>
       </c>
       <c r="J39" s="6" t="str">
         <f t="shared" si="6"/>
-        <v>e</v>
+        <v>x</v>
       </c>
       <c r="K39" s="6" t="str">
         <f t="shared" si="6"/>
-        <v>E</v>
+        <v>e</v>
       </c>
       <c r="L39" s="6" t="str">
         <f t="shared" si="6"/>
-        <v>d</v>
+        <v>E</v>
       </c>
       <c r="M39" s="6" t="str">
         <f t="shared" si="6"/>
-        <v>N</v>
+        <v>d</v>
       </c>
       <c r="N39" s="6" t="str">
         <f t="shared" si="6"/>
-        <v>c</v>
+        <v>N</v>
       </c>
       <c r="O39" s="6" t="str">
         <f t="shared" si="6"/>
-        <v>y</v>
+        <v>c</v>
       </c>
       <c r="P39" s="6" t="str">
         <f t="shared" si="6"/>
-        <v>Y</v>
+        <v>y</v>
       </c>
       <c r="Q39" s="6" t="str">
         <f t="shared" si="6"/>
-        <v>h</v>
+        <v>Y</v>
       </c>
       <c r="R39" s="6" t="str">
         <f t="shared" si="6"/>
-        <v>n</v>
+        <v>h</v>
       </c>
       <c r="S39" s="6" t="str">
         <f t="shared" si="6"/>
-        <v>r</v>
+        <v>n</v>
       </c>
       <c r="T39" s="6" t="str">
         <f t="shared" si="6"/>
-        <v>R</v>
+        <v>r</v>
       </c>
       <c r="U39" s="6" t="str">
         <f t="shared" si="6"/>
-        <v>f</v>
+        <v>R</v>
       </c>
       <c r="V39" s="6" t="str">
         <f t="shared" si="6"/>
-        <v>v</v>
+        <v>f</v>
       </c>
       <c r="W39" s="6" t="str">
         <f t="shared" si="6"/>
-        <v>8</v>
+        <v>v</v>
       </c>
       <c r="X39" s="6" t="str">
         <f t="shared" si="6"/>
-        <v>u</v>
+        <v>8</v>
       </c>
       <c r="Y39" s="6" t="str">
         <f t="shared" si="6"/>
-        <v>j</v>
+        <v>u</v>
       </c>
       <c r="Z39" s="6" t="str">
         <f t="shared" si="6"/>
-        <v>K</v>
+        <v>j</v>
       </c>
       <c r="AA39" s="6" t="str">
         <f t="shared" si="6"/>
-        <v>,</v>
+        <v>K</v>
       </c>
       <c r="AB39" s="6" t="str">
         <f t="shared" si="6"/>
-        <v>i</v>
+        <v>,</v>
       </c>
       <c r="AC39" s="6" t="str">
         <f t="shared" si="6"/>
-        <v>k</v>
+        <v>i</v>
       </c>
       <c r="AD39" s="6" t="str">
         <f t="shared" si="6"/>
-        <v>m</v>
+        <v>k</v>
       </c>
       <c r="AE39" s="6" t="str">
         <f t="shared" si="6"/>
-        <v>p</v>
+        <v>m</v>
       </c>
       <c r="AF39" s="6" t="str">
         <f t="shared" si="6"/>
-        <v>/</v>
+        <v>p</v>
       </c>
       <c r="AG39" s="6" t="str">
         <f t="shared" si="6"/>
-        <v>b</v>
+        <v>/</v>
       </c>
       <c r="AH39" s="6" t="str">
         <f t="shared" si="6"/>
-        <v>t</v>
+        <v>b</v>
       </c>
       <c r="AI39" s="6" t="str">
         <f t="shared" si="6"/>
-        <v>g</v>
+        <v>t</v>
       </c>
       <c r="AJ39" s="6" t="str">
         <f t="shared" si="6"/>
-        <v>z</v>
+        <v>g</v>
       </c>
       <c r="AK39" s="6" t="str">
         <f t="shared" si="6"/>
-        <v>9</v>
+        <v>z</v>
       </c>
       <c r="AL39" s="6" t="str">
         <f t="shared" si="6"/>
-        <v>l</v>
+        <v>9</v>
       </c>
       <c r="AM39" s="6" t="str">
         <f t="shared" si="6"/>
-        <v>M</v>
+        <v>l</v>
       </c>
       <c r="AN39" s="6" t="str">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>M</v>
       </c>
       <c r="AO39" s="6" t="str">
         <f t="shared" si="6"/>
-        <v>;</v>
+        <v>0</v>
       </c>
       <c r="AP39" s="6" t="str">
         <f t="shared" si="6"/>
-        <v>O</v>
+        <v>;</v>
       </c>
       <c r="AQ39" s="6" t="str">
         <f t="shared" si="6"/>
-        <v>o</v>
+        <v>O</v>
       </c>
       <c r="AR39" s="6" t="str">
         <f t="shared" si="6"/>
-        <v>*</v>
+        <v>o</v>
       </c>
       <c r="AS39" s="6" t="str">
         <f t="shared" si="6"/>
-        <v>U</v>
+        <v>*</v>
       </c>
       <c r="AT39" s="6" t="str">
         <f t="shared" si="6"/>
-        <v>J</v>
+        <v>U</v>
       </c>
       <c r="AU39" s="6" t="str">
         <f t="shared" si="6"/>
-        <v>&lt;</v>
+        <v>J</v>
       </c>
       <c r="AV39" s="6" t="str">
         <f t="shared" si="6"/>
-        <v>I</v>
+        <v>&lt;</v>
       </c>
       <c r="AW39" s="6" t="str">
         <f t="shared" si="6"/>
-        <v>(</v>
+        <v>I</v>
       </c>
       <c r="AX39" s="6" t="str">
         <f t="shared" si="6"/>
-        <v>L</v>
+        <v>(</v>
       </c>
       <c r="AY39" s="6" t="str">
         <f t="shared" si="6"/>
-        <v>:</v>
+        <v>L</v>
       </c>
       <c r="AZ39" s="6" t="str">
         <f t="shared" si="6"/>
-        <v>5</v>
+        <v>:</v>
       </c>
       <c r="BA39" s="6" t="str">
         <f t="shared" si="6"/>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="BB39" s="6" t="str">
         <f t="shared" si="6"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BC39" s="6" t="str">
         <f t="shared" si="6"/>
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="BD39" s="6" t="str">
         <f t="shared" si="6"/>
-        <v>]</v>
+        <v>6</v>
       </c>
       <c r="BE39" s="6" t="str">
         <f t="shared" si="6"/>
-        <v>[</v>
+        <v>]</v>
       </c>
       <c r="BF39" s="6" t="str">
         <f t="shared" si="6"/>
-        <v>7</v>
+        <v>[</v>
       </c>
       <c r="BG39" s="6" t="str">
         <f t="shared" si="6"/>
-        <v>-</v>
+        <v>7</v>
       </c>
       <c r="BH39" s="6" t="str">
         <f t="shared" si="6"/>
-        <v/>
+        <v>-</v>
       </c>
       <c r="BI39" s="6" t="str">
         <f t="shared" si="6"/>
@@ -14992,235 +14992,235 @@
       <c r="B40" s="1"/>
       <c r="C40" s="8" t="str">
         <f t="shared" ref="C40:BJ40" si="7" xml:space="preserve"> MID($C$35,C$37,1)</f>
-        <v>ㆠ</v>
+        <v>ㄅ</v>
       </c>
       <c r="D40" s="8" t="str">
         <f t="shared" si="7"/>
-        <v>ㄆ</v>
+        <v>ㆠ</v>
       </c>
       <c r="E40" s="8" t="str">
         <f t="shared" si="7"/>
-        <v>ㄇ</v>
+        <v>ㄆ</v>
       </c>
       <c r="F40" s="8" t="str">
         <f t="shared" si="7"/>
-        <v>ㄉ</v>
+        <v>ㄇ</v>
       </c>
       <c r="G40" s="8" t="str">
         <f t="shared" si="7"/>
-        <v>ㄊ</v>
+        <v>ㄉ</v>
       </c>
       <c r="H40" s="8" t="str">
         <f t="shared" si="7"/>
-        <v>ㄋ</v>
+        <v>ㄊ</v>
       </c>
       <c r="I40" s="8" t="str">
         <f t="shared" si="7"/>
-        <v>ㄌ</v>
+        <v>ㄋ</v>
       </c>
       <c r="J40" s="8" t="str">
         <f t="shared" si="7"/>
-        <v>ㄍ</v>
+        <v>ㄌ</v>
       </c>
       <c r="K40" s="8" t="str">
         <f t="shared" si="7"/>
-        <v>ㆣ</v>
+        <v>ㄍ</v>
       </c>
       <c r="L40" s="8" t="str">
         <f t="shared" si="7"/>
-        <v>ㄎ</v>
+        <v>ㆣ</v>
       </c>
       <c r="M40" s="8" t="str">
         <f t="shared" si="7"/>
-        <v>ㄫ</v>
+        <v>ㄎ</v>
       </c>
       <c r="N40" s="8" t="str">
         <f t="shared" si="7"/>
-        <v>ㄏ</v>
+        <v>ㄫ</v>
       </c>
       <c r="O40" s="8" t="str">
         <f t="shared" si="7"/>
-        <v>ㄗ</v>
+        <v>ㄏ</v>
       </c>
       <c r="P40" s="8" t="str">
         <f t="shared" si="7"/>
-        <v>ㆡ</v>
+        <v>ㄗ</v>
       </c>
       <c r="Q40" s="8" t="str">
         <f t="shared" si="7"/>
-        <v>ㄘ</v>
+        <v>ㆡ</v>
       </c>
       <c r="R40" s="8" t="str">
         <f t="shared" si="7"/>
-        <v>ㄙ</v>
+        <v>ㄘ</v>
       </c>
       <c r="S40" s="8" t="str">
         <f t="shared" si="7"/>
-        <v>ㄐ</v>
+        <v>ㄙ</v>
       </c>
       <c r="T40" s="8" t="str">
         <f t="shared" si="7"/>
-        <v>ㆢ</v>
+        <v>ㄐ</v>
       </c>
       <c r="U40" s="8" t="str">
         <f t="shared" si="7"/>
-        <v>ㄑ</v>
+        <v>ㆢ</v>
       </c>
       <c r="V40" s="8" t="str">
         <f t="shared" si="7"/>
-        <v>ㄒ</v>
+        <v>ㄑ</v>
       </c>
       <c r="W40" s="8" t="str">
         <f t="shared" si="7"/>
-        <v>ㄚ</v>
+        <v>ㄒ</v>
       </c>
       <c r="X40" s="8" t="str">
         <f t="shared" si="7"/>
-        <v>ㄧ</v>
+        <v>ㄚ</v>
       </c>
       <c r="Y40" s="8" t="str">
         <f t="shared" si="7"/>
-        <v>ㄨ</v>
+        <v>ㄧ</v>
       </c>
       <c r="Z40" s="8" t="str">
         <f t="shared" si="7"/>
-        <v>ㆨ</v>
+        <v>ㄨ</v>
       </c>
       <c r="AA40" s="8" t="str">
         <f t="shared" si="7"/>
-        <v>ㆤ</v>
+        <v>ㆨ</v>
       </c>
       <c r="AB40" s="8" t="str">
         <f t="shared" si="7"/>
-        <v>ㆦ</v>
+        <v>ㆤ</v>
       </c>
       <c r="AC40" s="8" t="str">
         <f t="shared" si="7"/>
-        <v>ㄜ</v>
+        <v>ㆦ</v>
       </c>
       <c r="AD40" s="8" t="str">
         <f t="shared" si="7"/>
-        <v>ㆬ</v>
+        <v>ㄜ</v>
       </c>
       <c r="AE40" s="8" t="str">
         <f t="shared" si="7"/>
-        <v>ㄣ</v>
+        <v>ㆬ</v>
       </c>
       <c r="AF40" s="8" t="str">
         <f t="shared" si="7"/>
-        <v>ㆭ</v>
+        <v>ㄣ</v>
       </c>
       <c r="AG40" s="8" t="str">
         <f t="shared" si="7"/>
-        <v>ㆴ</v>
+        <v>ㆭ</v>
       </c>
       <c r="AH40" s="8" t="str">
         <f t="shared" si="7"/>
-        <v>ㆵ</v>
+        <v>ㆴ</v>
       </c>
       <c r="AI40" s="8" t="str">
         <f t="shared" si="7"/>
-        <v>ㆻ</v>
+        <v>ㆵ</v>
       </c>
       <c r="AJ40" s="8" t="str">
         <f t="shared" si="7"/>
-        <v>ㆷ</v>
+        <v>ㆻ</v>
       </c>
       <c r="AK40" s="8" t="str">
         <f t="shared" si="7"/>
-        <v>ㄞ</v>
+        <v>ㆷ</v>
       </c>
       <c r="AL40" s="8" t="str">
         <f t="shared" si="7"/>
-        <v>ㄠ</v>
+        <v>ㄞ</v>
       </c>
       <c r="AM40" s="8" t="str">
         <f t="shared" si="7"/>
-        <v>ㆰ</v>
+        <v>ㄠ</v>
       </c>
       <c r="AN40" s="8" t="str">
         <f t="shared" si="7"/>
-        <v>ㄢ</v>
+        <v>ㆰ</v>
       </c>
       <c r="AO40" s="8" t="str">
         <f t="shared" si="7"/>
-        <v>ㄤ</v>
+        <v>ㄢ</v>
       </c>
       <c r="AP40" s="8" t="str">
         <f t="shared" si="7"/>
-        <v>ㆱ</v>
+        <v>ㄤ</v>
       </c>
       <c r="AQ40" s="8" t="str">
         <f t="shared" si="7"/>
-        <v>ㆲ</v>
+        <v>ㆱ</v>
       </c>
       <c r="AR40" s="8" t="str">
         <f t="shared" si="7"/>
-        <v>ㆩ</v>
+        <v>ㆲ</v>
       </c>
       <c r="AS40" s="8" t="str">
         <f t="shared" si="7"/>
-        <v>ㆪ</v>
+        <v>ㆩ</v>
       </c>
       <c r="AT40" s="8" t="str">
         <f t="shared" si="7"/>
-        <v>ㆫ</v>
+        <v>ㆪ</v>
       </c>
       <c r="AU40" s="8" t="str">
         <f t="shared" si="7"/>
-        <v>ㆥ</v>
+        <v>ㆫ</v>
       </c>
       <c r="AV40" s="8" t="str">
         <f t="shared" si="7"/>
-        <v>ㆧ</v>
+        <v>ㆥ</v>
       </c>
       <c r="AW40" s="8" t="str">
         <f t="shared" si="7"/>
-        <v>ㆮ</v>
+        <v>ㆧ</v>
       </c>
       <c r="AX40" s="8" t="str">
         <f t="shared" si="7"/>
-        <v>ㆯ</v>
+        <v>ㆮ</v>
       </c>
       <c r="AY40" s="8" t="str">
         <f t="shared" si="7"/>
-        <v>一</v>
+        <v>ㆯ</v>
       </c>
       <c r="AZ40" s="8" t="str">
         <f t="shared" si="7"/>
-        <v>七</v>
+        <v>一</v>
       </c>
       <c r="BA40" s="8" t="str">
         <f t="shared" si="7"/>
-        <v>三</v>
+        <v>七</v>
       </c>
       <c r="BB40" s="8" t="str">
         <f t="shared" si="7"/>
-        <v>二</v>
+        <v>三</v>
       </c>
       <c r="BC40" s="8" t="str">
         <f t="shared" si="7"/>
-        <v>五</v>
+        <v>二</v>
       </c>
       <c r="BD40" s="8" t="str">
         <f t="shared" si="7"/>
-        <v>八</v>
+        <v>五</v>
       </c>
       <c r="BE40" s="8" t="str">
         <f t="shared" si="7"/>
-        <v>四</v>
+        <v>八</v>
       </c>
       <c r="BF40" s="8" t="str">
         <f t="shared" si="7"/>
-        <v>入</v>
+        <v>四</v>
       </c>
       <c r="BG40" s="8" t="str">
         <f t="shared" si="7"/>
-        <v>゜</v>
+        <v>入</v>
       </c>
       <c r="BH40" s="8" t="str">
         <f t="shared" si="7"/>
-        <v/>
+        <v>゜</v>
       </c>
       <c r="BI40" s="8" t="str">
         <f t="shared" si="7"/>
@@ -24227,25 +24227,25 @@
   <sheetData>
     <row r="1" spans="2:19" ht="21.75" thickBot="1"/>
     <row r="2" spans="2:19" ht="24" thickBot="1">
-      <c r="B2" s="260" t="s">
+      <c r="B2" s="268" t="s">
         <v>332</v>
       </c>
-      <c r="C2" s="262" t="s">
+      <c r="C2" s="270" t="s">
         <v>333</v>
       </c>
-      <c r="D2" s="263"/>
-      <c r="E2" s="266" t="s">
+      <c r="D2" s="271"/>
+      <c r="E2" s="274" t="s">
         <v>334</v>
       </c>
-      <c r="F2" s="267"/>
-      <c r="G2" s="268"/>
-      <c r="H2" s="266" t="s">
+      <c r="F2" s="275"/>
+      <c r="G2" s="276"/>
+      <c r="H2" s="274" t="s">
         <v>335</v>
       </c>
-      <c r="I2" s="267"/>
-      <c r="J2" s="267"/>
-      <c r="K2" s="267"/>
-      <c r="L2" s="268"/>
+      <c r="I2" s="275"/>
+      <c r="J2" s="275"/>
+      <c r="K2" s="275"/>
+      <c r="L2" s="276"/>
       <c r="O2" s="236" t="s">
         <v>484</v>
       </c>
@@ -24260,9 +24260,9 @@
       </c>
     </row>
     <row r="3" spans="2:19" ht="24" thickBot="1">
-      <c r="B3" s="261"/>
-      <c r="C3" s="264"/>
-      <c r="D3" s="265"/>
+      <c r="B3" s="269"/>
+      <c r="C3" s="272"/>
+      <c r="D3" s="273"/>
       <c r="E3" s="234" t="s">
         <v>336</v>
       </c>
@@ -24281,10 +24281,10 @@
       <c r="J3" s="234" t="s">
         <v>341</v>
       </c>
-      <c r="K3" s="266" t="s">
+      <c r="K3" s="274" t="s">
         <v>342</v>
       </c>
-      <c r="L3" s="268"/>
+      <c r="L3" s="276"/>
       <c r="O3" s="236" t="s">
         <v>278</v>
       </c>
@@ -25176,57 +25176,57 @@
       <c r="B27" s="234" t="s">
         <v>447</v>
       </c>
-      <c r="C27" s="269" t="s">
+      <c r="C27" s="265" t="s">
         <v>192</v>
       </c>
-      <c r="D27" s="270"/>
-      <c r="E27" s="269" t="s">
+      <c r="D27" s="266"/>
+      <c r="E27" s="265" t="s">
         <v>448</v>
       </c>
-      <c r="F27" s="271"/>
-      <c r="G27" s="271"/>
-      <c r="H27" s="271"/>
-      <c r="I27" s="271"/>
-      <c r="J27" s="270"/>
-      <c r="K27" s="269" t="s">
+      <c r="F27" s="267"/>
+      <c r="G27" s="267"/>
+      <c r="H27" s="267"/>
+      <c r="I27" s="267"/>
+      <c r="J27" s="266"/>
+      <c r="K27" s="265" t="s">
         <v>449</v>
       </c>
-      <c r="L27" s="270"/>
+      <c r="L27" s="266"/>
     </row>
     <row r="28" spans="2:20" ht="24" thickBot="1">
       <c r="B28" s="234" t="s">
         <v>450</v>
       </c>
-      <c r="C28" s="269" t="s">
+      <c r="C28" s="265" t="s">
         <v>451</v>
       </c>
-      <c r="D28" s="270"/>
-      <c r="E28" s="269" t="s">
+      <c r="D28" s="266"/>
+      <c r="E28" s="265" t="s">
         <v>448</v>
       </c>
-      <c r="F28" s="271"/>
-      <c r="G28" s="271"/>
-      <c r="H28" s="271"/>
-      <c r="I28" s="271"/>
-      <c r="J28" s="270"/>
-      <c r="K28" s="269" t="s">
+      <c r="F28" s="267"/>
+      <c r="G28" s="267"/>
+      <c r="H28" s="267"/>
+      <c r="I28" s="267"/>
+      <c r="J28" s="266"/>
+      <c r="K28" s="265" t="s">
         <v>452</v>
       </c>
-      <c r="L28" s="270"/>
+      <c r="L28" s="266"/>
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="C2:D3"/>
+    <mergeCell ref="E2:G2"/>
+    <mergeCell ref="H2:L2"/>
+    <mergeCell ref="K3:L3"/>
     <mergeCell ref="C27:D27"/>
     <mergeCell ref="E27:J27"/>
     <mergeCell ref="K27:L27"/>
     <mergeCell ref="C28:D28"/>
     <mergeCell ref="E28:J28"/>
     <mergeCell ref="K28:L28"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="C2:D3"/>
-    <mergeCell ref="E2:G2"/>
-    <mergeCell ref="H2:L2"/>
-    <mergeCell ref="K3:L3"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -25248,30 +25248,30 @@
   <sheetData>
     <row r="1" spans="2:20" ht="21.75" thickBot="1"/>
     <row r="2" spans="2:20" ht="24" thickBot="1">
-      <c r="B2" s="260" t="s">
+      <c r="B2" s="268" t="s">
         <v>332</v>
       </c>
-      <c r="C2" s="262" t="s">
+      <c r="C2" s="270" t="s">
         <v>333</v>
       </c>
-      <c r="D2" s="263"/>
-      <c r="E2" s="266" t="s">
+      <c r="D2" s="271"/>
+      <c r="E2" s="274" t="s">
         <v>334</v>
       </c>
-      <c r="F2" s="267"/>
-      <c r="G2" s="268"/>
-      <c r="H2" s="266" t="s">
+      <c r="F2" s="275"/>
+      <c r="G2" s="276"/>
+      <c r="H2" s="274" t="s">
         <v>335</v>
       </c>
-      <c r="I2" s="267"/>
-      <c r="J2" s="267"/>
-      <c r="K2" s="267"/>
-      <c r="L2" s="268"/>
+      <c r="I2" s="275"/>
+      <c r="J2" s="275"/>
+      <c r="K2" s="275"/>
+      <c r="L2" s="276"/>
     </row>
     <row r="3" spans="2:20" ht="24" thickBot="1">
-      <c r="B3" s="261"/>
-      <c r="C3" s="264"/>
-      <c r="D3" s="265"/>
+      <c r="B3" s="269"/>
+      <c r="C3" s="272"/>
+      <c r="D3" s="273"/>
       <c r="E3" s="234" t="s">
         <v>336</v>
       </c>
@@ -25290,10 +25290,10 @@
       <c r="J3" s="234" t="s">
         <v>341</v>
       </c>
-      <c r="K3" s="266" t="s">
+      <c r="K3" s="274" t="s">
         <v>342</v>
       </c>
-      <c r="L3" s="268"/>
+      <c r="L3" s="276"/>
       <c r="N3" s="240" t="s">
         <v>509</v>
       </c>
@@ -26326,43 +26326,43 @@
       <c r="B27" s="234" t="s">
         <v>447</v>
       </c>
-      <c r="C27" s="269" t="s">
+      <c r="C27" s="265" t="s">
         <v>192</v>
       </c>
-      <c r="D27" s="270"/>
-      <c r="E27" s="269" t="s">
+      <c r="D27" s="266"/>
+      <c r="E27" s="265" t="s">
         <v>448</v>
       </c>
-      <c r="F27" s="271"/>
-      <c r="G27" s="271"/>
-      <c r="H27" s="271"/>
-      <c r="I27" s="271"/>
-      <c r="J27" s="270"/>
-      <c r="K27" s="269" t="s">
+      <c r="F27" s="267"/>
+      <c r="G27" s="267"/>
+      <c r="H27" s="267"/>
+      <c r="I27" s="267"/>
+      <c r="J27" s="266"/>
+      <c r="K27" s="265" t="s">
         <v>449</v>
       </c>
-      <c r="L27" s="270"/>
+      <c r="L27" s="266"/>
     </row>
     <row r="28" spans="2:21" ht="24" thickBot="1">
       <c r="B28" s="234" t="s">
         <v>450</v>
       </c>
-      <c r="C28" s="269" t="s">
+      <c r="C28" s="265" t="s">
         <v>451</v>
       </c>
-      <c r="D28" s="270"/>
-      <c r="E28" s="269" t="s">
+      <c r="D28" s="266"/>
+      <c r="E28" s="265" t="s">
         <v>448</v>
       </c>
-      <c r="F28" s="271"/>
-      <c r="G28" s="271"/>
-      <c r="H28" s="271"/>
-      <c r="I28" s="271"/>
-      <c r="J28" s="270"/>
-      <c r="K28" s="269" t="s">
+      <c r="F28" s="267"/>
+      <c r="G28" s="267"/>
+      <c r="H28" s="267"/>
+      <c r="I28" s="267"/>
+      <c r="J28" s="266"/>
+      <c r="K28" s="265" t="s">
         <v>452</v>
       </c>
-      <c r="L28" s="270"/>
+      <c r="L28" s="266"/>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="N4:T20">
@@ -26401,25 +26401,25 @@
   <sheetData>
     <row r="1" spans="2:18" ht="21.75" thickBot="1"/>
     <row r="2" spans="2:18" ht="24" thickBot="1">
-      <c r="B2" s="260" t="s">
+      <c r="B2" s="268" t="s">
         <v>332</v>
       </c>
-      <c r="C2" s="262" t="s">
+      <c r="C2" s="270" t="s">
         <v>333</v>
       </c>
-      <c r="D2" s="263"/>
-      <c r="E2" s="266" t="s">
+      <c r="D2" s="271"/>
+      <c r="E2" s="274" t="s">
         <v>334</v>
       </c>
-      <c r="F2" s="267"/>
-      <c r="G2" s="268"/>
-      <c r="H2" s="266" t="s">
+      <c r="F2" s="275"/>
+      <c r="G2" s="276"/>
+      <c r="H2" s="274" t="s">
         <v>335</v>
       </c>
-      <c r="I2" s="267"/>
-      <c r="J2" s="267"/>
-      <c r="K2" s="267"/>
-      <c r="L2" s="268"/>
+      <c r="I2" s="275"/>
+      <c r="J2" s="275"/>
+      <c r="K2" s="275"/>
+      <c r="L2" s="276"/>
       <c r="P2" s="236" t="str">
         <f xml:space="preserve"> "([48])"</f>
         <v>([48])</v>
@@ -26429,9 +26429,9 @@
       </c>
     </row>
     <row r="3" spans="2:18" ht="24" thickBot="1">
-      <c r="B3" s="261"/>
-      <c r="C3" s="264"/>
-      <c r="D3" s="265"/>
+      <c r="B3" s="269"/>
+      <c r="C3" s="272"/>
+      <c r="D3" s="273"/>
       <c r="E3" s="234" t="s">
         <v>336</v>
       </c>
@@ -26450,10 +26450,10 @@
       <c r="J3" s="234" t="s">
         <v>341</v>
       </c>
-      <c r="K3" s="266" t="s">
+      <c r="K3" s="274" t="s">
         <v>342</v>
       </c>
-      <c r="L3" s="268"/>
+      <c r="L3" s="276"/>
       <c r="N3" s="236" t="s">
         <v>454</v>
       </c>
@@ -27345,43 +27345,43 @@
       <c r="B27" s="234" t="s">
         <v>447</v>
       </c>
-      <c r="C27" s="269" t="s">
+      <c r="C27" s="265" t="s">
         <v>192</v>
       </c>
-      <c r="D27" s="270"/>
-      <c r="E27" s="269" t="s">
+      <c r="D27" s="266"/>
+      <c r="E27" s="265" t="s">
         <v>448</v>
       </c>
-      <c r="F27" s="271"/>
-      <c r="G27" s="271"/>
-      <c r="H27" s="271"/>
-      <c r="I27" s="271"/>
-      <c r="J27" s="270"/>
-      <c r="K27" s="269" t="s">
+      <c r="F27" s="267"/>
+      <c r="G27" s="267"/>
+      <c r="H27" s="267"/>
+      <c r="I27" s="267"/>
+      <c r="J27" s="266"/>
+      <c r="K27" s="265" t="s">
         <v>449</v>
       </c>
-      <c r="L27" s="270"/>
+      <c r="L27" s="266"/>
     </row>
     <row r="28" spans="2:19" ht="24" thickBot="1">
       <c r="B28" s="234" t="s">
         <v>450</v>
       </c>
-      <c r="C28" s="269" t="s">
+      <c r="C28" s="265" t="s">
         <v>451</v>
       </c>
-      <c r="D28" s="270"/>
-      <c r="E28" s="269" t="s">
+      <c r="D28" s="266"/>
+      <c r="E28" s="265" t="s">
         <v>448</v>
       </c>
-      <c r="F28" s="271"/>
-      <c r="G28" s="271"/>
-      <c r="H28" s="271"/>
-      <c r="I28" s="271"/>
-      <c r="J28" s="270"/>
-      <c r="K28" s="269" t="s">
+      <c r="F28" s="267"/>
+      <c r="G28" s="267"/>
+      <c r="H28" s="267"/>
+      <c r="I28" s="267"/>
+      <c r="J28" s="266"/>
+      <c r="K28" s="265" t="s">
         <v>452</v>
       </c>
-      <c r="L28" s="270"/>
+      <c r="L28" s="266"/>
     </row>
   </sheetData>
   <mergeCells count="11">
@@ -42765,196 +42765,196 @@
       </c>
     </row>
     <row r="118" spans="2:12" ht="51">
-      <c r="B118" s="272"/>
-      <c r="C118" s="274" t="s">
+      <c r="B118" s="260"/>
+      <c r="C118" s="262" t="s">
         <v>548</v>
       </c>
-      <c r="D118" s="275" t="s">
+      <c r="D118" s="263" t="s">
         <v>553</v>
       </c>
-      <c r="E118" s="276" t="s">
+      <c r="E118" s="264" t="s">
         <v>563</v>
       </c>
-      <c r="F118" s="274" t="str">
+      <c r="F118" s="262" t="str">
         <f xml:space="preserve"> _xlfn.CONCAT("[", L118, "]")</f>
         <v>[柳江五]</v>
       </c>
-      <c r="G118" s="274"/>
-      <c r="H118" s="274"/>
-      <c r="I118" s="272"/>
-      <c r="J118" s="272"/>
-      <c r="L118" s="273" t="s">
+      <c r="G118" s="262"/>
+      <c r="H118" s="262"/>
+      <c r="I118" s="260"/>
+      <c r="J118" s="260"/>
+      <c r="L118" s="261" t="s">
         <v>558</v>
       </c>
     </row>
     <row r="119" spans="2:12" ht="51">
-      <c r="B119" s="272"/>
-      <c r="C119" s="274" t="s">
+      <c r="B119" s="260"/>
+      <c r="C119" s="262" t="s">
         <v>549</v>
       </c>
-      <c r="D119" s="275" t="s">
+      <c r="D119" s="263" t="s">
         <v>554</v>
       </c>
-      <c r="E119" s="276" t="s">
+      <c r="E119" s="264" t="s">
         <v>564</v>
       </c>
-      <c r="F119" s="274" t="str">
+      <c r="F119" s="262" t="str">
         <f t="shared" ref="F119:F122" si="23" xml:space="preserve"> _xlfn.CONCAT("[", L119, "]")</f>
         <v>[柳沽七]</v>
       </c>
-      <c r="G119" s="274"/>
-      <c r="H119" s="274"/>
-      <c r="I119" s="272"/>
-      <c r="J119" s="272"/>
-      <c r="L119" s="273" t="s">
+      <c r="G119" s="262"/>
+      <c r="H119" s="262"/>
+      <c r="I119" s="260"/>
+      <c r="J119" s="260"/>
+      <c r="L119" s="261" t="s">
         <v>559</v>
       </c>
     </row>
     <row r="120" spans="2:12" ht="51">
-      <c r="B120" s="272"/>
-      <c r="C120" s="274" t="s">
+      <c r="B120" s="260"/>
+      <c r="C120" s="262" t="s">
         <v>550</v>
       </c>
-      <c r="D120" s="275" t="s">
+      <c r="D120" s="263" t="s">
         <v>555</v>
       </c>
-      <c r="E120" s="276" t="s">
+      <c r="E120" s="264" t="s">
         <v>565</v>
       </c>
-      <c r="F120" s="274" t="str">
+      <c r="F120" s="262" t="str">
         <f t="shared" si="23"/>
         <v>[柳姜五]</v>
       </c>
-      <c r="G120" s="274"/>
-      <c r="H120" s="274"/>
-      <c r="I120" s="272"/>
-      <c r="J120" s="272"/>
-      <c r="L120" s="273" t="s">
+      <c r="G120" s="262"/>
+      <c r="H120" s="262"/>
+      <c r="I120" s="260"/>
+      <c r="J120" s="260"/>
+      <c r="L120" s="261" t="s">
         <v>560</v>
       </c>
     </row>
     <row r="121" spans="2:12" ht="51">
-      <c r="B121" s="272"/>
-      <c r="C121" s="274" t="s">
+      <c r="B121" s="260"/>
+      <c r="C121" s="262" t="s">
         <v>551</v>
       </c>
-      <c r="D121" s="275" t="s">
+      <c r="D121" s="263" t="s">
         <v>556</v>
       </c>
-      <c r="E121" s="276" t="s">
+      <c r="E121" s="264" t="s">
         <v>566</v>
       </c>
-      <c r="F121" s="274" t="str">
+      <c r="F121" s="262" t="str">
         <f t="shared" si="23"/>
         <v>[柳高五]</v>
       </c>
-      <c r="G121" s="274"/>
-      <c r="H121" s="274"/>
-      <c r="I121" s="272"/>
-      <c r="J121" s="272"/>
-      <c r="L121" s="273" t="s">
+      <c r="G121" s="262"/>
+      <c r="H121" s="262"/>
+      <c r="I121" s="260"/>
+      <c r="J121" s="260"/>
+      <c r="L121" s="261" t="s">
         <v>561</v>
       </c>
     </row>
     <row r="122" spans="2:12" ht="51">
-      <c r="B122" s="272"/>
-      <c r="C122" s="274" t="s">
+      <c r="B122" s="260"/>
+      <c r="C122" s="262" t="s">
         <v>552</v>
       </c>
-      <c r="D122" s="275" t="s">
+      <c r="D122" s="263" t="s">
         <v>557</v>
       </c>
-      <c r="E122" s="276" t="s">
+      <c r="E122" s="264" t="s">
         <v>567</v>
       </c>
-      <c r="F122" s="274" t="str">
+      <c r="F122" s="262" t="str">
         <f t="shared" si="23"/>
         <v>[柳居二]</v>
       </c>
-      <c r="G122" s="274"/>
-      <c r="H122" s="274"/>
-      <c r="I122" s="272"/>
-      <c r="J122" s="272"/>
-      <c r="L122" s="273" t="s">
+      <c r="G122" s="262"/>
+      <c r="H122" s="262"/>
+      <c r="I122" s="260"/>
+      <c r="J122" s="260"/>
+      <c r="L122" s="261" t="s">
         <v>562</v>
       </c>
     </row>
     <row r="123" spans="2:12" ht="38.25">
-      <c r="B123" s="272"/>
-      <c r="C123" s="272"/>
-      <c r="D123" s="272"/>
-      <c r="E123" s="272"/>
-      <c r="F123" s="272"/>
-      <c r="G123" s="272"/>
-      <c r="H123" s="272"/>
-      <c r="I123" s="272"/>
-      <c r="J123" s="272"/>
+      <c r="B123" s="260"/>
+      <c r="C123" s="260"/>
+      <c r="D123" s="260"/>
+      <c r="E123" s="260"/>
+      <c r="F123" s="260"/>
+      <c r="G123" s="260"/>
+      <c r="H123" s="260"/>
+      <c r="I123" s="260"/>
+      <c r="J123" s="260"/>
     </row>
     <row r="124" spans="2:12" ht="38.25">
-      <c r="B124" s="272"/>
-      <c r="C124" s="272"/>
-      <c r="D124" s="272"/>
-      <c r="E124" s="272"/>
-      <c r="F124" s="272"/>
-      <c r="G124" s="272"/>
-      <c r="H124" s="272"/>
-      <c r="I124" s="272"/>
-      <c r="J124" s="272"/>
+      <c r="B124" s="260"/>
+      <c r="C124" s="260"/>
+      <c r="D124" s="260"/>
+      <c r="E124" s="260"/>
+      <c r="F124" s="260"/>
+      <c r="G124" s="260"/>
+      <c r="H124" s="260"/>
+      <c r="I124" s="260"/>
+      <c r="J124" s="260"/>
     </row>
     <row r="125" spans="2:12" ht="38.25">
-      <c r="B125" s="272"/>
-      <c r="C125" s="272"/>
-      <c r="D125" s="272"/>
-      <c r="E125" s="272"/>
-      <c r="F125" s="272"/>
-      <c r="G125" s="272"/>
-      <c r="H125" s="272"/>
-      <c r="I125" s="272"/>
-      <c r="J125" s="272"/>
+      <c r="B125" s="260"/>
+      <c r="C125" s="260"/>
+      <c r="D125" s="260"/>
+      <c r="E125" s="260"/>
+      <c r="F125" s="260"/>
+      <c r="G125" s="260"/>
+      <c r="H125" s="260"/>
+      <c r="I125" s="260"/>
+      <c r="J125" s="260"/>
     </row>
     <row r="126" spans="2:12" ht="38.25">
-      <c r="B126" s="272"/>
-      <c r="C126" s="272"/>
-      <c r="D126" s="272"/>
-      <c r="E126" s="272"/>
-      <c r="F126" s="272"/>
-      <c r="G126" s="272"/>
-      <c r="H126" s="272"/>
-      <c r="I126" s="272"/>
-      <c r="J126" s="272"/>
+      <c r="B126" s="260"/>
+      <c r="C126" s="260"/>
+      <c r="D126" s="260"/>
+      <c r="E126" s="260"/>
+      <c r="F126" s="260"/>
+      <c r="G126" s="260"/>
+      <c r="H126" s="260"/>
+      <c r="I126" s="260"/>
+      <c r="J126" s="260"/>
     </row>
     <row r="127" spans="2:12" ht="38.25">
-      <c r="B127" s="272"/>
-      <c r="C127" s="272"/>
-      <c r="D127" s="272"/>
-      <c r="E127" s="272"/>
-      <c r="F127" s="272"/>
-      <c r="G127" s="272"/>
-      <c r="H127" s="272"/>
-      <c r="I127" s="272"/>
-      <c r="J127" s="272"/>
+      <c r="B127" s="260"/>
+      <c r="C127" s="260"/>
+      <c r="D127" s="260"/>
+      <c r="E127" s="260"/>
+      <c r="F127" s="260"/>
+      <c r="G127" s="260"/>
+      <c r="H127" s="260"/>
+      <c r="I127" s="260"/>
+      <c r="J127" s="260"/>
     </row>
     <row r="128" spans="2:12" ht="38.25">
-      <c r="B128" s="272"/>
-      <c r="C128" s="272"/>
-      <c r="D128" s="272"/>
-      <c r="E128" s="272"/>
-      <c r="F128" s="272"/>
-      <c r="G128" s="272"/>
-      <c r="H128" s="272"/>
-      <c r="I128" s="272"/>
-      <c r="J128" s="272"/>
+      <c r="B128" s="260"/>
+      <c r="C128" s="260"/>
+      <c r="D128" s="260"/>
+      <c r="E128" s="260"/>
+      <c r="F128" s="260"/>
+      <c r="G128" s="260"/>
+      <c r="H128" s="260"/>
+      <c r="I128" s="260"/>
+      <c r="J128" s="260"/>
     </row>
     <row r="129" spans="2:10" ht="38.25">
-      <c r="B129" s="272"/>
-      <c r="C129" s="272"/>
-      <c r="D129" s="272"/>
-      <c r="E129" s="272"/>
-      <c r="F129" s="272"/>
-      <c r="G129" s="272"/>
-      <c r="H129" s="272"/>
-      <c r="I129" s="272"/>
-      <c r="J129" s="272"/>
+      <c r="B129" s="260"/>
+      <c r="C129" s="260"/>
+      <c r="D129" s="260"/>
+      <c r="E129" s="260"/>
+      <c r="F129" s="260"/>
+      <c r="G129" s="260"/>
+      <c r="H129" s="260"/>
+      <c r="I129" s="260"/>
+      <c r="J129" s="260"/>
     </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>

--- a/docs/301_鍵盤設計規格_方音符號輸入_台語音標編碼.xlsx
+++ b/docs/301_鍵盤設計規格_方音符號輸入_台語音標編碼.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AlanJui\work\rime-tlpa\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45E1D4C6-116B-4751-8A9C-78F2CC84B365}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA5934D9-38ED-458E-8B18-BA159A72FCCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="67080" yWindow="-120" windowWidth="16440" windowHeight="28320" activeTab="1" xr2:uid="{6D6F034E-466E-416C-B3CC-1F7937B8DE3D}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="38640" windowHeight="15720" tabRatio="763" activeTab="1" xr2:uid="{6D6F034E-466E-416C-B3CC-1F7937B8DE3D}"/>
   </bookViews>
   <sheets>
     <sheet name="xlit對映工具" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,12 @@
     <sheet name="韻母列表 (3)" sheetId="6" r:id="rId6"/>
     <sheet name="聲調符號" sheetId="3" r:id="rId7"/>
     <sheet name="RIME設定【台語音標】" sheetId="2" r:id="rId8"/>
+    <sheet name="符號工具" sheetId="9" r:id="rId9"/>
+    <sheet name="方音符號" sheetId="10" r:id="rId10"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId11"/>
+  </externalReferences>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">RIME設定【台語音標】!$BR$4:$BT$59</definedName>
     <definedName name="_xlnm.Criteria" localSheetId="7">RIME設定【台語音標】!$CQ$1:$CQ$2</definedName>
@@ -91,7 +96,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2436" uniqueCount="568">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2553" uniqueCount="633">
   <si>
     <t>algebra:</t>
     <phoneticPr fontId="4" type="noConversion"/>
@@ -2193,6 +2198,458 @@
     <t>ㄌㄧˋ</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
+  <si>
+    <t>=</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>= UNICHAR(HEX2DEC(RIGHT("U+014B",4)))</t>
+  </si>
+  <si>
+    <t>符號</t>
+    <phoneticPr fontId="128" type="noConversion"/>
+  </si>
+  <si>
+    <t>Unicode 編碼</t>
+    <phoneticPr fontId="128" type="noConversion"/>
+  </si>
+  <si>
+    <t>實例</t>
+    <phoneticPr fontId="128" type="noConversion"/>
+  </si>
+  <si>
+    <t>Unicode
+十進制</t>
+    <phoneticPr fontId="128" type="noConversion"/>
+  </si>
+  <si>
+    <t>Unicode
+十六進制</t>
+    <phoneticPr fontId="128" type="noConversion"/>
+  </si>
+  <si>
+    <t>Unicode
+編碼</t>
+    <phoneticPr fontId="128" type="noConversion"/>
+  </si>
+  <si>
+    <t>驗證</t>
+    <phoneticPr fontId="128" type="noConversion"/>
+  </si>
+  <si>
+    <t>公式</t>
+    <phoneticPr fontId="128" type="noConversion"/>
+  </si>
+  <si>
+    <t>ʔ</t>
+  </si>
+  <si>
+    <t>U+0294</t>
+  </si>
+  <si>
+    <t>a</t>
+    <phoneticPr fontId="128" type="noConversion"/>
+  </si>
+  <si>
+    <t>i</t>
+    <phoneticPr fontId="128" type="noConversion"/>
+  </si>
+  <si>
+    <t>u</t>
+    <phoneticPr fontId="128" type="noConversion"/>
+  </si>
+  <si>
+    <t>e</t>
+    <phoneticPr fontId="128" type="noConversion"/>
+  </si>
+  <si>
+    <t>o</t>
+    <phoneticPr fontId="128" type="noConversion"/>
+  </si>
+  <si>
+    <t>m</t>
+    <phoneticPr fontId="128" type="noConversion"/>
+  </si>
+  <si>
+    <t>n</t>
+    <phoneticPr fontId="128" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="18"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>゜</t>
+    </r>
+    <phoneticPr fontId="128" type="noConversion"/>
+  </si>
+  <si>
+    <t>U+309C</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="18"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>゜</t>
+    </r>
+    <phoneticPr fontId="128" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="18"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>ⁿ</t>
+    </r>
+  </si>
+  <si>
+    <t>U+3125</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="18"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>ㄥ</t>
+    </r>
+    <phoneticPr fontId="128" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="18"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>ㄥ</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="18"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>ⁿ</t>
+    </r>
+    <phoneticPr fontId="128" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="18"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="254"/>
+      </rPr>
+      <t>ŋ</t>
+    </r>
+    <phoneticPr fontId="128" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="18"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>ŋ</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="18"/>
+        <color rgb="FF000000"/>
+        <rFont val="Charis SIL"/>
+      </rPr>
+      <t>̍</t>
+    </r>
+  </si>
+  <si>
+    <t>ə</t>
+    <phoneticPr fontId="128" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>o</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Charis SIL"/>
+      </rPr>
+      <t>͘</t>
+    </r>
+    <phoneticPr fontId="128" type="noConversion"/>
+  </si>
+  <si>
+    <t>U+0303</t>
+    <phoneticPr fontId="128" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄥ</t>
+    <phoneticPr fontId="144" type="noConversion"/>
+  </si>
+  <si>
+    <t>゜</t>
+    <phoneticPr fontId="144" type="noConversion"/>
+  </si>
+  <si>
+    <t>鼻韻母</t>
+    <phoneticPr fontId="144" type="noConversion"/>
+  </si>
+  <si>
+    <t>方音符號</t>
+    <phoneticPr fontId="144" type="noConversion"/>
+  </si>
+  <si>
+    <t>改鼻韻符</t>
+    <phoneticPr fontId="144" type="noConversion"/>
+  </si>
+  <si>
+    <t>鼻韻符置前</t>
+    <phoneticPr fontId="144" type="noConversion"/>
+  </si>
+  <si>
+    <t>鼻韻符置前方音符號</t>
+  </si>
+  <si>
+    <t>inn</t>
+    <phoneticPr fontId="144" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>ㄧ</t>
+    </r>
+  </si>
+  <si>
+    <t>unn</t>
+    <phoneticPr fontId="144" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>ㄨ</t>
+    </r>
+  </si>
+  <si>
+    <t>ann</t>
+    <phoneticPr fontId="144" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>ㄚ</t>
+    </r>
+  </si>
+  <si>
+    <t>onn</t>
+    <phoneticPr fontId="144" type="noConversion"/>
+  </si>
+  <si>
+    <t>enn</t>
+    <phoneticPr fontId="144" type="noConversion"/>
+  </si>
+  <si>
+    <t>ainn</t>
+    <phoneticPr fontId="144" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>ㄞ</t>
+    </r>
+  </si>
+  <si>
+    <t>aunn</t>
+    <phoneticPr fontId="144" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>ㄠ</t>
+    </r>
+  </si>
+  <si>
+    <t>ionn</t>
+    <phoneticPr fontId="144" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>ㄧ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei UI"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>ㆦ</t>
+    </r>
+    <phoneticPr fontId="144" type="noConversion"/>
+  </si>
+  <si>
+    <t>iunn</t>
+    <phoneticPr fontId="144" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>ㄧㄨ</t>
+    </r>
+  </si>
+  <si>
+    <t>iann</t>
+    <phoneticPr fontId="144" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>ㄧㄚ</t>
+    </r>
+  </si>
+  <si>
+    <t>iaunn</t>
+    <phoneticPr fontId="144" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>ㄧㄠ</t>
+    </r>
+  </si>
+  <si>
+    <t>uann</t>
+    <phoneticPr fontId="144" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>ㄨㄚ</t>
+    </r>
+  </si>
+  <si>
+    <t>uainn</t>
+    <phoneticPr fontId="144" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>ㄨㄞ</t>
+    </r>
+  </si>
+  <si>
+    <t>ㄥ</t>
+    <phoneticPr fontId="128" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㆭ</t>
+    <phoneticPr fontId="128" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -2201,7 +2658,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="General;;"/>
   </numFmts>
-  <fonts count="121">
+  <fonts count="149">
     <font>
       <sz val="16"/>
       <color rgb="FF000000"/>
@@ -3000,8 +3457,199 @@
       <name val="Microsoft JhengHei"/>
       <charset val="136"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="新細明體"/>
+      <family val="2"/>
+      <charset val="136"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="新細明體"/>
+      <family val="2"/>
+      <charset val="136"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <name val="微軟正黑體"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Cambria Math"/>
+      <family val="1"/>
+      <charset val="254"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Noto Sans TC SemiBold"/>
+      <family val="2"/>
+      <charset val="136"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FF000000"/>
+      <name val="微軟正黑體"/>
+      <family val="2"/>
+      <charset val="136"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="Noto Sans TC Medium"/>
+      <family val="2"/>
+      <charset val="136"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="新細明體"/>
+      <family val="2"/>
+      <charset val="136"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Noto Serif HK Black"/>
+      <family val="1"/>
+      <charset val="136"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Noto Serif HK Black"/>
+      <family val="1"/>
+      <charset val="136"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FFFF0000"/>
+      <name val="Noto Serif HK Black"/>
+      <family val="1"/>
+      <charset val="136"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Noto Sans TC Medium"/>
+      <family val="2"/>
+      <charset val="136"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <name val="微軟正黑體"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="254"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color rgb="FFFF0000"/>
+      <name val="Charis SIL"/>
+    </font>
+    <font>
+      <sz val="18"/>
+      <color rgb="FFC00000"/>
+      <name val="Noto Sans TC Medium"/>
+      <family val="2"/>
+      <charset val="136"/>
+    </font>
+    <font>
+      <sz val="22"/>
+      <color theme="1"/>
+      <name val="霞鶩文楷 TC Medium"/>
+      <family val="1"/>
+      <charset val="136"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color rgb="FF000000"/>
+      <name val="Charis SIL"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color rgb="FF000000"/>
+      <name val="微軟正黑體"/>
+      <family val="2"/>
+      <charset val="136"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color rgb="FFFF0000"/>
+      <name val="微軟正黑體"/>
+      <family val="2"/>
+      <charset val="136"/>
+    </font>
+    <font>
+      <sz val="18"/>
+      <color rgb="FF000000"/>
+      <name val="Noto Sans"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Charis SIL"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="新細明體"/>
+      <family val="2"/>
+      <charset val="136"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Charis SIL"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Microsoft JhengHei UI"/>
+      <family val="2"/>
+      <charset val="136"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Charis SIL"/>
+      <family val="2"/>
+      <charset val="136"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="細明體"/>
+      <family val="3"/>
+      <charset val="136"/>
+    </font>
   </fonts>
-  <fills count="33">
+  <fills count="36">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -3194,8 +3842,26 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.89999084444715716"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="23">
+  <borders count="25">
     <border>
       <left/>
       <right/>
@@ -3457,14 +4123,53 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFDEE2E6"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFDEE2E6"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFDEE2E6"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFDEE2E6"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="3" tint="0.749992370372631"/>
+      </left>
+      <right style="thin">
+        <color theme="3" tint="0.749992370372631"/>
+      </right>
+      <top style="thin">
+        <color theme="3" tint="0.749992370372631"/>
+      </top>
+      <bottom style="thin">
+        <color theme="3" tint="0.749992370372631"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="4">
+  <cellStyleXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="121" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="121" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="133" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="277">
+  <cellXfs count="318">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -4156,15 +4861,6 @@
     <xf numFmtId="0" fontId="117" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="118" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="119" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="108" fillId="29" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="108" fillId="29" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="108" fillId="29" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="107" fillId="30" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -4192,12 +4888,143 @@
     <xf numFmtId="0" fontId="107" fillId="30" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="108" fillId="29" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="108" fillId="29" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="108" fillId="29" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="64" fillId="0" borderId="0" xfId="1" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="121" fillId="0" borderId="0" xfId="4" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="121" fillId="0" borderId="0" xfId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="123" fillId="33" borderId="23" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="124" fillId="0" borderId="0" xfId="5" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="125" fillId="0" borderId="0" xfId="5" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="121" fillId="0" borderId="0" xfId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="126" fillId="0" borderId="0" xfId="5" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="126" fillId="0" borderId="0" xfId="5" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="127" fillId="24" borderId="23" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="129" fillId="0" borderId="0" xfId="4" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="130" fillId="34" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="131" fillId="34" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="132" fillId="34" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="127" fillId="0" borderId="0" xfId="5" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="133" fillId="0" borderId="0" xfId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="115" fillId="33" borderId="23" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="134" fillId="33" borderId="23" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="135" fillId="33" borderId="23" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="136" fillId="24" borderId="23" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="137" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="138" fillId="35" borderId="1" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="133" fillId="35" borderId="1" xfId="6" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="139" fillId="33" borderId="23" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="138" fillId="0" borderId="1" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="140" fillId="33" borderId="23" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="142" fillId="33" borderId="23" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="135" fillId="28" borderId="23" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="140" fillId="28" borderId="23" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="142" fillId="33" borderId="23" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="138" fillId="0" borderId="1" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="3"/>
+    </xf>
+    <xf numFmtId="0" fontId="122" fillId="0" borderId="0" xfId="4" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="145" fillId="0" borderId="0" xfId="4" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="121" fillId="0" borderId="24" xfId="4" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="146" fillId="0" borderId="24" xfId="4" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="145" fillId="0" borderId="24" xfId="4" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="147" fillId="0" borderId="0" xfId="4" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="148" fillId="0" borderId="0" xfId="4" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="4">
+  <cellStyles count="7">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
     <cellStyle name="一般 2" xfId="3" xr:uid="{82C09742-F2A0-488F-B715-51F74F221E36}"/>
+    <cellStyle name="一般 3" xfId="4" xr:uid="{1FCE98B0-77F0-4309-B3C4-64F2D8A54DE8}"/>
     <cellStyle name="一般 3 2" xfId="1" xr:uid="{8D496EB8-39F8-40DC-90A7-9567B775091F}"/>
+    <cellStyle name="一般 3 3" xfId="6" xr:uid="{171DC839-6999-4A26-BE2F-2CEC8387EFEB}"/>
     <cellStyle name="一般 4" xfId="2" xr:uid="{FCDA43F1-3668-4A20-A0B6-816AA98335F1}"/>
+    <cellStyle name="一般 4 2" xfId="5" xr:uid="{143C506F-73C5-41F0-B07E-06D8EE70262A}"/>
   </cellStyles>
   <dxfs count="4">
     <dxf>
@@ -4254,6 +5081,179 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="朱兆祥方音符號聲母表"/>
+      <sheetName val="宋人三十六字母表"/>
+      <sheetName val="宋人三十六字母表 (2)"/>
+      <sheetName val="聲母"/>
+      <sheetName val="韻母"/>
+      <sheetName val="【聲】聲母排序表"/>
+      <sheetName val="【聲】聲母對照表"/>
+      <sheetName val="【韻】韻母對照表"/>
+      <sheetName val="【調】韻母標調"/>
+      <sheetName val="符號工具"/>
+      <sheetName val="方音符號"/>
+      <sheetName val="十五音音節表 (BPM)"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="3" refreshError="1"/>
+      <sheetData sheetId="4" refreshError="1"/>
+      <sheetData sheetId="5" refreshError="1"/>
+      <sheetData sheetId="6" refreshError="1"/>
+      <sheetData sheetId="7" refreshError="1"/>
+      <sheetData sheetId="8">
+        <row r="3">
+          <cell r="M3" t="str">
+            <v>台羅調符編碼</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="O4" t="str">
+            <v>U+0304</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="E5" t="str">
+            <v>U+0301</v>
+          </cell>
+          <cell r="M5" t="str">
+            <v>U+0304</v>
+          </cell>
+          <cell r="O5" t="str">
+            <v>U+0302</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="E6" t="str">
+            <v>U+0300</v>
+          </cell>
+          <cell r="M6" t="str">
+            <v>U+0301</v>
+          </cell>
+          <cell r="O6" t="str">
+            <v>U+0300</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="M7" t="str">
+            <v>U+0300</v>
+          </cell>
+          <cell r="O7" t="str">
+            <v>U+030C</v>
+          </cell>
+        </row>
+        <row r="8">
+          <cell r="E8" t="str">
+            <v>U+030C</v>
+          </cell>
+          <cell r="M8" t="str">
+            <v>U+0301</v>
+          </cell>
+          <cell r="O8" t="str">
+            <v>U+0301</v>
+          </cell>
+        </row>
+        <row r="9">
+          <cell r="E9" t="str">
+            <v>U+0301</v>
+          </cell>
+          <cell r="M9" t="str">
+            <v>U+030C</v>
+          </cell>
+          <cell r="O9" t="str">
+            <v>U+0304</v>
+          </cell>
+        </row>
+        <row r="10">
+          <cell r="E10" t="str">
+            <v>U+0304</v>
+          </cell>
+          <cell r="M10" t="str">
+            <v>U+030D</v>
+          </cell>
+          <cell r="O10" t="str">
+            <v>U+0301</v>
+          </cell>
+        </row>
+        <row r="11">
+          <cell r="E11" t="str">
+            <v>U+030D</v>
+          </cell>
+          <cell r="M11" t="str">
+            <v>U+0301</v>
+          </cell>
+          <cell r="O11" t="str">
+            <v>U+030C</v>
+          </cell>
+        </row>
+        <row r="12">
+          <cell r="E12" t="str">
+            <v>U+030B</v>
+          </cell>
+        </row>
+        <row r="13">
+          <cell r="E13" t="str">
+            <v>U+030A</v>
+          </cell>
+        </row>
+        <row r="17">
+          <cell r="E17" t="str">
+            <v>U+0304</v>
+          </cell>
+        </row>
+        <row r="18">
+          <cell r="E18" t="str">
+            <v>U+0301</v>
+          </cell>
+        </row>
+        <row r="19">
+          <cell r="E19" t="str">
+            <v>U+030C</v>
+          </cell>
+        </row>
+        <row r="20">
+          <cell r="E20" t="str">
+            <v>U+030C</v>
+          </cell>
+        </row>
+        <row r="21">
+          <cell r="E21" t="str">
+            <v>U+0300</v>
+          </cell>
+        </row>
+        <row r="22">
+          <cell r="E22" t="str">
+            <v>U+0302</v>
+          </cell>
+        </row>
+        <row r="23">
+          <cell r="E23" t="str">
+            <v>U+0304</v>
+          </cell>
+        </row>
+        <row r="24">
+          <cell r="E24" t="str">
+            <v>U+0301</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="9" refreshError="1"/>
+      <sheetData sheetId="10" refreshError="1"/>
+      <sheetData sheetId="11" refreshError="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -9555,6 +10555,605 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF721241-4F3B-4D82-A21D-D937A9B2FB8A}">
+  <dimension ref="B1:M39"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
+  <cols>
+    <col min="1" max="1" width="8.796875" style="279"/>
+    <col min="2" max="5" width="10.59765625" style="279" customWidth="1"/>
+    <col min="6" max="6" width="16.3984375" style="279" customWidth="1"/>
+    <col min="7" max="16384" width="8.796875" style="279"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:13" ht="29.25">
+      <c r="C1" s="279" t="s">
+        <v>600</v>
+      </c>
+      <c r="D1" s="308" t="s">
+        <v>601</v>
+      </c>
+      <c r="E1" s="309" t="s">
+        <v>282</v>
+      </c>
+      <c r="F1" s="310" t="s">
+        <v>281</v>
+      </c>
+      <c r="L1" s="310"/>
+      <c r="M1" s="310"/>
+    </row>
+    <row r="2" spans="2:13" ht="20.25">
+      <c r="B2" s="311" t="s">
+        <v>602</v>
+      </c>
+      <c r="C2" s="312" t="s">
+        <v>603</v>
+      </c>
+      <c r="D2" s="312" t="s">
+        <v>604</v>
+      </c>
+      <c r="E2" s="311" t="s">
+        <v>605</v>
+      </c>
+      <c r="F2" s="311" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="3" spans="2:13" ht="29.25">
+      <c r="B3" s="313" t="s">
+        <v>607</v>
+      </c>
+      <c r="C3" s="313" t="s">
+        <v>87</v>
+      </c>
+      <c r="D3" s="313" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT( H3, "ⁿ")</f>
+        <v>iⁿ</v>
+      </c>
+      <c r="E3" s="313" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT("ⁿ", H3)</f>
+        <v>ⁿi</v>
+      </c>
+      <c r="F3" s="313" t="str">
+        <f t="shared" ref="F3:F15" si="0" xml:space="preserve"> _xlfn.CONCAT($D$1,I3)</f>
+        <v>゜ㄧ</v>
+      </c>
+      <c r="G3" s="309"/>
+      <c r="H3" s="309" t="str">
+        <f>LEFT(B3,1)</f>
+        <v>i</v>
+      </c>
+      <c r="I3" s="309" t="s">
+        <v>608</v>
+      </c>
+      <c r="J3" s="309"/>
+    </row>
+    <row r="4" spans="2:13" ht="29.25">
+      <c r="B4" s="313" t="s">
+        <v>609</v>
+      </c>
+      <c r="C4" s="313" t="s">
+        <v>123</v>
+      </c>
+      <c r="D4" s="313" t="str">
+        <f t="shared" ref="D4:D15" si="1" xml:space="preserve"> _xlfn.CONCAT( H4, "ⁿ")</f>
+        <v>uⁿ</v>
+      </c>
+      <c r="E4" s="313" t="str">
+        <f t="shared" ref="E4:E15" si="2" xml:space="preserve"> _xlfn.CONCAT("ⁿ", H4)</f>
+        <v>ⁿu</v>
+      </c>
+      <c r="F4" s="313" t="str">
+        <f t="shared" si="0"/>
+        <v>゜ㄨ</v>
+      </c>
+      <c r="G4" s="309"/>
+      <c r="H4" s="309" t="str">
+        <f t="shared" ref="H4:H7" si="3">LEFT(B4,1)</f>
+        <v>u</v>
+      </c>
+      <c r="I4" s="309" t="s">
+        <v>610</v>
+      </c>
+      <c r="J4" s="309"/>
+    </row>
+    <row r="5" spans="2:13" ht="29.25">
+      <c r="B5" s="313" t="s">
+        <v>611</v>
+      </c>
+      <c r="C5" s="313" t="s">
+        <v>39</v>
+      </c>
+      <c r="D5" s="313" t="str">
+        <f t="shared" si="1"/>
+        <v>aⁿ</v>
+      </c>
+      <c r="E5" s="313" t="str">
+        <f t="shared" si="2"/>
+        <v>ⁿa</v>
+      </c>
+      <c r="F5" s="313" t="str">
+        <f t="shared" si="0"/>
+        <v>゜ㄚ</v>
+      </c>
+      <c r="G5" s="309"/>
+      <c r="H5" s="309" t="str">
+        <f t="shared" si="3"/>
+        <v>a</v>
+      </c>
+      <c r="I5" s="309" t="s">
+        <v>612</v>
+      </c>
+      <c r="J5" s="309"/>
+    </row>
+    <row r="6" spans="2:13" ht="29.25">
+      <c r="B6" s="313" t="s">
+        <v>613</v>
+      </c>
+      <c r="C6" s="313" t="s">
+        <v>89</v>
+      </c>
+      <c r="D6" s="313" t="str">
+        <f t="shared" si="1"/>
+        <v>oⁿ</v>
+      </c>
+      <c r="E6" s="313" t="str">
+        <f t="shared" si="2"/>
+        <v>ⁿo</v>
+      </c>
+      <c r="F6" s="313" t="str">
+        <f t="shared" si="0"/>
+        <v>゜ㆦ</v>
+      </c>
+      <c r="G6" s="309"/>
+      <c r="H6" s="309" t="str">
+        <f t="shared" si="3"/>
+        <v>o</v>
+      </c>
+      <c r="I6" s="309" t="s">
+        <v>106</v>
+      </c>
+      <c r="J6" s="309"/>
+    </row>
+    <row r="7" spans="2:13" ht="29.25">
+      <c r="B7" s="313" t="s">
+        <v>614</v>
+      </c>
+      <c r="C7" s="313" t="s">
+        <v>163</v>
+      </c>
+      <c r="D7" s="313" t="str">
+        <f t="shared" si="1"/>
+        <v>eⁿ</v>
+      </c>
+      <c r="E7" s="313" t="str">
+        <f t="shared" si="2"/>
+        <v>ⁿe</v>
+      </c>
+      <c r="F7" s="313" t="str">
+        <f t="shared" si="0"/>
+        <v>゜ㆤ</v>
+      </c>
+      <c r="G7" s="309"/>
+      <c r="H7" s="309" t="str">
+        <f t="shared" si="3"/>
+        <v>e</v>
+      </c>
+      <c r="I7" s="309" t="s">
+        <v>182</v>
+      </c>
+      <c r="J7" s="309"/>
+    </row>
+    <row r="8" spans="2:13" ht="29.25">
+      <c r="B8" s="313" t="s">
+        <v>615</v>
+      </c>
+      <c r="C8" s="313" t="s">
+        <v>41</v>
+      </c>
+      <c r="D8" s="313" t="str">
+        <f t="shared" si="1"/>
+        <v>aiⁿ</v>
+      </c>
+      <c r="E8" s="313" t="str">
+        <f t="shared" si="2"/>
+        <v>ⁿai</v>
+      </c>
+      <c r="F8" s="313" t="str">
+        <f t="shared" si="0"/>
+        <v>゜ㄞ</v>
+      </c>
+      <c r="G8" s="309"/>
+      <c r="H8" s="309" t="str">
+        <f>LEFT(B8,2)</f>
+        <v>ai</v>
+      </c>
+      <c r="I8" s="309" t="s">
+        <v>616</v>
+      </c>
+      <c r="J8" s="309"/>
+    </row>
+    <row r="9" spans="2:13" ht="29.25">
+      <c r="B9" s="313" t="s">
+        <v>617</v>
+      </c>
+      <c r="C9" s="313" t="s">
+        <v>127</v>
+      </c>
+      <c r="D9" s="313" t="str">
+        <f t="shared" si="1"/>
+        <v>auⁿ</v>
+      </c>
+      <c r="E9" s="313" t="str">
+        <f t="shared" si="2"/>
+        <v>ⁿau</v>
+      </c>
+      <c r="F9" s="313" t="str">
+        <f t="shared" si="0"/>
+        <v>゜ㄠ</v>
+      </c>
+      <c r="G9" s="309"/>
+      <c r="H9" s="309" t="str">
+        <f>LEFT(B9,2)</f>
+        <v>au</v>
+      </c>
+      <c r="I9" s="309" t="s">
+        <v>618</v>
+      </c>
+      <c r="J9" s="309"/>
+    </row>
+    <row r="10" spans="2:13" ht="29.25">
+      <c r="B10" s="313" t="s">
+        <v>619</v>
+      </c>
+      <c r="C10" s="313" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT("ㄧ",C6)</f>
+        <v>ㄧㆧ</v>
+      </c>
+      <c r="D10" s="313" t="str">
+        <f t="shared" si="1"/>
+        <v>ioⁿ</v>
+      </c>
+      <c r="E10" s="313" t="str">
+        <f t="shared" si="2"/>
+        <v>ⁿio</v>
+      </c>
+      <c r="F10" s="313" t="str">
+        <f t="shared" si="0"/>
+        <v>゜ㄧㆦ</v>
+      </c>
+      <c r="G10" s="309"/>
+      <c r="H10" s="309" t="str">
+        <f t="shared" ref="H10:H12" si="4">LEFT(B10,2)</f>
+        <v>io</v>
+      </c>
+      <c r="I10" s="314" t="s">
+        <v>620</v>
+      </c>
+      <c r="J10" s="309"/>
+    </row>
+    <row r="11" spans="2:13" ht="29.25">
+      <c r="B11" s="313" t="s">
+        <v>621</v>
+      </c>
+      <c r="C11" s="313" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT("ㄧ",C4)</f>
+        <v>ㄧㆫ</v>
+      </c>
+      <c r="D11" s="313" t="str">
+        <f t="shared" si="1"/>
+        <v>iuⁿ</v>
+      </c>
+      <c r="E11" s="313" t="str">
+        <f t="shared" si="2"/>
+        <v>ⁿiu</v>
+      </c>
+      <c r="F11" s="313" t="str">
+        <f t="shared" si="0"/>
+        <v>゜ㄧㄨ</v>
+      </c>
+      <c r="G11" s="309"/>
+      <c r="H11" s="309" t="str">
+        <f t="shared" si="4"/>
+        <v>iu</v>
+      </c>
+      <c r="I11" s="309" t="s">
+        <v>622</v>
+      </c>
+      <c r="J11" s="309"/>
+    </row>
+    <row r="12" spans="2:13" ht="29.25">
+      <c r="B12" s="313" t="s">
+        <v>623</v>
+      </c>
+      <c r="C12" s="313" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT("ㄧ",C5)</f>
+        <v>ㄧㆩ</v>
+      </c>
+      <c r="D12" s="313" t="str">
+        <f t="shared" si="1"/>
+        <v>iaⁿ</v>
+      </c>
+      <c r="E12" s="313" t="str">
+        <f t="shared" si="2"/>
+        <v>ⁿia</v>
+      </c>
+      <c r="F12" s="313" t="str">
+        <f t="shared" si="0"/>
+        <v>゜ㄧㄚ</v>
+      </c>
+      <c r="G12" s="309"/>
+      <c r="H12" s="309" t="str">
+        <f t="shared" si="4"/>
+        <v>ia</v>
+      </c>
+      <c r="I12" s="309" t="s">
+        <v>624</v>
+      </c>
+      <c r="J12" s="309"/>
+    </row>
+    <row r="13" spans="2:13" ht="29.25">
+      <c r="B13" s="313" t="s">
+        <v>625</v>
+      </c>
+      <c r="C13" s="313" t="str">
+        <f t="shared" ref="C13" si="5" xml:space="preserve"> _xlfn.CONCAT("ㄧ",C9)</f>
+        <v>ㄧㆯ</v>
+      </c>
+      <c r="D13" s="313" t="str">
+        <f t="shared" si="1"/>
+        <v>iauⁿ</v>
+      </c>
+      <c r="E13" s="313" t="str">
+        <f t="shared" si="2"/>
+        <v>ⁿiau</v>
+      </c>
+      <c r="F13" s="313" t="str">
+        <f t="shared" si="0"/>
+        <v>゜ㄧㄠ</v>
+      </c>
+      <c r="G13" s="309"/>
+      <c r="H13" s="309" t="str">
+        <f>LEFT(B13,3)</f>
+        <v>iau</v>
+      </c>
+      <c r="I13" s="309" t="s">
+        <v>626</v>
+      </c>
+      <c r="J13" s="309"/>
+    </row>
+    <row r="14" spans="2:13" ht="29.25">
+      <c r="B14" s="313" t="s">
+        <v>627</v>
+      </c>
+      <c r="C14" s="313" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT("ㄨ",C5)</f>
+        <v>ㄨㆩ</v>
+      </c>
+      <c r="D14" s="313" t="str">
+        <f t="shared" si="1"/>
+        <v>uaⁿ</v>
+      </c>
+      <c r="E14" s="313" t="str">
+        <f t="shared" si="2"/>
+        <v>ⁿua</v>
+      </c>
+      <c r="F14" s="313" t="str">
+        <f t="shared" si="0"/>
+        <v>゜ㄨㄚ</v>
+      </c>
+      <c r="G14" s="309"/>
+      <c r="H14" s="309" t="str">
+        <f>LEFT(B14,2)</f>
+        <v>ua</v>
+      </c>
+      <c r="I14" s="309" t="s">
+        <v>628</v>
+      </c>
+      <c r="J14" s="309"/>
+    </row>
+    <row r="15" spans="2:13" ht="29.25">
+      <c r="B15" s="313" t="s">
+        <v>629</v>
+      </c>
+      <c r="C15" s="313" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT("ㄨ",C8)</f>
+        <v>ㄨㆮ</v>
+      </c>
+      <c r="D15" s="313" t="str">
+        <f t="shared" si="1"/>
+        <v>uaiⁿ</v>
+      </c>
+      <c r="E15" s="313" t="str">
+        <f t="shared" si="2"/>
+        <v>ⁿuai</v>
+      </c>
+      <c r="F15" s="313" t="str">
+        <f t="shared" si="0"/>
+        <v>゜ㄨㄞ</v>
+      </c>
+      <c r="G15" s="309"/>
+      <c r="H15" s="309" t="str">
+        <f>LEFT(B15,3)</f>
+        <v>uai</v>
+      </c>
+      <c r="I15" s="309" t="s">
+        <v>630</v>
+      </c>
+      <c r="J15" s="309"/>
+    </row>
+    <row r="16" spans="2:13" ht="29.25">
+      <c r="B16" s="309"/>
+      <c r="C16" s="309"/>
+      <c r="D16" s="309"/>
+      <c r="E16" s="309"/>
+      <c r="F16" s="309"/>
+      <c r="G16" s="309"/>
+      <c r="H16" s="309"/>
+    </row>
+    <row r="17" spans="2:8" ht="29.25">
+      <c r="B17" s="315" t="s">
+        <v>102</v>
+      </c>
+      <c r="C17" s="315" t="s">
+        <v>99</v>
+      </c>
+      <c r="D17" s="309" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT(B17, $I$3)</f>
+        <v>ㄗㄧ</v>
+      </c>
+      <c r="E17" s="309" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT(C17, $I$3)</f>
+        <v>ㄐㄧ</v>
+      </c>
+      <c r="F17" s="309"/>
+      <c r="G17" s="309"/>
+      <c r="H17" s="309"/>
+    </row>
+    <row r="18" spans="2:8" ht="29.25">
+      <c r="B18" s="315" t="s">
+        <v>139</v>
+      </c>
+      <c r="C18" s="315" t="s">
+        <v>135</v>
+      </c>
+      <c r="D18" s="309" t="str">
+        <f t="shared" ref="D18:E19" si="6" xml:space="preserve"> _xlfn.CONCAT(B18, $I$3)</f>
+        <v>ㄘㄧ</v>
+      </c>
+      <c r="E18" s="309" t="str">
+        <f t="shared" si="6"/>
+        <v>ㄑㄧ</v>
+      </c>
+      <c r="F18" s="309"/>
+      <c r="G18" s="309"/>
+      <c r="H18" s="309"/>
+    </row>
+    <row r="19" spans="2:8" ht="29.25">
+      <c r="B19" s="279" t="s">
+        <v>178</v>
+      </c>
+      <c r="C19" s="279" t="s">
+        <v>174</v>
+      </c>
+      <c r="D19" s="309" t="str">
+        <f t="shared" si="6"/>
+        <v>ㄙㄧ</v>
+      </c>
+      <c r="E19" s="309" t="str">
+        <f t="shared" si="6"/>
+        <v>ㄒㄧ</v>
+      </c>
+      <c r="F19" s="309"/>
+      <c r="G19" s="309"/>
+      <c r="H19" s="309"/>
+    </row>
+    <row r="20" spans="2:8" ht="29.25">
+      <c r="B20" s="309" t="s">
+        <v>85</v>
+      </c>
+      <c r="C20" s="309" t="s">
+        <v>83</v>
+      </c>
+      <c r="D20" s="309" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT(B20, $I$3)</f>
+        <v>ㆡㄧ</v>
+      </c>
+      <c r="E20" s="309" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT(C20, $I$3)</f>
+        <v>ㆢㄧ</v>
+      </c>
+    </row>
+    <row r="22" spans="2:8" ht="29.25">
+      <c r="B22" s="315" t="s">
+        <v>102</v>
+      </c>
+      <c r="C22" s="309" t="s">
+        <v>85</v>
+      </c>
+      <c r="D22" s="315" t="s">
+        <v>139</v>
+      </c>
+      <c r="E22" s="279" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="23" spans="2:8" ht="29.25">
+      <c r="B23" s="315" t="s">
+        <v>99</v>
+      </c>
+      <c r="C23" s="315" t="s">
+        <v>135</v>
+      </c>
+      <c r="D23" s="279" t="s">
+        <v>174</v>
+      </c>
+      <c r="E23" s="309" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="27" spans="2:8">
+      <c r="B27" s="283" t="s">
+        <v>631</v>
+      </c>
+      <c r="C27" s="283"/>
+    </row>
+    <row r="28" spans="2:8">
+      <c r="B28" s="283" t="s">
+        <v>632</v>
+      </c>
+      <c r="C28" s="283"/>
+    </row>
+    <row r="29" spans="2:8">
+      <c r="B29" s="278"/>
+      <c r="C29" s="278"/>
+    </row>
+    <row r="30" spans="2:8">
+      <c r="B30" s="278"/>
+      <c r="C30" s="278"/>
+    </row>
+    <row r="31" spans="2:8">
+      <c r="B31" s="278"/>
+      <c r="C31" s="278"/>
+    </row>
+    <row r="32" spans="2:8">
+      <c r="B32" s="278"/>
+      <c r="C32" s="278"/>
+    </row>
+    <row r="33" spans="2:3">
+      <c r="B33" s="278"/>
+      <c r="C33" s="278"/>
+    </row>
+    <row r="34" spans="2:3">
+      <c r="B34" s="278"/>
+      <c r="C34" s="278"/>
+    </row>
+    <row r="35" spans="2:3">
+      <c r="B35" s="278"/>
+      <c r="C35" s="278"/>
+    </row>
+    <row r="36" spans="2:3">
+      <c r="B36" s="278"/>
+      <c r="C36" s="278"/>
+    </row>
+    <row r="37" spans="2:3">
+      <c r="B37" s="278"/>
+      <c r="C37" s="278"/>
+    </row>
+    <row r="38" spans="2:3">
+      <c r="B38" s="278"/>
+      <c r="C38" s="278"/>
+    </row>
+    <row r="39" spans="2:3">
+      <c r="B39" s="278"/>
+      <c r="C39" s="278"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6784CB5E-E995-4102-B564-0AA16E059A52}">
   <dimension ref="A1:CI63"/>
@@ -15332,66 +16931,246 @@
     <row r="42" spans="1:87" s="245" customFormat="1">
       <c r="A42" s="1"/>
       <c r="B42" s="1"/>
-      <c r="C42" s="1"/>
-      <c r="D42" s="1"/>
-      <c r="E42" s="1"/>
-      <c r="F42" s="1"/>
-      <c r="G42" s="1"/>
-      <c r="H42" s="1"/>
-      <c r="I42" s="1"/>
-      <c r="J42" s="1"/>
-      <c r="K42" s="1"/>
-      <c r="L42" s="1"/>
-      <c r="M42" s="1"/>
-      <c r="N42" s="1"/>
-      <c r="O42" s="1"/>
-      <c r="P42" s="1"/>
-      <c r="Q42" s="1"/>
-      <c r="R42" s="1"/>
-      <c r="S42" s="1"/>
-      <c r="T42" s="1"/>
-      <c r="U42" s="1"/>
-      <c r="V42" s="1"/>
-      <c r="W42" s="1"/>
-      <c r="X42" s="1"/>
-      <c r="Y42" s="1"/>
-      <c r="Z42" s="1"/>
-      <c r="AA42" s="1"/>
-      <c r="AB42" s="1"/>
-      <c r="AC42" s="1"/>
-      <c r="AD42" s="1"/>
-      <c r="AE42" s="1"/>
-      <c r="AF42" s="1"/>
-      <c r="AG42" s="1"/>
-      <c r="AH42" s="1"/>
-      <c r="AI42" s="1"/>
-      <c r="AJ42" s="1"/>
-      <c r="AK42" s="1"/>
-      <c r="AL42" s="1"/>
-      <c r="AM42" s="1"/>
-      <c r="AN42" s="1"/>
-      <c r="AO42" s="1"/>
-      <c r="AP42" s="1"/>
-      <c r="AQ42" s="1"/>
-      <c r="AR42" s="1"/>
-      <c r="AS42" s="1"/>
-      <c r="AT42" s="1"/>
-      <c r="AU42" s="1"/>
-      <c r="AV42" s="1"/>
-      <c r="AW42" s="1"/>
-      <c r="AX42" s="1"/>
-      <c r="AY42" s="1"/>
-      <c r="AZ42" s="1"/>
-      <c r="BA42" s="1"/>
-      <c r="BB42" s="1"/>
-      <c r="BC42" s="1"/>
-      <c r="BD42" s="1"/>
-      <c r="BE42" s="1"/>
-      <c r="BF42" s="1"/>
-      <c r="BG42" s="1"/>
-      <c r="BH42" s="1"/>
-      <c r="BI42" s="1"/>
-      <c r="BJ42" s="1"/>
+      <c r="C42" s="3">
+        <f>C2</f>
+        <v>1</v>
+      </c>
+      <c r="D42" s="3">
+        <f>D2</f>
+        <v>2</v>
+      </c>
+      <c r="E42" s="3">
+        <f>E2</f>
+        <v>3</v>
+      </c>
+      <c r="F42" s="3">
+        <f>F2</f>
+        <v>4</v>
+      </c>
+      <c r="G42" s="3">
+        <f>G2</f>
+        <v>5</v>
+      </c>
+      <c r="H42" s="3">
+        <f>H2</f>
+        <v>6</v>
+      </c>
+      <c r="I42" s="3">
+        <f>I2</f>
+        <v>7</v>
+      </c>
+      <c r="J42" s="3">
+        <f>J2</f>
+        <v>8</v>
+      </c>
+      <c r="K42" s="3">
+        <f>K2</f>
+        <v>9</v>
+      </c>
+      <c r="L42" s="3">
+        <f>L2</f>
+        <v>10</v>
+      </c>
+      <c r="M42" s="3">
+        <f>M2</f>
+        <v>11</v>
+      </c>
+      <c r="N42" s="3">
+        <f>N2</f>
+        <v>12</v>
+      </c>
+      <c r="O42" s="3">
+        <f>O2</f>
+        <v>13</v>
+      </c>
+      <c r="P42" s="3">
+        <f>P2</f>
+        <v>14</v>
+      </c>
+      <c r="Q42" s="3">
+        <f>Q2</f>
+        <v>15</v>
+      </c>
+      <c r="R42" s="3">
+        <f>R2</f>
+        <v>16</v>
+      </c>
+      <c r="S42" s="3">
+        <f>S2</f>
+        <v>17</v>
+      </c>
+      <c r="T42" s="3">
+        <f>T2</f>
+        <v>18</v>
+      </c>
+      <c r="U42" s="3">
+        <f>U2</f>
+        <v>19</v>
+      </c>
+      <c r="V42" s="3">
+        <f>V2</f>
+        <v>20</v>
+      </c>
+      <c r="W42" s="3">
+        <f>W2</f>
+        <v>21</v>
+      </c>
+      <c r="X42" s="3">
+        <f>X2</f>
+        <v>22</v>
+      </c>
+      <c r="Y42" s="3">
+        <f>Y2</f>
+        <v>23</v>
+      </c>
+      <c r="Z42" s="3">
+        <f>Z2</f>
+        <v>24</v>
+      </c>
+      <c r="AA42" s="3">
+        <f>AA2</f>
+        <v>25</v>
+      </c>
+      <c r="AB42" s="3">
+        <f>AB2</f>
+        <v>26</v>
+      </c>
+      <c r="AC42" s="3">
+        <f>AC2</f>
+        <v>27</v>
+      </c>
+      <c r="AD42" s="3">
+        <f>AD2</f>
+        <v>28</v>
+      </c>
+      <c r="AE42" s="3">
+        <f>AE2</f>
+        <v>29</v>
+      </c>
+      <c r="AF42" s="3">
+        <f>AF2</f>
+        <v>30</v>
+      </c>
+      <c r="AG42" s="3">
+        <f>AG2</f>
+        <v>31</v>
+      </c>
+      <c r="AH42" s="3">
+        <f>AH2</f>
+        <v>32</v>
+      </c>
+      <c r="AI42" s="3">
+        <f>AI2</f>
+        <v>33</v>
+      </c>
+      <c r="AJ42" s="3">
+        <f>AJ2</f>
+        <v>34</v>
+      </c>
+      <c r="AK42" s="3">
+        <f>AK2</f>
+        <v>35</v>
+      </c>
+      <c r="AL42" s="3">
+        <f>AL2</f>
+        <v>36</v>
+      </c>
+      <c r="AM42" s="3">
+        <f>AM2</f>
+        <v>37</v>
+      </c>
+      <c r="AN42" s="3">
+        <f>AN2</f>
+        <v>38</v>
+      </c>
+      <c r="AO42" s="3">
+        <f>AO2</f>
+        <v>39</v>
+      </c>
+      <c r="AP42" s="3">
+        <f>AP2</f>
+        <v>40</v>
+      </c>
+      <c r="AQ42" s="3">
+        <f>AQ2</f>
+        <v>41</v>
+      </c>
+      <c r="AR42" s="3">
+        <f>AR2</f>
+        <v>42</v>
+      </c>
+      <c r="AS42" s="3">
+        <f>AS2</f>
+        <v>43</v>
+      </c>
+      <c r="AT42" s="3">
+        <f>AT2</f>
+        <v>44</v>
+      </c>
+      <c r="AU42" s="3">
+        <f>AU2</f>
+        <v>45</v>
+      </c>
+      <c r="AV42" s="3">
+        <f>AV2</f>
+        <v>46</v>
+      </c>
+      <c r="AW42" s="3">
+        <f>AW2</f>
+        <v>47</v>
+      </c>
+      <c r="AX42" s="3">
+        <f>AX2</f>
+        <v>48</v>
+      </c>
+      <c r="AY42" s="3">
+        <f>AY2</f>
+        <v>49</v>
+      </c>
+      <c r="AZ42" s="3">
+        <f>AZ2</f>
+        <v>50</v>
+      </c>
+      <c r="BA42" s="3">
+        <f>BA2</f>
+        <v>51</v>
+      </c>
+      <c r="BB42" s="3">
+        <f>BB2</f>
+        <v>52</v>
+      </c>
+      <c r="BC42" s="3">
+        <f>BC2</f>
+        <v>53</v>
+      </c>
+      <c r="BD42" s="3">
+        <f>BD2</f>
+        <v>54</v>
+      </c>
+      <c r="BE42" s="3">
+        <f>BE2</f>
+        <v>55</v>
+      </c>
+      <c r="BF42" s="3">
+        <f>BF2</f>
+        <v>56</v>
+      </c>
+      <c r="BG42" s="3">
+        <f>BG2</f>
+        <v>57</v>
+      </c>
+      <c r="BH42" s="3">
+        <f>BH2</f>
+        <v>58</v>
+      </c>
+      <c r="BI42" s="3">
+        <f>BI2</f>
+        <v>59</v>
+      </c>
+      <c r="BJ42" s="3">
+        <f>BJ2</f>
+        <v>60</v>
+      </c>
       <c r="BK42" s="1"/>
       <c r="BL42" s="246">
         <v>41</v>
@@ -15411,68 +17190,250 @@
       <c r="CI42" s="1"/>
     </row>
     <row r="43" spans="1:87" s="245" customFormat="1">
-      <c r="A43" s="1"/>
-      <c r="B43" s="1"/>
-      <c r="C43" s="1"/>
-      <c r="D43" s="1"/>
-      <c r="E43" s="1"/>
-      <c r="F43" s="1"/>
-      <c r="G43" s="1"/>
-      <c r="H43" s="1"/>
-      <c r="I43" s="1"/>
-      <c r="J43" s="1"/>
-      <c r="K43" s="1"/>
-      <c r="L43" s="1"/>
-      <c r="M43" s="1"/>
-      <c r="N43" s="1"/>
-      <c r="O43" s="1"/>
-      <c r="P43" s="1"/>
-      <c r="Q43" s="1"/>
-      <c r="R43" s="1"/>
-      <c r="S43" s="1"/>
-      <c r="T43" s="1"/>
-      <c r="U43" s="1"/>
-      <c r="V43" s="1"/>
-      <c r="W43" s="1"/>
-      <c r="X43" s="1"/>
-      <c r="Y43" s="1"/>
-      <c r="Z43" s="1"/>
-      <c r="AA43" s="1"/>
-      <c r="AB43" s="1"/>
-      <c r="AC43" s="1"/>
-      <c r="AD43" s="1"/>
-      <c r="AE43" s="1"/>
-      <c r="AF43" s="1"/>
-      <c r="AG43" s="1"/>
-      <c r="AH43" s="1"/>
-      <c r="AI43" s="1"/>
-      <c r="AJ43" s="1"/>
-      <c r="AK43" s="1"/>
-      <c r="AL43" s="1"/>
-      <c r="AM43" s="1"/>
-      <c r="AN43" s="1"/>
-      <c r="AO43" s="1"/>
-      <c r="AP43" s="1"/>
-      <c r="AQ43" s="1"/>
-      <c r="AR43" s="1"/>
-      <c r="AS43" s="1"/>
-      <c r="AT43" s="1"/>
-      <c r="AU43" s="1"/>
-      <c r="AV43" s="1"/>
-      <c r="AW43" s="1"/>
-      <c r="AX43" s="1"/>
-      <c r="AY43" s="1"/>
-      <c r="AZ43" s="1"/>
-      <c r="BA43" s="1"/>
-      <c r="BB43" s="1"/>
-      <c r="BC43" s="1"/>
-      <c r="BD43" s="1"/>
-      <c r="BE43" s="1"/>
-      <c r="BF43" s="1"/>
-      <c r="BG43" s="1"/>
-      <c r="BH43" s="1"/>
-      <c r="BI43" s="1"/>
-      <c r="BJ43" s="1"/>
+      <c r="B43" s="316" t="str">
+        <f>A3</f>
+        <v>台羅拼音</v>
+      </c>
+      <c r="C43" s="217" t="str">
+        <f>C3</f>
+        <v>p</v>
+      </c>
+      <c r="D43" s="217" t="str">
+        <f>D3</f>
+        <v>b</v>
+      </c>
+      <c r="E43" s="217" t="str">
+        <f>E3</f>
+        <v>ph</v>
+      </c>
+      <c r="F43" s="217" t="str">
+        <f>F3</f>
+        <v>m</v>
+      </c>
+      <c r="G43" s="217" t="str">
+        <f>G3</f>
+        <v>t</v>
+      </c>
+      <c r="H43" s="217" t="str">
+        <f>H3</f>
+        <v>th</v>
+      </c>
+      <c r="I43" s="217" t="str">
+        <f>I3</f>
+        <v>n</v>
+      </c>
+      <c r="J43" s="217" t="str">
+        <f>J3</f>
+        <v>l</v>
+      </c>
+      <c r="K43" s="217" t="str">
+        <f>K3</f>
+        <v>k</v>
+      </c>
+      <c r="L43" s="217" t="str">
+        <f>L3</f>
+        <v>g</v>
+      </c>
+      <c r="M43" s="217" t="str">
+        <f>M3</f>
+        <v>kh</v>
+      </c>
+      <c r="N43" s="217" t="str">
+        <f>N3</f>
+        <v>ng</v>
+      </c>
+      <c r="O43" s="217" t="str">
+        <f>O3</f>
+        <v>h</v>
+      </c>
+      <c r="P43" s="217" t="str">
+        <f>P3</f>
+        <v>ts</v>
+      </c>
+      <c r="Q43" s="217" t="str">
+        <f>Q3</f>
+        <v>j</v>
+      </c>
+      <c r="R43" s="217" t="str">
+        <f>R3</f>
+        <v>tsh</v>
+      </c>
+      <c r="S43" s="217" t="str">
+        <f>S3</f>
+        <v>s</v>
+      </c>
+      <c r="T43" s="217" t="str">
+        <f>T3</f>
+        <v>ts(i)</v>
+      </c>
+      <c r="U43" s="217" t="str">
+        <f>U3</f>
+        <v>j(i)</v>
+      </c>
+      <c r="V43" s="217" t="str">
+        <f>V3</f>
+        <v>tsh(i)</v>
+      </c>
+      <c r="W43" s="217" t="str">
+        <f>W3</f>
+        <v>s(i)</v>
+      </c>
+      <c r="X43" s="217" t="str">
+        <f>X3</f>
+        <v>a</v>
+      </c>
+      <c r="Y43" s="217" t="str">
+        <f>Y3</f>
+        <v>i</v>
+      </c>
+      <c r="Z43" s="217" t="str">
+        <f>Z3</f>
+        <v>u</v>
+      </c>
+      <c r="AA43" s="217" t="str">
+        <f>AA3</f>
+        <v>ir</v>
+      </c>
+      <c r="AB43" s="217" t="str">
+        <f>AB3</f>
+        <v>e</v>
+      </c>
+      <c r="AC43" s="217" t="str">
+        <f>AC3</f>
+        <v>oo</v>
+      </c>
+      <c r="AD43" s="217" t="str">
+        <f>AD3</f>
+        <v>o</v>
+      </c>
+      <c r="AE43" s="218" t="str">
+        <f>AE3</f>
+        <v>-m</v>
+      </c>
+      <c r="AF43" s="218" t="str">
+        <f>AF3</f>
+        <v>-n</v>
+      </c>
+      <c r="AG43" s="218" t="str">
+        <f>AG3</f>
+        <v>-ng</v>
+      </c>
+      <c r="AH43" s="219" t="str">
+        <f>AH3</f>
+        <v>-p</v>
+      </c>
+      <c r="AI43" s="219" t="str">
+        <f>AI3</f>
+        <v>-t</v>
+      </c>
+      <c r="AJ43" s="219" t="str">
+        <f>AJ3</f>
+        <v>-k</v>
+      </c>
+      <c r="AK43" s="219" t="str">
+        <f>AK3</f>
+        <v>-h</v>
+      </c>
+      <c r="AL43" s="217" t="str">
+        <f>AL3</f>
+        <v>ai</v>
+      </c>
+      <c r="AM43" s="217" t="str">
+        <f>AM3</f>
+        <v>au</v>
+      </c>
+      <c r="AN43" s="217" t="str">
+        <f>AN3</f>
+        <v>am</v>
+      </c>
+      <c r="AO43" s="217" t="str">
+        <f>AO3</f>
+        <v>an</v>
+      </c>
+      <c r="AP43" s="217" t="str">
+        <f>AP3</f>
+        <v>ang</v>
+      </c>
+      <c r="AQ43" s="217" t="str">
+        <f>AQ3</f>
+        <v>om</v>
+      </c>
+      <c r="AR43" s="217" t="str">
+        <f>AR3</f>
+        <v>ong</v>
+      </c>
+      <c r="AS43" s="217" t="str">
+        <f>AS3</f>
+        <v>aⁿ</v>
+      </c>
+      <c r="AT43" s="217" t="str">
+        <f>AT3</f>
+        <v>iⁿ</v>
+      </c>
+      <c r="AU43" s="217" t="str">
+        <f>AU3</f>
+        <v>uⁿ</v>
+      </c>
+      <c r="AV43" s="217" t="str">
+        <f>AV3</f>
+        <v>eⁿ</v>
+      </c>
+      <c r="AW43" s="217" t="str">
+        <f>AW3</f>
+        <v>oⁿ</v>
+      </c>
+      <c r="AX43" s="217" t="str">
+        <f>AX3</f>
+        <v>aiⁿ</v>
+      </c>
+      <c r="AY43" s="217" t="str">
+        <f>AY3</f>
+        <v>auⁿ</v>
+      </c>
+      <c r="AZ43" s="217">
+        <f>AZ3</f>
+        <v>1</v>
+      </c>
+      <c r="BA43" s="217">
+        <f>BA3</f>
+        <v>7</v>
+      </c>
+      <c r="BB43" s="217">
+        <f>BB3</f>
+        <v>3</v>
+      </c>
+      <c r="BC43" s="217">
+        <f>BC3</f>
+        <v>2</v>
+      </c>
+      <c r="BD43" s="217">
+        <f>BD3</f>
+        <v>5</v>
+      </c>
+      <c r="BE43" s="217">
+        <f>BE3</f>
+        <v>8</v>
+      </c>
+      <c r="BF43" s="217">
+        <f>BF3</f>
+        <v>4</v>
+      </c>
+      <c r="BG43" s="217">
+        <f>BG3</f>
+        <v>0</v>
+      </c>
+      <c r="BH43" s="217" t="str">
+        <f>BH3</f>
+        <v>L</v>
+      </c>
+      <c r="BI43" s="217" t="str">
+        <f>BI3</f>
+        <v/>
+      </c>
+      <c r="BJ43" s="217">
+        <f>BJ3</f>
+        <v>0</v>
+      </c>
       <c r="BK43" s="1"/>
       <c r="BL43" s="246">
         <v>42</v>
@@ -15492,68 +17453,250 @@
       <c r="CI43" s="1"/>
     </row>
     <row r="44" spans="1:87" s="245" customFormat="1">
-      <c r="A44" s="1"/>
-      <c r="B44" s="1"/>
-      <c r="C44" s="1"/>
-      <c r="D44" s="1"/>
-      <c r="E44" s="1"/>
-      <c r="F44" s="1"/>
-      <c r="G44" s="1"/>
-      <c r="H44" s="1"/>
-      <c r="I44" s="1"/>
-      <c r="J44" s="1"/>
-      <c r="K44" s="1"/>
-      <c r="L44" s="1"/>
-      <c r="M44" s="1"/>
-      <c r="N44" s="1"/>
-      <c r="O44" s="1"/>
-      <c r="P44" s="1"/>
-      <c r="Q44" s="1"/>
-      <c r="R44" s="1"/>
-      <c r="S44" s="1"/>
-      <c r="T44" s="1"/>
-      <c r="U44" s="1"/>
-      <c r="V44" s="1"/>
-      <c r="W44" s="1"/>
-      <c r="X44" s="1"/>
-      <c r="Y44" s="1"/>
-      <c r="Z44" s="1"/>
-      <c r="AA44" s="1"/>
-      <c r="AB44" s="1"/>
-      <c r="AC44" s="1"/>
-      <c r="AD44" s="1"/>
-      <c r="AE44" s="1"/>
-      <c r="AF44" s="1"/>
-      <c r="AG44" s="1"/>
-      <c r="AH44" s="1"/>
-      <c r="AI44" s="1"/>
-      <c r="AJ44" s="1"/>
-      <c r="AK44" s="1"/>
-      <c r="AL44" s="1"/>
-      <c r="AM44" s="1"/>
-      <c r="AN44" s="1"/>
-      <c r="AO44" s="1"/>
-      <c r="AP44" s="1"/>
-      <c r="AQ44" s="1"/>
-      <c r="AR44" s="1"/>
-      <c r="AS44" s="1"/>
-      <c r="AT44" s="1"/>
-      <c r="AU44" s="1"/>
-      <c r="AV44" s="1"/>
-      <c r="AW44" s="1"/>
-      <c r="AX44" s="1"/>
-      <c r="AY44" s="1"/>
-      <c r="AZ44" s="1"/>
-      <c r="BA44" s="1"/>
-      <c r="BB44" s="1"/>
-      <c r="BC44" s="1"/>
-      <c r="BD44" s="1"/>
-      <c r="BE44" s="1"/>
-      <c r="BF44" s="1"/>
-      <c r="BG44" s="1"/>
-      <c r="BH44" s="1"/>
-      <c r="BI44" s="1"/>
-      <c r="BJ44" s="1"/>
+      <c r="B44" s="317" t="str">
+        <f>A4</f>
+        <v>字典編碼</v>
+      </c>
+      <c r="C44" s="5" t="str">
+        <f>C4</f>
+        <v>p</v>
+      </c>
+      <c r="D44" s="5" t="str">
+        <f>D4</f>
+        <v>b</v>
+      </c>
+      <c r="E44" s="5" t="str">
+        <f>E4</f>
+        <v>P</v>
+      </c>
+      <c r="F44" s="5" t="str">
+        <f>F4</f>
+        <v>m</v>
+      </c>
+      <c r="G44" s="5" t="str">
+        <f>G4</f>
+        <v>t</v>
+      </c>
+      <c r="H44" s="5" t="str">
+        <f>H4</f>
+        <v>T</v>
+      </c>
+      <c r="I44" s="5" t="str">
+        <f>I4</f>
+        <v>n</v>
+      </c>
+      <c r="J44" s="5" t="str">
+        <f>J4</f>
+        <v>l</v>
+      </c>
+      <c r="K44" s="5" t="str">
+        <f>K4</f>
+        <v>k</v>
+      </c>
+      <c r="L44" s="5" t="str">
+        <f>L4</f>
+        <v>g</v>
+      </c>
+      <c r="M44" s="5" t="str">
+        <f>M4</f>
+        <v>K</v>
+      </c>
+      <c r="N44" s="5" t="str">
+        <f>N4</f>
+        <v>ŋ</v>
+      </c>
+      <c r="O44" s="5" t="str">
+        <f>O4</f>
+        <v>h</v>
+      </c>
+      <c r="P44" s="5" t="str">
+        <f>P4</f>
+        <v>z</v>
+      </c>
+      <c r="Q44" s="5" t="str">
+        <f>Q4</f>
+        <v>j</v>
+      </c>
+      <c r="R44" s="5" t="str">
+        <f>R4</f>
+        <v>c</v>
+      </c>
+      <c r="S44" s="5" t="str">
+        <f>S4</f>
+        <v>s</v>
+      </c>
+      <c r="T44" s="5" t="str">
+        <f>T4</f>
+        <v>Z</v>
+      </c>
+      <c r="U44" s="5" t="str">
+        <f>U4</f>
+        <v>J</v>
+      </c>
+      <c r="V44" s="5" t="str">
+        <f>V4</f>
+        <v>C</v>
+      </c>
+      <c r="W44" s="5" t="str">
+        <f>W4</f>
+        <v>S</v>
+      </c>
+      <c r="X44" s="5" t="str">
+        <f>X4</f>
+        <v>a</v>
+      </c>
+      <c r="Y44" s="5" t="str">
+        <f>Y4</f>
+        <v>i</v>
+      </c>
+      <c r="Z44" s="5" t="str">
+        <f>Z4</f>
+        <v>u</v>
+      </c>
+      <c r="AA44" s="5" t="str">
+        <f>AA4</f>
+        <v>w</v>
+      </c>
+      <c r="AB44" s="5" t="str">
+        <f>AB4</f>
+        <v>e</v>
+      </c>
+      <c r="AC44" s="7" t="str">
+        <f>AC4</f>
+        <v>O</v>
+      </c>
+      <c r="AD44" s="7" t="str">
+        <f>AD4</f>
+        <v>ə</v>
+      </c>
+      <c r="AE44" s="5" t="str">
+        <f>AE4</f>
+        <v>M</v>
+      </c>
+      <c r="AF44" s="5" t="str">
+        <f>AF4</f>
+        <v>N</v>
+      </c>
+      <c r="AG44" s="5" t="str">
+        <f>AG4</f>
+        <v>G</v>
+      </c>
+      <c r="AH44" s="5" t="str">
+        <f>AH4</f>
+        <v>R</v>
+      </c>
+      <c r="AI44" s="5" t="str">
+        <f>AI4</f>
+        <v>F</v>
+      </c>
+      <c r="AJ44" s="7" t="str">
+        <f>AJ4</f>
+        <v>Q</v>
+      </c>
+      <c r="AK44" s="5" t="str">
+        <f>AK4</f>
+        <v>V</v>
+      </c>
+      <c r="AL44" s="5" t="str">
+        <f>AL4</f>
+        <v>I</v>
+      </c>
+      <c r="AM44" s="5" t="str">
+        <f>AM4</f>
+        <v>U</v>
+      </c>
+      <c r="AN44" s="5" t="str">
+        <f>AN4</f>
+        <v>Y</v>
+      </c>
+      <c r="AO44" s="5" t="str">
+        <f>AO4</f>
+        <v>@</v>
+      </c>
+      <c r="AP44" s="5" t="str">
+        <f>AP4</f>
+        <v>A</v>
+      </c>
+      <c r="AQ44" s="5" t="str">
+        <f>AQ4</f>
+        <v>W</v>
+      </c>
+      <c r="AR44" s="5" t="str">
+        <f>AR4</f>
+        <v>H</v>
+      </c>
+      <c r="AS44" s="5" t="str">
+        <f>AS4</f>
+        <v>d</v>
+      </c>
+      <c r="AT44" s="5" t="str">
+        <f>AT4</f>
+        <v>f</v>
+      </c>
+      <c r="AU44" s="5" t="str">
+        <f>AU4</f>
+        <v>q</v>
+      </c>
+      <c r="AV44" s="5" t="str">
+        <f>AV4</f>
+        <v>r</v>
+      </c>
+      <c r="AW44" s="5" t="str">
+        <f>AW4</f>
+        <v>v</v>
+      </c>
+      <c r="AX44" s="5" t="str">
+        <f>AX4</f>
+        <v>x</v>
+      </c>
+      <c r="AY44" s="5" t="str">
+        <f>AY4</f>
+        <v>y</v>
+      </c>
+      <c r="AZ44" s="5">
+        <f>AZ4</f>
+        <v>1</v>
+      </c>
+      <c r="BA44" s="5">
+        <f>BA4</f>
+        <v>7</v>
+      </c>
+      <c r="BB44" s="5">
+        <f>BB4</f>
+        <v>3</v>
+      </c>
+      <c r="BC44" s="5">
+        <f>BC4</f>
+        <v>2</v>
+      </c>
+      <c r="BD44" s="5">
+        <f>BD4</f>
+        <v>5</v>
+      </c>
+      <c r="BE44" s="5">
+        <f>BE4</f>
+        <v>8</v>
+      </c>
+      <c r="BF44" s="5">
+        <f>BF4</f>
+        <v>4</v>
+      </c>
+      <c r="BG44" s="7" t="str">
+        <f>BG4</f>
+        <v>&amp;</v>
+      </c>
+      <c r="BH44" s="5" t="str">
+        <f>BH4</f>
+        <v>L</v>
+      </c>
+      <c r="BI44" s="5" t="str">
+        <f>BI4</f>
+        <v/>
+      </c>
+      <c r="BJ44" s="5">
+        <f>BJ4</f>
+        <v>0</v>
+      </c>
       <c r="BK44" s="1"/>
       <c r="BL44" s="246">
         <v>43</v>
@@ -15573,68 +17716,250 @@
       <c r="CI44" s="1"/>
     </row>
     <row r="45" spans="1:87" s="245" customFormat="1">
-      <c r="A45" s="1"/>
-      <c r="B45" s="1"/>
-      <c r="C45" s="1"/>
-      <c r="D45" s="1"/>
-      <c r="E45" s="1"/>
-      <c r="F45" s="1"/>
-      <c r="G45" s="1"/>
-      <c r="H45" s="1"/>
-      <c r="I45" s="1"/>
-      <c r="J45" s="1"/>
-      <c r="K45" s="1"/>
-      <c r="L45" s="1"/>
-      <c r="M45" s="1"/>
-      <c r="N45" s="1"/>
-      <c r="O45" s="1"/>
-      <c r="P45" s="1"/>
-      <c r="Q45" s="1"/>
-      <c r="R45" s="1"/>
-      <c r="S45" s="1"/>
-      <c r="T45" s="1"/>
-      <c r="U45" s="1"/>
-      <c r="V45" s="1"/>
-      <c r="W45" s="1"/>
-      <c r="X45" s="1"/>
-      <c r="Y45" s="1"/>
-      <c r="Z45" s="1"/>
-      <c r="AA45" s="1"/>
-      <c r="AB45" s="1"/>
-      <c r="AC45" s="1"/>
-      <c r="AD45" s="1"/>
-      <c r="AE45" s="1"/>
-      <c r="AF45" s="1"/>
-      <c r="AG45" s="1"/>
-      <c r="AH45" s="1"/>
-      <c r="AI45" s="1"/>
-      <c r="AJ45" s="1"/>
-      <c r="AK45" s="1"/>
-      <c r="AL45" s="1"/>
-      <c r="AM45" s="1"/>
-      <c r="AN45" s="1"/>
-      <c r="AO45" s="1"/>
-      <c r="AP45" s="1"/>
-      <c r="AQ45" s="1"/>
-      <c r="AR45" s="1"/>
-      <c r="AS45" s="1"/>
-      <c r="AT45" s="1"/>
-      <c r="AU45" s="1"/>
-      <c r="AV45" s="1"/>
-      <c r="AW45" s="1"/>
-      <c r="AX45" s="1"/>
-      <c r="AY45" s="1"/>
-      <c r="AZ45" s="1"/>
-      <c r="BA45" s="1"/>
-      <c r="BB45" s="1"/>
-      <c r="BC45" s="1"/>
-      <c r="BD45" s="1"/>
-      <c r="BE45" s="1"/>
-      <c r="BF45" s="1"/>
-      <c r="BG45" s="1"/>
-      <c r="BH45" s="1"/>
-      <c r="BI45" s="1"/>
-      <c r="BJ45" s="1"/>
+      <c r="B45" s="316" t="str">
+        <f>A5</f>
+        <v>按鍵</v>
+      </c>
+      <c r="C45" s="6" t="str">
+        <f>C5</f>
+        <v>1</v>
+      </c>
+      <c r="D45" s="6" t="str">
+        <f>D5</f>
+        <v>!</v>
+      </c>
+      <c r="E45" s="6" t="str">
+        <f>E5</f>
+        <v>q</v>
+      </c>
+      <c r="F45" s="6" t="str">
+        <f>F5</f>
+        <v>a</v>
+      </c>
+      <c r="G45" s="6" t="str">
+        <f>G5</f>
+        <v>2</v>
+      </c>
+      <c r="H45" s="6" t="str">
+        <f>H5</f>
+        <v>w</v>
+      </c>
+      <c r="I45" s="6" t="str">
+        <f>I5</f>
+        <v>s</v>
+      </c>
+      <c r="J45" s="6" t="str">
+        <f>J5</f>
+        <v>x</v>
+      </c>
+      <c r="K45" s="6" t="str">
+        <f>K5</f>
+        <v>e</v>
+      </c>
+      <c r="L45" s="6" t="str">
+        <f>L5</f>
+        <v>E</v>
+      </c>
+      <c r="M45" s="6" t="str">
+        <f>M5</f>
+        <v>d</v>
+      </c>
+      <c r="N45" s="6" t="str">
+        <f>N5</f>
+        <v>N</v>
+      </c>
+      <c r="O45" s="6" t="str">
+        <f>O5</f>
+        <v>c</v>
+      </c>
+      <c r="P45" s="6" t="str">
+        <f>P5</f>
+        <v>y</v>
+      </c>
+      <c r="Q45" s="6" t="str">
+        <f>Q5</f>
+        <v>Y</v>
+      </c>
+      <c r="R45" s="6" t="str">
+        <f>R5</f>
+        <v>h</v>
+      </c>
+      <c r="S45" s="6" t="str">
+        <f>S5</f>
+        <v>n</v>
+      </c>
+      <c r="T45" s="6" t="str">
+        <f>T5</f>
+        <v>r</v>
+      </c>
+      <c r="U45" s="6" t="str">
+        <f>U5</f>
+        <v>R</v>
+      </c>
+      <c r="V45" s="6" t="str">
+        <f>V5</f>
+        <v>f</v>
+      </c>
+      <c r="W45" s="6" t="str">
+        <f>W5</f>
+        <v>v</v>
+      </c>
+      <c r="X45" s="6" t="str">
+        <f>X5</f>
+        <v>8</v>
+      </c>
+      <c r="Y45" s="6" t="str">
+        <f>Y5</f>
+        <v>u</v>
+      </c>
+      <c r="Z45" s="6" t="str">
+        <f>Z5</f>
+        <v>j</v>
+      </c>
+      <c r="AA45" s="6" t="str">
+        <f>AA5</f>
+        <v>K</v>
+      </c>
+      <c r="AB45" s="6" t="str">
+        <f>AB5</f>
+        <v>,</v>
+      </c>
+      <c r="AC45" s="6" t="str">
+        <f>AC5</f>
+        <v>i</v>
+      </c>
+      <c r="AD45" s="6" t="str">
+        <f>AD5</f>
+        <v>k</v>
+      </c>
+      <c r="AE45" s="6" t="str">
+        <f>AE5</f>
+        <v>m</v>
+      </c>
+      <c r="AF45" s="6" t="str">
+        <f>AF5</f>
+        <v>p</v>
+      </c>
+      <c r="AG45" s="6" t="str">
+        <f>AG5</f>
+        <v>/</v>
+      </c>
+      <c r="AH45" s="6" t="str">
+        <f>AH5</f>
+        <v>b</v>
+      </c>
+      <c r="AI45" s="6" t="str">
+        <f>AI5</f>
+        <v>t</v>
+      </c>
+      <c r="AJ45" s="6" t="str">
+        <f>AJ5</f>
+        <v>g</v>
+      </c>
+      <c r="AK45" s="6" t="str">
+        <f>AK5</f>
+        <v>z</v>
+      </c>
+      <c r="AL45" s="6" t="str">
+        <f>AL5</f>
+        <v>9</v>
+      </c>
+      <c r="AM45" s="6" t="str">
+        <f>AM5</f>
+        <v>l</v>
+      </c>
+      <c r="AN45" s="6" t="str">
+        <f>AN5</f>
+        <v>M</v>
+      </c>
+      <c r="AO45" s="6" t="str">
+        <f>AO5</f>
+        <v>0</v>
+      </c>
+      <c r="AP45" s="6" t="str">
+        <f>AP5</f>
+        <v>;</v>
+      </c>
+      <c r="AQ45" s="6" t="str">
+        <f>AQ5</f>
+        <v>O</v>
+      </c>
+      <c r="AR45" s="6" t="str">
+        <f>AR5</f>
+        <v>o</v>
+      </c>
+      <c r="AS45" s="6" t="str">
+        <f>AS5</f>
+        <v>*</v>
+      </c>
+      <c r="AT45" s="6" t="str">
+        <f>AT5</f>
+        <v>U</v>
+      </c>
+      <c r="AU45" s="6" t="str">
+        <f>AU5</f>
+        <v>J</v>
+      </c>
+      <c r="AV45" s="6" t="str">
+        <f>AV5</f>
+        <v>&lt;</v>
+      </c>
+      <c r="AW45" s="6" t="str">
+        <f>AW5</f>
+        <v>I</v>
+      </c>
+      <c r="AX45" s="6" t="str">
+        <f>AX5</f>
+        <v>(</v>
+      </c>
+      <c r="AY45" s="6" t="str">
+        <f>AY5</f>
+        <v>L</v>
+      </c>
+      <c r="AZ45" s="6" t="str">
+        <f>AZ5</f>
+        <v>:</v>
+      </c>
+      <c r="BA45" s="6">
+        <f>BA5</f>
+        <v>5</v>
+      </c>
+      <c r="BB45" s="6">
+        <f>BB5</f>
+        <v>3</v>
+      </c>
+      <c r="BC45" s="6">
+        <f>BC5</f>
+        <v>4</v>
+      </c>
+      <c r="BD45" s="6">
+        <f>BD5</f>
+        <v>6</v>
+      </c>
+      <c r="BE45" s="6" t="str">
+        <f>BE5</f>
+        <v>]</v>
+      </c>
+      <c r="BF45" s="6" t="str">
+        <f>BF5</f>
+        <v>[</v>
+      </c>
+      <c r="BG45" s="6">
+        <f>BG5</f>
+        <v>7</v>
+      </c>
+      <c r="BH45" s="6" t="str">
+        <f>BH5</f>
+        <v>-</v>
+      </c>
+      <c r="BI45" s="6" t="str">
+        <f>BI5</f>
+        <v/>
+      </c>
+      <c r="BJ45" s="6">
+        <f>BJ5</f>
+        <v>0</v>
+      </c>
       <c r="BK45" s="1"/>
       <c r="BL45" s="246">
         <v>44</v>
@@ -15654,68 +17979,250 @@
       <c r="CI45" s="1"/>
     </row>
     <row r="46" spans="1:87" s="245" customFormat="1">
-      <c r="A46" s="1"/>
-      <c r="B46" s="1"/>
-      <c r="C46" s="1"/>
-      <c r="D46" s="1"/>
-      <c r="E46" s="1"/>
-      <c r="F46" s="1"/>
-      <c r="G46" s="1"/>
-      <c r="H46" s="1"/>
-      <c r="I46" s="1"/>
-      <c r="J46" s="1"/>
-      <c r="K46" s="1"/>
-      <c r="L46" s="1"/>
-      <c r="M46" s="1"/>
-      <c r="N46" s="1"/>
-      <c r="O46" s="1"/>
-      <c r="P46" s="1"/>
-      <c r="Q46" s="1"/>
-      <c r="R46" s="1"/>
-      <c r="S46" s="1"/>
-      <c r="T46" s="1"/>
-      <c r="U46" s="1"/>
-      <c r="V46" s="1"/>
-      <c r="W46" s="1"/>
-      <c r="X46" s="1"/>
-      <c r="Y46" s="1"/>
-      <c r="Z46" s="1"/>
-      <c r="AA46" s="1"/>
-      <c r="AB46" s="1"/>
-      <c r="AC46" s="1"/>
-      <c r="AD46" s="1"/>
-      <c r="AE46" s="1"/>
-      <c r="AF46" s="1"/>
-      <c r="AG46" s="1"/>
-      <c r="AH46" s="1"/>
-      <c r="AI46" s="1"/>
-      <c r="AJ46" s="1"/>
-      <c r="AK46" s="1"/>
-      <c r="AL46" s="1"/>
-      <c r="AM46" s="1"/>
-      <c r="AN46" s="1"/>
-      <c r="AO46" s="1"/>
-      <c r="AP46" s="1"/>
-      <c r="AQ46" s="1"/>
-      <c r="AR46" s="1"/>
-      <c r="AS46" s="1"/>
-      <c r="AT46" s="1"/>
-      <c r="AU46" s="1"/>
-      <c r="AV46" s="1"/>
-      <c r="AW46" s="1"/>
-      <c r="AX46" s="1"/>
-      <c r="AY46" s="1"/>
-      <c r="AZ46" s="1"/>
-      <c r="BA46" s="1"/>
-      <c r="BB46" s="1"/>
-      <c r="BC46" s="1"/>
-      <c r="BD46" s="1"/>
-      <c r="BE46" s="1"/>
-      <c r="BF46" s="1"/>
-      <c r="BG46" s="1"/>
-      <c r="BH46" s="1"/>
-      <c r="BI46" s="1"/>
-      <c r="BJ46" s="1"/>
+      <c r="B46" s="316" t="str">
+        <f>A6</f>
+        <v>注音符號</v>
+      </c>
+      <c r="C46" s="8" t="str">
+        <f>C6</f>
+        <v>ㄅ</v>
+      </c>
+      <c r="D46" s="8" t="str">
+        <f>D6</f>
+        <v>ㆠ</v>
+      </c>
+      <c r="E46" s="8" t="str">
+        <f>E6</f>
+        <v>ㄆ</v>
+      </c>
+      <c r="F46" s="8" t="str">
+        <f>F6</f>
+        <v>ㄇ</v>
+      </c>
+      <c r="G46" s="8" t="str">
+        <f>G6</f>
+        <v>ㄉ</v>
+      </c>
+      <c r="H46" s="8" t="str">
+        <f>H6</f>
+        <v>ㄊ</v>
+      </c>
+      <c r="I46" s="8" t="str">
+        <f>I6</f>
+        <v>ㄋ</v>
+      </c>
+      <c r="J46" s="8" t="str">
+        <f>J6</f>
+        <v>ㄌ</v>
+      </c>
+      <c r="K46" s="8" t="str">
+        <f>K6</f>
+        <v>ㄍ</v>
+      </c>
+      <c r="L46" s="8" t="str">
+        <f>L6</f>
+        <v>ㆣ</v>
+      </c>
+      <c r="M46" s="8" t="str">
+        <f>M6</f>
+        <v>ㄎ</v>
+      </c>
+      <c r="N46" s="8" t="str">
+        <f>N6</f>
+        <v>ㄫ</v>
+      </c>
+      <c r="O46" s="8" t="str">
+        <f>O6</f>
+        <v>ㄏ</v>
+      </c>
+      <c r="P46" s="8" t="str">
+        <f>P6</f>
+        <v>ㄗ</v>
+      </c>
+      <c r="Q46" s="8" t="str">
+        <f>Q6</f>
+        <v>ㆡ</v>
+      </c>
+      <c r="R46" s="8" t="str">
+        <f>R6</f>
+        <v>ㄘ</v>
+      </c>
+      <c r="S46" s="8" t="str">
+        <f>S6</f>
+        <v>ㄙ</v>
+      </c>
+      <c r="T46" s="8" t="str">
+        <f>T6</f>
+        <v>ㄐ</v>
+      </c>
+      <c r="U46" s="8" t="str">
+        <f>U6</f>
+        <v>ㆢ</v>
+      </c>
+      <c r="V46" s="8" t="str">
+        <f>V6</f>
+        <v>ㄑ</v>
+      </c>
+      <c r="W46" s="8" t="str">
+        <f>W6</f>
+        <v>ㄒ</v>
+      </c>
+      <c r="X46" s="8" t="str">
+        <f>X6</f>
+        <v>ㄚ</v>
+      </c>
+      <c r="Y46" s="8" t="str">
+        <f>Y6</f>
+        <v>ㄧ</v>
+      </c>
+      <c r="Z46" s="8" t="str">
+        <f>Z6</f>
+        <v>ㄨ</v>
+      </c>
+      <c r="AA46" s="8" t="str">
+        <f>AA6</f>
+        <v>ㆨ</v>
+      </c>
+      <c r="AB46" s="8" t="str">
+        <f>AB6</f>
+        <v>ㆤ</v>
+      </c>
+      <c r="AC46" s="8" t="str">
+        <f>AC6</f>
+        <v>ㆦ</v>
+      </c>
+      <c r="AD46" s="8" t="str">
+        <f>AD6</f>
+        <v>ㄜ</v>
+      </c>
+      <c r="AE46" s="8" t="str">
+        <f>AE6</f>
+        <v>ㆬ</v>
+      </c>
+      <c r="AF46" s="8" t="str">
+        <f>AF6</f>
+        <v>ㄣ</v>
+      </c>
+      <c r="AG46" s="8" t="str">
+        <f>AG6</f>
+        <v>ㆭ</v>
+      </c>
+      <c r="AH46" s="8" t="str">
+        <f>AH6</f>
+        <v>ㆴ</v>
+      </c>
+      <c r="AI46" s="8" t="str">
+        <f>AI6</f>
+        <v>ㆵ</v>
+      </c>
+      <c r="AJ46" s="8" t="str">
+        <f>AJ6</f>
+        <v>ㆻ</v>
+      </c>
+      <c r="AK46" s="8" t="str">
+        <f>AK6</f>
+        <v>ㆷ</v>
+      </c>
+      <c r="AL46" s="8" t="str">
+        <f>AL6</f>
+        <v>ㄞ</v>
+      </c>
+      <c r="AM46" s="8" t="str">
+        <f>AM6</f>
+        <v>ㄠ</v>
+      </c>
+      <c r="AN46" s="8" t="str">
+        <f>AN6</f>
+        <v>ㆰ</v>
+      </c>
+      <c r="AO46" s="8" t="str">
+        <f>AO6</f>
+        <v>ㄢ</v>
+      </c>
+      <c r="AP46" s="8" t="str">
+        <f>AP6</f>
+        <v>ㄤ</v>
+      </c>
+      <c r="AQ46" s="8" t="str">
+        <f>AQ6</f>
+        <v>ㆱ</v>
+      </c>
+      <c r="AR46" s="8" t="str">
+        <f>AR6</f>
+        <v>ㆲ</v>
+      </c>
+      <c r="AS46" s="8" t="str">
+        <f>AS6</f>
+        <v>ㆩ</v>
+      </c>
+      <c r="AT46" s="8" t="str">
+        <f>AT6</f>
+        <v>ㆪ</v>
+      </c>
+      <c r="AU46" s="8" t="str">
+        <f>AU6</f>
+        <v>ㆫ</v>
+      </c>
+      <c r="AV46" s="8" t="str">
+        <f>AV6</f>
+        <v>ㆥ</v>
+      </c>
+      <c r="AW46" s="8" t="str">
+        <f>AW6</f>
+        <v>ㆧ</v>
+      </c>
+      <c r="AX46" s="8" t="str">
+        <f>AX6</f>
+        <v>ㆮ</v>
+      </c>
+      <c r="AY46" s="8" t="str">
+        <f>AY6</f>
+        <v>ㆯ</v>
+      </c>
+      <c r="AZ46" s="8" t="str">
+        <f>AZ6</f>
+        <v>一</v>
+      </c>
+      <c r="BA46" s="8" t="str">
+        <f>BA6</f>
+        <v>七</v>
+      </c>
+      <c r="BB46" s="8" t="str">
+        <f>BB6</f>
+        <v>三</v>
+      </c>
+      <c r="BC46" s="8" t="str">
+        <f>BC6</f>
+        <v>二</v>
+      </c>
+      <c r="BD46" s="8" t="str">
+        <f>BD6</f>
+        <v>五</v>
+      </c>
+      <c r="BE46" s="8" t="str">
+        <f>BE6</f>
+        <v>八</v>
+      </c>
+      <c r="BF46" s="8" t="str">
+        <f>BF6</f>
+        <v>四</v>
+      </c>
+      <c r="BG46" s="8" t="str">
+        <f>BG6</f>
+        <v>入</v>
+      </c>
+      <c r="BH46" s="8" t="str">
+        <f>BH6</f>
+        <v>゜</v>
+      </c>
+      <c r="BI46" s="8" t="str">
+        <f>BI6</f>
+        <v/>
+      </c>
+      <c r="BJ46" s="8">
+        <f>BJ6</f>
+        <v>0</v>
+      </c>
       <c r="BK46" s="1"/>
       <c r="BL46" s="246">
         <v>45</v>
@@ -15980,12 +18487,18 @@
     <row r="50" spans="1:87" s="245" customFormat="1">
       <c r="A50" s="1"/>
       <c r="B50" s="1"/>
-      <c r="C50" s="1"/>
+      <c r="C50" s="1" t="str">
+        <f>符號工具!B2</f>
+        <v>符號</v>
+      </c>
       <c r="D50" s="1"/>
       <c r="E50" s="1"/>
       <c r="F50" s="1"/>
       <c r="G50" s="1"/>
-      <c r="H50" s="1"/>
+      <c r="H50" s="1" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT(Y46,AS46," = ", C52,Y46,X46)</f>
+        <v>ㄧㆩ = ゜ㄧㄚ</v>
+      </c>
       <c r="I50" s="1"/>
       <c r="J50" s="1"/>
       <c r="K50" s="1"/>
@@ -16061,7 +18574,10 @@
     <row r="51" spans="1:87" s="245" customFormat="1">
       <c r="A51" s="1"/>
       <c r="B51" s="1"/>
-      <c r="C51" s="1"/>
+      <c r="C51" s="1" t="str">
+        <f>符號工具!B3</f>
+        <v>ʔ</v>
+      </c>
       <c r="D51" s="1"/>
       <c r="E51" s="1"/>
       <c r="F51" s="1"/>
@@ -16142,7 +18658,10 @@
     <row r="52" spans="1:87" s="245" customFormat="1">
       <c r="A52" s="1"/>
       <c r="B52" s="1"/>
-      <c r="C52" s="1"/>
+      <c r="C52" s="1" t="str">
+        <f>符號工具!B4</f>
+        <v>゜</v>
+      </c>
       <c r="D52" s="1"/>
       <c r="E52" s="1"/>
       <c r="F52" s="1"/>
@@ -16223,7 +18742,10 @@
     <row r="53" spans="1:87" s="245" customFormat="1">
       <c r="A53" s="1"/>
       <c r="B53" s="1"/>
-      <c r="C53" s="1"/>
+      <c r="C53" s="1" t="str">
+        <f>符號工具!B5</f>
+        <v>ⁿ</v>
+      </c>
       <c r="D53" s="1"/>
       <c r="E53" s="1"/>
       <c r="F53" s="1"/>
@@ -16304,7 +18826,10 @@
     <row r="54" spans="1:87" s="245" customFormat="1">
       <c r="A54" s="1"/>
       <c r="B54" s="1"/>
-      <c r="C54" s="1"/>
+      <c r="C54" s="1" t="str">
+        <f>符號工具!B6</f>
+        <v>ㄥ</v>
+      </c>
       <c r="D54" s="1"/>
       <c r="E54" s="1"/>
       <c r="F54" s="1"/>
@@ -24227,25 +26752,25 @@
   <sheetData>
     <row r="1" spans="2:19" ht="21.75" thickBot="1"/>
     <row r="2" spans="2:19" ht="24" thickBot="1">
-      <c r="B2" s="268" t="s">
+      <c r="B2" s="265" t="s">
         <v>332</v>
       </c>
-      <c r="C2" s="270" t="s">
+      <c r="C2" s="267" t="s">
         <v>333</v>
       </c>
-      <c r="D2" s="271"/>
-      <c r="E2" s="274" t="s">
+      <c r="D2" s="268"/>
+      <c r="E2" s="271" t="s">
         <v>334</v>
       </c>
-      <c r="F2" s="275"/>
-      <c r="G2" s="276"/>
-      <c r="H2" s="274" t="s">
+      <c r="F2" s="272"/>
+      <c r="G2" s="273"/>
+      <c r="H2" s="271" t="s">
         <v>335</v>
       </c>
-      <c r="I2" s="275"/>
-      <c r="J2" s="275"/>
-      <c r="K2" s="275"/>
-      <c r="L2" s="276"/>
+      <c r="I2" s="272"/>
+      <c r="J2" s="272"/>
+      <c r="K2" s="272"/>
+      <c r="L2" s="273"/>
       <c r="O2" s="236" t="s">
         <v>484</v>
       </c>
@@ -24260,9 +26785,9 @@
       </c>
     </row>
     <row r="3" spans="2:19" ht="24" thickBot="1">
-      <c r="B3" s="269"/>
-      <c r="C3" s="272"/>
-      <c r="D3" s="273"/>
+      <c r="B3" s="266"/>
+      <c r="C3" s="269"/>
+      <c r="D3" s="270"/>
       <c r="E3" s="234" t="s">
         <v>336</v>
       </c>
@@ -24281,10 +26806,10 @@
       <c r="J3" s="234" t="s">
         <v>341</v>
       </c>
-      <c r="K3" s="274" t="s">
+      <c r="K3" s="271" t="s">
         <v>342</v>
       </c>
-      <c r="L3" s="276"/>
+      <c r="L3" s="273"/>
       <c r="O3" s="236" t="s">
         <v>278</v>
       </c>
@@ -25176,57 +27701,57 @@
       <c r="B27" s="234" t="s">
         <v>447</v>
       </c>
-      <c r="C27" s="265" t="s">
+      <c r="C27" s="274" t="s">
         <v>192</v>
       </c>
-      <c r="D27" s="266"/>
-      <c r="E27" s="265" t="s">
+      <c r="D27" s="275"/>
+      <c r="E27" s="274" t="s">
         <v>448</v>
       </c>
-      <c r="F27" s="267"/>
-      <c r="G27" s="267"/>
-      <c r="H27" s="267"/>
-      <c r="I27" s="267"/>
-      <c r="J27" s="266"/>
-      <c r="K27" s="265" t="s">
+      <c r="F27" s="276"/>
+      <c r="G27" s="276"/>
+      <c r="H27" s="276"/>
+      <c r="I27" s="276"/>
+      <c r="J27" s="275"/>
+      <c r="K27" s="274" t="s">
         <v>449</v>
       </c>
-      <c r="L27" s="266"/>
+      <c r="L27" s="275"/>
     </row>
     <row r="28" spans="2:20" ht="24" thickBot="1">
       <c r="B28" s="234" t="s">
         <v>450</v>
       </c>
-      <c r="C28" s="265" t="s">
+      <c r="C28" s="274" t="s">
         <v>451</v>
       </c>
-      <c r="D28" s="266"/>
-      <c r="E28" s="265" t="s">
+      <c r="D28" s="275"/>
+      <c r="E28" s="274" t="s">
         <v>448</v>
       </c>
-      <c r="F28" s="267"/>
-      <c r="G28" s="267"/>
-      <c r="H28" s="267"/>
-      <c r="I28" s="267"/>
-      <c r="J28" s="266"/>
-      <c r="K28" s="265" t="s">
+      <c r="F28" s="276"/>
+      <c r="G28" s="276"/>
+      <c r="H28" s="276"/>
+      <c r="I28" s="276"/>
+      <c r="J28" s="275"/>
+      <c r="K28" s="274" t="s">
         <v>452</v>
       </c>
-      <c r="L28" s="266"/>
+      <c r="L28" s="275"/>
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="C2:D3"/>
-    <mergeCell ref="E2:G2"/>
-    <mergeCell ref="H2:L2"/>
-    <mergeCell ref="K3:L3"/>
     <mergeCell ref="C27:D27"/>
     <mergeCell ref="E27:J27"/>
     <mergeCell ref="K27:L27"/>
     <mergeCell ref="C28:D28"/>
     <mergeCell ref="E28:J28"/>
     <mergeCell ref="K28:L28"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="C2:D3"/>
+    <mergeCell ref="E2:G2"/>
+    <mergeCell ref="H2:L2"/>
+    <mergeCell ref="K3:L3"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -25248,30 +27773,30 @@
   <sheetData>
     <row r="1" spans="2:20" ht="21.75" thickBot="1"/>
     <row r="2" spans="2:20" ht="24" thickBot="1">
-      <c r="B2" s="268" t="s">
+      <c r="B2" s="265" t="s">
         <v>332</v>
       </c>
-      <c r="C2" s="270" t="s">
+      <c r="C2" s="267" t="s">
         <v>333</v>
       </c>
-      <c r="D2" s="271"/>
-      <c r="E2" s="274" t="s">
+      <c r="D2" s="268"/>
+      <c r="E2" s="271" t="s">
         <v>334</v>
       </c>
-      <c r="F2" s="275"/>
-      <c r="G2" s="276"/>
-      <c r="H2" s="274" t="s">
+      <c r="F2" s="272"/>
+      <c r="G2" s="273"/>
+      <c r="H2" s="271" t="s">
         <v>335</v>
       </c>
-      <c r="I2" s="275"/>
-      <c r="J2" s="275"/>
-      <c r="K2" s="275"/>
-      <c r="L2" s="276"/>
+      <c r="I2" s="272"/>
+      <c r="J2" s="272"/>
+      <c r="K2" s="272"/>
+      <c r="L2" s="273"/>
     </row>
     <row r="3" spans="2:20" ht="24" thickBot="1">
-      <c r="B3" s="269"/>
-      <c r="C3" s="272"/>
-      <c r="D3" s="273"/>
+      <c r="B3" s="266"/>
+      <c r="C3" s="269"/>
+      <c r="D3" s="270"/>
       <c r="E3" s="234" t="s">
         <v>336</v>
       </c>
@@ -25290,10 +27815,10 @@
       <c r="J3" s="234" t="s">
         <v>341</v>
       </c>
-      <c r="K3" s="274" t="s">
+      <c r="K3" s="271" t="s">
         <v>342</v>
       </c>
-      <c r="L3" s="276"/>
+      <c r="L3" s="273"/>
       <c r="N3" s="240" t="s">
         <v>509</v>
       </c>
@@ -26326,43 +28851,43 @@
       <c r="B27" s="234" t="s">
         <v>447</v>
       </c>
-      <c r="C27" s="265" t="s">
+      <c r="C27" s="274" t="s">
         <v>192</v>
       </c>
-      <c r="D27" s="266"/>
-      <c r="E27" s="265" t="s">
+      <c r="D27" s="275"/>
+      <c r="E27" s="274" t="s">
         <v>448</v>
       </c>
-      <c r="F27" s="267"/>
-      <c r="G27" s="267"/>
-      <c r="H27" s="267"/>
-      <c r="I27" s="267"/>
-      <c r="J27" s="266"/>
-      <c r="K27" s="265" t="s">
+      <c r="F27" s="276"/>
+      <c r="G27" s="276"/>
+      <c r="H27" s="276"/>
+      <c r="I27" s="276"/>
+      <c r="J27" s="275"/>
+      <c r="K27" s="274" t="s">
         <v>449</v>
       </c>
-      <c r="L27" s="266"/>
+      <c r="L27" s="275"/>
     </row>
     <row r="28" spans="2:21" ht="24" thickBot="1">
       <c r="B28" s="234" t="s">
         <v>450</v>
       </c>
-      <c r="C28" s="265" t="s">
+      <c r="C28" s="274" t="s">
         <v>451</v>
       </c>
-      <c r="D28" s="266"/>
-      <c r="E28" s="265" t="s">
+      <c r="D28" s="275"/>
+      <c r="E28" s="274" t="s">
         <v>448</v>
       </c>
-      <c r="F28" s="267"/>
-      <c r="G28" s="267"/>
-      <c r="H28" s="267"/>
-      <c r="I28" s="267"/>
-      <c r="J28" s="266"/>
-      <c r="K28" s="265" t="s">
+      <c r="F28" s="276"/>
+      <c r="G28" s="276"/>
+      <c r="H28" s="276"/>
+      <c r="I28" s="276"/>
+      <c r="J28" s="275"/>
+      <c r="K28" s="274" t="s">
         <v>452</v>
       </c>
-      <c r="L28" s="266"/>
+      <c r="L28" s="275"/>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="N4:T20">
@@ -26401,25 +28926,25 @@
   <sheetData>
     <row r="1" spans="2:18" ht="21.75" thickBot="1"/>
     <row r="2" spans="2:18" ht="24" thickBot="1">
-      <c r="B2" s="268" t="s">
+      <c r="B2" s="265" t="s">
         <v>332</v>
       </c>
-      <c r="C2" s="270" t="s">
+      <c r="C2" s="267" t="s">
         <v>333</v>
       </c>
-      <c r="D2" s="271"/>
-      <c r="E2" s="274" t="s">
+      <c r="D2" s="268"/>
+      <c r="E2" s="271" t="s">
         <v>334</v>
       </c>
-      <c r="F2" s="275"/>
-      <c r="G2" s="276"/>
-      <c r="H2" s="274" t="s">
+      <c r="F2" s="272"/>
+      <c r="G2" s="273"/>
+      <c r="H2" s="271" t="s">
         <v>335</v>
       </c>
-      <c r="I2" s="275"/>
-      <c r="J2" s="275"/>
-      <c r="K2" s="275"/>
-      <c r="L2" s="276"/>
+      <c r="I2" s="272"/>
+      <c r="J2" s="272"/>
+      <c r="K2" s="272"/>
+      <c r="L2" s="273"/>
       <c r="P2" s="236" t="str">
         <f xml:space="preserve"> "([48])"</f>
         <v>([48])</v>
@@ -26429,9 +28954,9 @@
       </c>
     </row>
     <row r="3" spans="2:18" ht="24" thickBot="1">
-      <c r="B3" s="269"/>
-      <c r="C3" s="272"/>
-      <c r="D3" s="273"/>
+      <c r="B3" s="266"/>
+      <c r="C3" s="269"/>
+      <c r="D3" s="270"/>
       <c r="E3" s="234" t="s">
         <v>336</v>
       </c>
@@ -26450,10 +28975,10 @@
       <c r="J3" s="234" t="s">
         <v>341</v>
       </c>
-      <c r="K3" s="274" t="s">
+      <c r="K3" s="271" t="s">
         <v>342</v>
       </c>
-      <c r="L3" s="276"/>
+      <c r="L3" s="273"/>
       <c r="N3" s="236" t="s">
         <v>454</v>
       </c>
@@ -27345,43 +29870,43 @@
       <c r="B27" s="234" t="s">
         <v>447</v>
       </c>
-      <c r="C27" s="265" t="s">
+      <c r="C27" s="274" t="s">
         <v>192</v>
       </c>
-      <c r="D27" s="266"/>
-      <c r="E27" s="265" t="s">
+      <c r="D27" s="275"/>
+      <c r="E27" s="274" t="s">
         <v>448</v>
       </c>
-      <c r="F27" s="267"/>
-      <c r="G27" s="267"/>
-      <c r="H27" s="267"/>
-      <c r="I27" s="267"/>
-      <c r="J27" s="266"/>
-      <c r="K27" s="265" t="s">
+      <c r="F27" s="276"/>
+      <c r="G27" s="276"/>
+      <c r="H27" s="276"/>
+      <c r="I27" s="276"/>
+      <c r="J27" s="275"/>
+      <c r="K27" s="274" t="s">
         <v>449</v>
       </c>
-      <c r="L27" s="266"/>
+      <c r="L27" s="275"/>
     </row>
     <row r="28" spans="2:19" ht="24" thickBot="1">
       <c r="B28" s="234" t="s">
         <v>450</v>
       </c>
-      <c r="C28" s="265" t="s">
+      <c r="C28" s="274" t="s">
         <v>451</v>
       </c>
-      <c r="D28" s="266"/>
-      <c r="E28" s="265" t="s">
+      <c r="D28" s="275"/>
+      <c r="E28" s="274" t="s">
         <v>448</v>
       </c>
-      <c r="F28" s="267"/>
-      <c r="G28" s="267"/>
-      <c r="H28" s="267"/>
-      <c r="I28" s="267"/>
-      <c r="J28" s="266"/>
-      <c r="K28" s="265" t="s">
+      <c r="F28" s="276"/>
+      <c r="G28" s="276"/>
+      <c r="H28" s="276"/>
+      <c r="I28" s="276"/>
+      <c r="J28" s="275"/>
+      <c r="K28" s="274" t="s">
         <v>452</v>
       </c>
-      <c r="L28" s="266"/>
+      <c r="L28" s="275"/>
     </row>
   </sheetData>
   <mergeCells count="11">
@@ -33092,6 +35617,13 @@
       <c r="DG24" s="18"/>
     </row>
     <row r="25" spans="1:111" s="143" customFormat="1" ht="45" customHeight="1">
+      <c r="G25" s="143" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT(Z20, AT20)</f>
+        <v>ㄧㆩ</v>
+      </c>
+      <c r="H25" s="277" t="s">
+        <v>568</v>
+      </c>
       <c r="AD25" s="152"/>
       <c r="AF25" s="152"/>
       <c r="AG25" s="152"/>
@@ -42981,4 +45513,1448 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="200" verticalDpi="200" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC470F5E-8204-4863-A7A7-EFB41AB826B2}">
+  <dimension ref="B1:Z37"/>
+  <sheetFormatPr defaultRowHeight="25.5"/>
+  <cols>
+    <col min="1" max="1" width="6.09765625" style="279" customWidth="1"/>
+    <col min="2" max="2" width="8.796875" style="278"/>
+    <col min="3" max="4" width="15.69921875" style="279" customWidth="1"/>
+    <col min="5" max="5" width="8.09765625" style="279" customWidth="1"/>
+    <col min="6" max="10" width="9.19921875" style="279" customWidth="1"/>
+    <col min="11" max="11" width="40.19921875" style="279" customWidth="1"/>
+    <col min="12" max="12" width="15.69921875" style="279" customWidth="1"/>
+    <col min="13" max="13" width="2.59765625" style="292" bestFit="1" customWidth="1"/>
+    <col min="14" max="22" width="8.5" style="292" customWidth="1"/>
+    <col min="23" max="26" width="8.796875" style="292"/>
+    <col min="27" max="16384" width="8.796875" style="279"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:26" ht="36" customHeight="1" thickBot="1">
+      <c r="K1" s="280" t="s">
+        <v>569</v>
+      </c>
+      <c r="M1" s="281"/>
+      <c r="N1" s="281"/>
+      <c r="O1" s="281"/>
+      <c r="P1" s="282"/>
+      <c r="Q1" s="282"/>
+      <c r="R1" s="283"/>
+      <c r="S1" s="283"/>
+      <c r="T1" s="283"/>
+      <c r="U1" s="283"/>
+      <c r="V1" s="284"/>
+      <c r="W1" s="285"/>
+      <c r="X1" s="285"/>
+      <c r="Y1" s="284"/>
+      <c r="Z1" s="283"/>
+    </row>
+    <row r="2" spans="2:26" s="287" customFormat="1" ht="35.25" customHeight="1" thickBot="1">
+      <c r="B2" s="286" t="s">
+        <v>570</v>
+      </c>
+      <c r="C2" s="286" t="s">
+        <v>571</v>
+      </c>
+      <c r="D2" s="286" t="s">
+        <v>572</v>
+      </c>
+      <c r="F2" s="288" t="s">
+        <v>570</v>
+      </c>
+      <c r="G2" s="289" t="s">
+        <v>573</v>
+      </c>
+      <c r="H2" s="289" t="s">
+        <v>574</v>
+      </c>
+      <c r="I2" s="289" t="s">
+        <v>575</v>
+      </c>
+      <c r="J2" s="290" t="s">
+        <v>576</v>
+      </c>
+      <c r="K2" s="290" t="s">
+        <v>577</v>
+      </c>
+      <c r="L2" s="291"/>
+      <c r="M2" s="281"/>
+      <c r="N2" s="292"/>
+      <c r="O2" s="292"/>
+      <c r="P2" s="292"/>
+      <c r="Q2" s="292"/>
+      <c r="R2" s="292"/>
+      <c r="S2" s="292"/>
+      <c r="T2" s="292"/>
+      <c r="U2" s="292"/>
+      <c r="V2" s="292"/>
+      <c r="W2" s="292"/>
+      <c r="X2" s="292"/>
+      <c r="Y2" s="292"/>
+      <c r="Z2" s="292"/>
+    </row>
+    <row r="3" spans="2:26" ht="35.25" thickBot="1">
+      <c r="B3" s="293" t="s">
+        <v>578</v>
+      </c>
+      <c r="C3" s="294" t="s">
+        <v>579</v>
+      </c>
+      <c r="D3" s="295" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT("a", _xlfn.UNICHAR(HEX2DEC(RIGHT(C3,4))))</f>
+        <v>aʔ</v>
+      </c>
+      <c r="F3" s="296" t="s">
+        <v>578</v>
+      </c>
+      <c r="G3" s="294">
+        <f xml:space="preserve"> _xlfn.UNICODE(F3)</f>
+        <v>660</v>
+      </c>
+      <c r="H3" s="294" t="str">
+        <f xml:space="preserve"> DEC2HEX(G3, 4)</f>
+        <v>0294</v>
+      </c>
+      <c r="I3" s="294" t="str">
+        <f>_xlfn.CONCAT("U+",H3)</f>
+        <v>U+0294</v>
+      </c>
+      <c r="J3" s="297" t="str">
+        <f xml:space="preserve"> _xlfn.UNICHAR(HEX2DEC(RIGHT(I3,4)))</f>
+        <v>ʔ</v>
+      </c>
+      <c r="K3" s="280" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT("= UNICHAR(HEX2DEC(RIGHT(""", I3,""",4)))")</f>
+        <v>= UNICHAR(HEX2DEC(RIGHT("U+0294",4)))</v>
+      </c>
+      <c r="L3" s="283"/>
+      <c r="N3" s="298" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT("o", _xlfn.UNICHAR(HEX2DEC(RIGHT("U+0358",4))))</f>
+        <v>o͘</v>
+      </c>
+      <c r="O3" s="299" t="s">
+        <v>580</v>
+      </c>
+      <c r="P3" s="299" t="s">
+        <v>581</v>
+      </c>
+      <c r="Q3" s="299" t="s">
+        <v>582</v>
+      </c>
+      <c r="R3" s="299" t="s">
+        <v>583</v>
+      </c>
+      <c r="S3" s="299" t="s">
+        <v>584</v>
+      </c>
+      <c r="T3" s="299" t="s">
+        <v>585</v>
+      </c>
+      <c r="U3" s="299" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="4" spans="2:26" ht="30.75" thickBot="1">
+      <c r="B4" s="300" t="s">
+        <v>587</v>
+      </c>
+      <c r="C4" s="294" t="s">
+        <v>588</v>
+      </c>
+      <c r="D4" s="295" t="str">
+        <f xml:space="preserve"> _xlfn.UNICHAR(HEX2DEC(RIGHT(C4,4)))</f>
+        <v>゜</v>
+      </c>
+      <c r="F4" s="296" t="s">
+        <v>589</v>
+      </c>
+      <c r="G4" s="294">
+        <f xml:space="preserve"> _xlfn.UNICODE(F4)</f>
+        <v>12444</v>
+      </c>
+      <c r="H4" s="294" t="str">
+        <f xml:space="preserve"> DEC2HEX(G4, 4)</f>
+        <v>309C</v>
+      </c>
+      <c r="I4" s="294" t="str">
+        <f>_xlfn.CONCAT("U+",H4)</f>
+        <v>U+309C</v>
+      </c>
+      <c r="J4" s="297" t="str">
+        <f xml:space="preserve"> _xlfn.UNICHAR(HEX2DEC(RIGHT(I4,4)))</f>
+        <v>゜</v>
+      </c>
+      <c r="K4" s="280" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT("= UNICHAR(HEX2DEC(RIGHT(""", I4,""",4)))")</f>
+        <v>= UNICHAR(HEX2DEC(RIGHT("U+309C",4)))</v>
+      </c>
+      <c r="L4" s="283"/>
+      <c r="M4" s="292">
+        <v>1</v>
+      </c>
+      <c r="N4" s="301" t="str">
+        <f>IFERROR( _xlfn.CONCAT("o", _xlfn.UNICHAR(HEX2DEC(RIGHT("U+0358",4))), _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!E4,4)))), $N$3)</f>
+        <v>o͘</v>
+      </c>
+      <c r="O4" s="301" t="str">
+        <f>IFERROR( _xlfn.CONCAT(O$3, IF([1]【調】韻母標調!$E4="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!$E4,4))))), "")</f>
+        <v>a</v>
+      </c>
+      <c r="P4" s="301" t="str">
+        <f>IFERROR( _xlfn.CONCAT(P$3, IF([1]【調】韻母標調!$E4="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!$E4,4))))), "")</f>
+        <v>i</v>
+      </c>
+      <c r="Q4" s="301" t="str">
+        <f>IFERROR( _xlfn.CONCAT(Q$3, IF([1]【調】韻母標調!$E4="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!$E4,4))))), "")</f>
+        <v>u</v>
+      </c>
+      <c r="R4" s="301" t="str">
+        <f>IFERROR( _xlfn.CONCAT(R$3, IF([1]【調】韻母標調!$E4="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!$E4,4))))), "")</f>
+        <v>e</v>
+      </c>
+      <c r="S4" s="301" t="str">
+        <f>IFERROR( _xlfn.CONCAT(S$3, IF([1]【調】韻母標調!$E4="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!$E4,4))))), "")</f>
+        <v>o</v>
+      </c>
+      <c r="T4" s="301" t="str">
+        <f>IFERROR( _xlfn.CONCAT(T$3, IF([1]【調】韻母標調!$E4="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!$E4,4))))), "")</f>
+        <v>m</v>
+      </c>
+      <c r="U4" s="301" t="str">
+        <f>IFERROR( _xlfn.CONCAT(U$3, IF([1]【調】韻母標調!$E4="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!$E4,4))))), "")</f>
+        <v>n</v>
+      </c>
+    </row>
+    <row r="5" spans="2:26" ht="30.75" thickBot="1">
+      <c r="B5" s="300" t="s">
+        <v>590</v>
+      </c>
+      <c r="C5" s="294" t="s">
+        <v>591</v>
+      </c>
+      <c r="D5" s="302"/>
+      <c r="F5" s="296" t="s">
+        <v>592</v>
+      </c>
+      <c r="G5" s="294">
+        <f xml:space="preserve"> _xlfn.UNICODE(F5)</f>
+        <v>12581</v>
+      </c>
+      <c r="H5" s="294" t="str">
+        <f xml:space="preserve"> DEC2HEX(G5, 4)</f>
+        <v>3125</v>
+      </c>
+      <c r="I5" s="294" t="str">
+        <f>_xlfn.CONCAT("U+",H5)</f>
+        <v>U+3125</v>
+      </c>
+      <c r="J5" s="297" t="str">
+        <f xml:space="preserve"> _xlfn.UNICHAR(HEX2DEC(RIGHT(I5,4)))</f>
+        <v>ㄥ</v>
+      </c>
+      <c r="K5" s="280" t="str">
+        <f t="shared" ref="K5:K6" si="0" xml:space="preserve"> _xlfn.CONCAT("= UNICHAR(HEX2DEC(RIGHT(""", I5,""",4)))")</f>
+        <v>= UNICHAR(HEX2DEC(RIGHT("U+3125",4)))</v>
+      </c>
+      <c r="L5" s="283"/>
+      <c r="M5" s="292">
+        <v>2</v>
+      </c>
+      <c r="N5" s="301" t="str">
+        <f>IFERROR( _xlfn.CONCAT("o", _xlfn.UNICHAR(HEX2DEC(RIGHT("U+0358",4))), _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!E5,4)))), $N$3)</f>
+        <v>ó͘</v>
+      </c>
+      <c r="O5" s="301" t="str">
+        <f>IFERROR( _xlfn.CONCAT(O$3, IF([1]【調】韻母標調!$E5="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!$E5,4))))), "")</f>
+        <v>á</v>
+      </c>
+      <c r="P5" s="301" t="str">
+        <f>IFERROR( _xlfn.CONCAT(P$3, IF([1]【調】韻母標調!$E5="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!$E5,4))))), "")</f>
+        <v>í</v>
+      </c>
+      <c r="Q5" s="301" t="str">
+        <f>IFERROR( _xlfn.CONCAT(Q$3, IF([1]【調】韻母標調!$E5="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!$E5,4))))), "")</f>
+        <v>ú</v>
+      </c>
+      <c r="R5" s="301" t="str">
+        <f>IFERROR( _xlfn.CONCAT(R$3, IF([1]【調】韻母標調!$E5="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!$E5,4))))), "")</f>
+        <v>é</v>
+      </c>
+      <c r="S5" s="301" t="str">
+        <f>IFERROR( _xlfn.CONCAT(S$3, IF([1]【調】韻母標調!$E5="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!$E5,4))))), "")</f>
+        <v>ó</v>
+      </c>
+      <c r="T5" s="301" t="str">
+        <f>IFERROR( _xlfn.CONCAT(T$3, IF([1]【調】韻母標調!$E5="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!$E5,4))))), "")</f>
+        <v>ḿ</v>
+      </c>
+      <c r="U5" s="301" t="str">
+        <f>IFERROR( _xlfn.CONCAT(U$3, IF([1]【調】韻母標調!$E5="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!$E5,4))))), "")</f>
+        <v>ń</v>
+      </c>
+    </row>
+    <row r="6" spans="2:26" ht="30.75" thickBot="1">
+      <c r="B6" s="300" t="s">
+        <v>593</v>
+      </c>
+      <c r="C6" s="294" t="s">
+        <v>281</v>
+      </c>
+      <c r="D6" s="295" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT("a", _xlfn.UNICHAR(HEX2DEC(RIGHT(C6,4))))</f>
+        <v>aⁿ</v>
+      </c>
+      <c r="F6" s="296" t="s">
+        <v>594</v>
+      </c>
+      <c r="G6" s="294">
+        <f xml:space="preserve"> _xlfn.UNICODE(F6)</f>
+        <v>8319</v>
+      </c>
+      <c r="H6" s="294" t="str">
+        <f xml:space="preserve"> DEC2HEX(G6, 4)</f>
+        <v>207F</v>
+      </c>
+      <c r="I6" s="294" t="str">
+        <f>_xlfn.CONCAT("U+",H6)</f>
+        <v>U+207F</v>
+      </c>
+      <c r="J6" s="297" t="str">
+        <f xml:space="preserve"> _xlfn.UNICHAR(HEX2DEC(RIGHT(I6,4)))</f>
+        <v>ⁿ</v>
+      </c>
+      <c r="K6" s="280" t="str">
+        <f t="shared" si="0"/>
+        <v>= UNICHAR(HEX2DEC(RIGHT("U+207F",4)))</v>
+      </c>
+      <c r="L6" s="283"/>
+      <c r="M6" s="292">
+        <v>3</v>
+      </c>
+      <c r="N6" s="301" t="str">
+        <f>IFERROR( _xlfn.CONCAT("o", _xlfn.UNICHAR(HEX2DEC(RIGHT("U+0358",4))), _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!E6,4)))), $N$3)</f>
+        <v>ò͘</v>
+      </c>
+      <c r="O6" s="301" t="str">
+        <f>IFERROR( _xlfn.CONCAT(O$3, IF([1]【調】韻母標調!$E6="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!$E6,4))))), "")</f>
+        <v>à</v>
+      </c>
+      <c r="P6" s="301" t="str">
+        <f>IFERROR( _xlfn.CONCAT(P$3, IF([1]【調】韻母標調!$E6="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!$E6,4))))), "")</f>
+        <v>ì</v>
+      </c>
+      <c r="Q6" s="301" t="str">
+        <f>IFERROR( _xlfn.CONCAT(Q$3, IF([1]【調】韻母標調!$E6="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!$E6,4))))), "")</f>
+        <v>ù</v>
+      </c>
+      <c r="R6" s="301" t="str">
+        <f>IFERROR( _xlfn.CONCAT(R$3, IF([1]【調】韻母標調!$E6="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!$E6,4))))), "")</f>
+        <v>è</v>
+      </c>
+      <c r="S6" s="301" t="str">
+        <f>IFERROR( _xlfn.CONCAT(S$3, IF([1]【調】韻母標調!$E6="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!$E6,4))))), "")</f>
+        <v>ò</v>
+      </c>
+      <c r="T6" s="301" t="str">
+        <f>IFERROR( _xlfn.CONCAT(T$3, IF([1]【調】韻母標調!$E6="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!$E6,4))))), "")</f>
+        <v>m̀</v>
+      </c>
+      <c r="U6" s="301" t="str">
+        <f>IFERROR( _xlfn.CONCAT(U$3, IF([1]【調】韻母標調!$E6="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!$E6,4))))), "")</f>
+        <v>ǹ</v>
+      </c>
+    </row>
+    <row r="7" spans="2:26" ht="30.75" thickBot="1">
+      <c r="B7" s="279"/>
+      <c r="E7" s="283"/>
+      <c r="F7" s="283"/>
+      <c r="G7" s="283"/>
+      <c r="H7" s="283"/>
+      <c r="I7" s="283"/>
+      <c r="J7" s="283"/>
+      <c r="K7" s="283"/>
+      <c r="L7" s="283"/>
+      <c r="M7" s="292">
+        <v>4</v>
+      </c>
+      <c r="N7" s="301" t="str">
+        <f>IFERROR( _xlfn.CONCAT("o", _xlfn.UNICHAR(HEX2DEC(RIGHT("U+0358",4))), _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!E7,4)))), $N$3)</f>
+        <v>o͘</v>
+      </c>
+      <c r="O7" s="301" t="str">
+        <f>IFERROR( _xlfn.CONCAT(O$3, IF([1]【調】韻母標調!$E7="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!$E7,4))))), "")</f>
+        <v>a</v>
+      </c>
+      <c r="P7" s="301" t="str">
+        <f>IFERROR( _xlfn.CONCAT(P$3, IF([1]【調】韻母標調!$E7="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!$E7,4))))), "")</f>
+        <v>i</v>
+      </c>
+      <c r="Q7" s="301" t="str">
+        <f>IFERROR( _xlfn.CONCAT(Q$3, IF([1]【調】韻母標調!$E7="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!$E7,4))))), "")</f>
+        <v>u</v>
+      </c>
+      <c r="R7" s="301" t="str">
+        <f>IFERROR( _xlfn.CONCAT(R$3, IF([1]【調】韻母標調!$E7="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!$E7,4))))), "")</f>
+        <v>e</v>
+      </c>
+      <c r="S7" s="301" t="str">
+        <f>IFERROR( _xlfn.CONCAT(S$3, IF([1]【調】韻母標調!$E7="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!$E7,4))))), "")</f>
+        <v>o</v>
+      </c>
+      <c r="T7" s="301" t="str">
+        <f>IFERROR( _xlfn.CONCAT(T$3, IF([1]【調】韻母標調!$E7="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!$E7,4))))), "")</f>
+        <v>m</v>
+      </c>
+      <c r="U7" s="301" t="str">
+        <f>IFERROR( _xlfn.CONCAT(U$3, IF([1]【調】韻母標調!$E7="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!$E7,4))))), "")</f>
+        <v>n</v>
+      </c>
+    </row>
+    <row r="8" spans="2:26" ht="30.75" thickBot="1">
+      <c r="B8" s="286" t="s">
+        <v>570</v>
+      </c>
+      <c r="C8" s="286" t="s">
+        <v>571</v>
+      </c>
+      <c r="D8" s="286" t="s">
+        <v>572</v>
+      </c>
+      <c r="F8" s="283"/>
+      <c r="G8" s="283"/>
+      <c r="H8" s="283"/>
+      <c r="I8" s="283"/>
+      <c r="J8" s="283"/>
+      <c r="K8" s="283"/>
+      <c r="L8" s="283"/>
+      <c r="M8" s="292">
+        <v>5</v>
+      </c>
+      <c r="N8" s="301" t="str">
+        <f>IFERROR( _xlfn.CONCAT("o", _xlfn.UNICHAR(HEX2DEC(RIGHT("U+0358",4))), _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!E8,4)))), "")</f>
+        <v>ǒ͘</v>
+      </c>
+      <c r="O8" s="301" t="str">
+        <f>IFERROR( _xlfn.CONCAT(O$3, IF([1]【調】韻母標調!$E8="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!$E8,4))))), "")</f>
+        <v>ǎ</v>
+      </c>
+      <c r="P8" s="301" t="str">
+        <f>IFERROR( _xlfn.CONCAT(P$3, IF([1]【調】韻母標調!$E8="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!$E8,4))))), "")</f>
+        <v>ǐ</v>
+      </c>
+      <c r="Q8" s="301" t="str">
+        <f>IFERROR( _xlfn.CONCAT(Q$3, IF([1]【調】韻母標調!$E8="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!$E8,4))))), "")</f>
+        <v>ǔ</v>
+      </c>
+      <c r="R8" s="301" t="str">
+        <f>IFERROR( _xlfn.CONCAT(R$3, IF([1]【調】韻母標調!$E8="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!$E8,4))))), "")</f>
+        <v>ě</v>
+      </c>
+      <c r="S8" s="301" t="str">
+        <f>IFERROR( _xlfn.CONCAT(S$3, IF([1]【調】韻母標調!$E8="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!$E8,4))))), "")</f>
+        <v>ǒ</v>
+      </c>
+      <c r="T8" s="301" t="str">
+        <f>IFERROR( _xlfn.CONCAT(T$3, IF([1]【調】韻母標調!$E8="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!$E8,4))))), "")</f>
+        <v>m̌</v>
+      </c>
+      <c r="U8" s="301" t="str">
+        <f>IFERROR( _xlfn.CONCAT(U$3, IF([1]【調】韻母標調!$E8="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!$E8,4))))), "")</f>
+        <v>ň</v>
+      </c>
+    </row>
+    <row r="9" spans="2:26" ht="30.75" thickBot="1">
+      <c r="B9" s="300" t="s">
+        <v>595</v>
+      </c>
+      <c r="C9" s="303" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT("U+", DEC2HEX(_xlfn.UNICODE(B9),4))</f>
+        <v>U+014B</v>
+      </c>
+      <c r="D9" s="304"/>
+      <c r="F9" s="283"/>
+      <c r="G9" s="283"/>
+      <c r="H9" s="283"/>
+      <c r="I9" s="283"/>
+      <c r="J9" s="283"/>
+      <c r="L9" s="283"/>
+      <c r="M9" s="292">
+        <v>6</v>
+      </c>
+      <c r="N9" s="301" t="str">
+        <f>IFERROR( _xlfn.CONCAT("o", _xlfn.UNICHAR(HEX2DEC(RIGHT("U+0358",4))), _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!E9,4)))), "")</f>
+        <v>ó͘</v>
+      </c>
+      <c r="O9" s="301" t="str">
+        <f>IFERROR( _xlfn.CONCAT(O$3, IF([1]【調】韻母標調!$E9="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!$E9,4))))), "")</f>
+        <v>á</v>
+      </c>
+      <c r="P9" s="301" t="str">
+        <f>IFERROR( _xlfn.CONCAT(P$3, IF([1]【調】韻母標調!$E9="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!$E9,4))))), "")</f>
+        <v>í</v>
+      </c>
+      <c r="Q9" s="301" t="str">
+        <f>IFERROR( _xlfn.CONCAT(Q$3, IF([1]【調】韻母標調!$E9="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!$E9,4))))), "")</f>
+        <v>ú</v>
+      </c>
+      <c r="R9" s="301" t="str">
+        <f>IFERROR( _xlfn.CONCAT(R$3, IF([1]【調】韻母標調!$E9="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!$E9,4))))), "")</f>
+        <v>é</v>
+      </c>
+      <c r="S9" s="301" t="str">
+        <f>IFERROR( _xlfn.CONCAT(S$3, IF([1]【調】韻母標調!$E9="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!$E9,4))))), "")</f>
+        <v>ó</v>
+      </c>
+      <c r="T9" s="301" t="str">
+        <f>IFERROR( _xlfn.CONCAT(T$3, IF([1]【調】韻母標調!$E9="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!$E9,4))))), "")</f>
+        <v>ḿ</v>
+      </c>
+      <c r="U9" s="301" t="str">
+        <f>IFERROR( _xlfn.CONCAT(U$3, IF([1]【調】韻母標調!$E9="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!$E9,4))))), "")</f>
+        <v>ń</v>
+      </c>
+    </row>
+    <row r="10" spans="2:26" ht="35.25" thickBot="1">
+      <c r="B10" s="300" t="s">
+        <v>596</v>
+      </c>
+      <c r="C10" s="303" t="str">
+        <f t="shared" ref="C10:C12" si="1" xml:space="preserve"> _xlfn.CONCAT("U+", DEC2HEX(_xlfn.UNICODE(B10),4))</f>
+        <v>U+014B</v>
+      </c>
+      <c r="D10" s="305"/>
+      <c r="F10" s="283"/>
+      <c r="G10" s="283"/>
+      <c r="H10" s="283"/>
+      <c r="I10" s="283"/>
+      <c r="J10" s="283"/>
+      <c r="L10" s="283"/>
+      <c r="M10" s="292">
+        <v>7</v>
+      </c>
+      <c r="N10" s="301" t="str">
+        <f>IFERROR( _xlfn.CONCAT("o", _xlfn.UNICHAR(HEX2DEC(RIGHT("U+0358",4))), _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!E10,4)))), "")</f>
+        <v>ō͘</v>
+      </c>
+      <c r="O10" s="301" t="str">
+        <f>IFERROR( _xlfn.CONCAT(O$3, IF([1]【調】韻母標調!$E10="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!$E10,4))))), "")</f>
+        <v>ā</v>
+      </c>
+      <c r="P10" s="301" t="str">
+        <f>IFERROR( _xlfn.CONCAT(P$3, IF([1]【調】韻母標調!$E10="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!$E10,4))))), "")</f>
+        <v>ī</v>
+      </c>
+      <c r="Q10" s="301" t="str">
+        <f>IFERROR( _xlfn.CONCAT(Q$3, IF([1]【調】韻母標調!$E10="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!$E10,4))))), "")</f>
+        <v>ū</v>
+      </c>
+      <c r="R10" s="301" t="str">
+        <f>IFERROR( _xlfn.CONCAT(R$3, IF([1]【調】韻母標調!$E10="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!$E10,4))))), "")</f>
+        <v>ē</v>
+      </c>
+      <c r="S10" s="301" t="str">
+        <f>IFERROR( _xlfn.CONCAT(S$3, IF([1]【調】韻母標調!$E10="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!$E10,4))))), "")</f>
+        <v>ō</v>
+      </c>
+      <c r="T10" s="301" t="str">
+        <f>IFERROR( _xlfn.CONCAT(T$3, IF([1]【調】韻母標調!$E10="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!$E10,4))))), "")</f>
+        <v>m̄</v>
+      </c>
+      <c r="U10" s="301" t="str">
+        <f>IFERROR( _xlfn.CONCAT(U$3, IF([1]【調】韻母標調!$E10="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!$E10,4))))), "")</f>
+        <v>n̄</v>
+      </c>
+    </row>
+    <row r="11" spans="2:26" ht="35.25" thickBot="1">
+      <c r="B11" s="300" t="s">
+        <v>597</v>
+      </c>
+      <c r="C11" s="303" t="str">
+        <f t="shared" si="1"/>
+        <v>U+0259</v>
+      </c>
+      <c r="D11" s="304"/>
+      <c r="F11" s="283"/>
+      <c r="G11" s="283"/>
+      <c r="H11" s="283"/>
+      <c r="I11" s="283"/>
+      <c r="J11" s="283"/>
+      <c r="L11" s="283"/>
+      <c r="M11" s="292">
+        <v>8</v>
+      </c>
+      <c r="N11" s="301" t="str">
+        <f>IFERROR( _xlfn.CONCAT("o", _xlfn.UNICHAR(HEX2DEC(RIGHT("U+0358",4))), _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!E11,4)))), "")</f>
+        <v>o̍͘</v>
+      </c>
+      <c r="O11" s="301" t="str">
+        <f>IFERROR( _xlfn.CONCAT(O$3, IF([1]【調】韻母標調!$E11="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!$E11,4))))), "")</f>
+        <v>a̍</v>
+      </c>
+      <c r="P11" s="301" t="str">
+        <f>IFERROR( _xlfn.CONCAT(P$3, IF([1]【調】韻母標調!$E11="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!$E11,4))))), "")</f>
+        <v>i̍</v>
+      </c>
+      <c r="Q11" s="301" t="str">
+        <f>IFERROR( _xlfn.CONCAT(Q$3, IF([1]【調】韻母標調!$E11="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!$E11,4))))), "")</f>
+        <v>u̍</v>
+      </c>
+      <c r="R11" s="301" t="str">
+        <f>IFERROR( _xlfn.CONCAT(R$3, IF([1]【調】韻母標調!$E11="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!$E11,4))))), "")</f>
+        <v>e̍</v>
+      </c>
+      <c r="S11" s="301" t="str">
+        <f>IFERROR( _xlfn.CONCAT(S$3, IF([1]【調】韻母標調!$E11="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!$E11,4))))), "")</f>
+        <v>o̍</v>
+      </c>
+      <c r="T11" s="301" t="str">
+        <f>IFERROR( _xlfn.CONCAT(T$3, IF([1]【調】韻母標調!$E11="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!$E11,4))))), "")</f>
+        <v>m̍</v>
+      </c>
+      <c r="U11" s="301" t="str">
+        <f>IFERROR( _xlfn.CONCAT(U$3, IF([1]【調】韻母標調!$E11="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!$E11,4))))), "")</f>
+        <v>n̍</v>
+      </c>
+    </row>
+    <row r="12" spans="2:26" ht="35.25" thickBot="1">
+      <c r="B12" s="300" t="s">
+        <v>598</v>
+      </c>
+      <c r="C12" s="303" t="str">
+        <f t="shared" si="1"/>
+        <v>U+006F</v>
+      </c>
+      <c r="D12" s="304"/>
+      <c r="F12" s="283"/>
+      <c r="G12" s="283"/>
+      <c r="H12" s="283"/>
+      <c r="I12" s="283"/>
+      <c r="J12" s="283"/>
+      <c r="M12" s="292">
+        <v>9</v>
+      </c>
+      <c r="N12" s="301" t="str">
+        <f>IFERROR( _xlfn.CONCAT("o", _xlfn.UNICHAR(HEX2DEC(RIGHT("U+0358",4))), _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!E12,4)))), "")</f>
+        <v>ő͘</v>
+      </c>
+      <c r="O12" s="301" t="str">
+        <f>IFERROR( _xlfn.CONCAT(O$3, IF([1]【調】韻母標調!$E12="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!$E12,4))))), "")</f>
+        <v>a̋</v>
+      </c>
+      <c r="P12" s="301" t="str">
+        <f>IFERROR( _xlfn.CONCAT(P$3, IF([1]【調】韻母標調!$E12="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!$E12,4))))), "")</f>
+        <v>i̋</v>
+      </c>
+      <c r="Q12" s="301" t="str">
+        <f>IFERROR( _xlfn.CONCAT(Q$3, IF([1]【調】韻母標調!$E12="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!$E12,4))))), "")</f>
+        <v>ű</v>
+      </c>
+      <c r="R12" s="301" t="str">
+        <f>IFERROR( _xlfn.CONCAT(R$3, IF([1]【調】韻母標調!$E12="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!$E12,4))))), "")</f>
+        <v>e̋</v>
+      </c>
+      <c r="S12" s="301" t="str">
+        <f>IFERROR( _xlfn.CONCAT(S$3, IF([1]【調】韻母標調!$E12="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!$E12,4))))), "")</f>
+        <v>ő</v>
+      </c>
+      <c r="T12" s="301" t="str">
+        <f>IFERROR( _xlfn.CONCAT(T$3, IF([1]【調】韻母標調!$E12="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!$E12,4))))), "")</f>
+        <v>m̋</v>
+      </c>
+      <c r="U12" s="301" t="str">
+        <f>IFERROR( _xlfn.CONCAT(U$3, IF([1]【調】韻母標調!$E12="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!$E12,4))))), "")</f>
+        <v>n̋</v>
+      </c>
+    </row>
+    <row r="13" spans="2:26" ht="30.75" thickBot="1">
+      <c r="B13" s="279"/>
+      <c r="F13" s="283"/>
+      <c r="G13" s="283"/>
+      <c r="H13" s="283"/>
+      <c r="I13" s="283"/>
+      <c r="J13" s="283"/>
+      <c r="M13" s="292">
+        <v>0</v>
+      </c>
+      <c r="N13" s="301" t="str">
+        <f>IFERROR( _xlfn.CONCAT("o", _xlfn.UNICHAR(HEX2DEC(RIGHT("U+0358",4))), _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!E13,4)))), "")</f>
+        <v>o̊͘</v>
+      </c>
+      <c r="O13" s="301" t="str">
+        <f>IFERROR( _xlfn.CONCAT(O$3, IF([1]【調】韻母標調!$E13="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!$E13,4))))), "")</f>
+        <v>å</v>
+      </c>
+      <c r="P13" s="301" t="str">
+        <f>IFERROR( _xlfn.CONCAT(P$3, IF([1]【調】韻母標調!$E13="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!$E13,4))))), "")</f>
+        <v>i̊</v>
+      </c>
+      <c r="Q13" s="301" t="str">
+        <f>IFERROR( _xlfn.CONCAT(Q$3, IF([1]【調】韻母標調!$E13="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!$E13,4))))), "")</f>
+        <v>ů</v>
+      </c>
+      <c r="R13" s="301" t="str">
+        <f>IFERROR( _xlfn.CONCAT(R$3, IF([1]【調】韻母標調!$E13="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!$E13,4))))), "")</f>
+        <v>e̊</v>
+      </c>
+      <c r="S13" s="301" t="str">
+        <f>IFERROR( _xlfn.CONCAT(S$3, IF([1]【調】韻母標調!$E13="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!$E13,4))))), "")</f>
+        <v>o̊</v>
+      </c>
+      <c r="T13" s="301" t="str">
+        <f>IFERROR( _xlfn.CONCAT(T$3, IF([1]【調】韻母標調!$E13="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!$E13,4))))), "")</f>
+        <v>m̊</v>
+      </c>
+      <c r="U13" s="301" t="str">
+        <f>IFERROR( _xlfn.CONCAT(U$3, IF([1]【調】韻母標調!$E13="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!$E13,4))))), "")</f>
+        <v>n̊</v>
+      </c>
+    </row>
+    <row r="14" spans="2:26" ht="26.25" thickBot="1">
+      <c r="B14" s="286" t="s">
+        <v>570</v>
+      </c>
+      <c r="C14" s="286" t="s">
+        <v>571</v>
+      </c>
+      <c r="D14" s="286" t="s">
+        <v>572</v>
+      </c>
+      <c r="F14" s="283" t="str">
+        <f xml:space="preserve"> RIGHT(B12,1)</f>
+        <v>͘</v>
+      </c>
+      <c r="G14" s="283"/>
+      <c r="H14" s="283"/>
+      <c r="I14" s="283"/>
+      <c r="J14" s="283"/>
+    </row>
+    <row r="15" spans="2:26" ht="27.75" thickBot="1">
+      <c r="B15" s="303" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT("a", _xlfn.UNICHAR(HEX2DEC(RIGHT("U+0303",4))))</f>
+        <v>ã</v>
+      </c>
+      <c r="C15" s="306" t="s">
+        <v>599</v>
+      </c>
+      <c r="D15" s="295" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT("a", _xlfn.UNICHAR(HEX2DEC(RIGHT(C15,4))))</f>
+        <v>ã</v>
+      </c>
+      <c r="H15" s="283"/>
+    </row>
+    <row r="16" spans="2:26">
+      <c r="N16" s="299" t="s">
+        <v>580</v>
+      </c>
+      <c r="O16" s="299" t="s">
+        <v>581</v>
+      </c>
+      <c r="P16" s="299" t="s">
+        <v>582</v>
+      </c>
+      <c r="Q16" s="299" t="s">
+        <v>583</v>
+      </c>
+      <c r="R16" s="299" t="s">
+        <v>584</v>
+      </c>
+      <c r="S16" s="299" t="s">
+        <v>585</v>
+      </c>
+      <c r="T16" s="299" t="s">
+        <v>586</v>
+      </c>
+      <c r="W16" s="292" t="str">
+        <f xml:space="preserve"> IFERROR( _xlfn.CONCAT("l", "u", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!$O4,4))), "n"), "")</f>
+        <v>lūn</v>
+      </c>
+      <c r="X16" s="292" t="str">
+        <f xml:space="preserve"> IFERROR( _xlfn.CONCAT("n", "g", "o", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!$O4,4))), "o"), "")</f>
+        <v>ngōo</v>
+      </c>
+    </row>
+    <row r="17" spans="13:24" ht="30">
+      <c r="M17" s="292">
+        <v>1</v>
+      </c>
+      <c r="N17" s="301" t="str">
+        <f>IFERROR( _xlfn.CONCAT(O$3, IF([1]【調】韻母標調!$E17="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!$E17,4))))), "")</f>
+        <v>ā</v>
+      </c>
+      <c r="O17" s="301" t="str">
+        <f>IFERROR( _xlfn.CONCAT(P$3, IF([1]【調】韻母標調!$E17="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!$E17,4))))), "")</f>
+        <v>ī</v>
+      </c>
+      <c r="P17" s="301" t="str">
+        <f>IFERROR( _xlfn.CONCAT(Q$3, IF([1]【調】韻母標調!$E17="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!$E17,4))))), "")</f>
+        <v>ū</v>
+      </c>
+      <c r="Q17" s="301" t="str">
+        <f>IFERROR( _xlfn.CONCAT(R$3, IF([1]【調】韻母標調!$E17="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!$E17,4))))), "")</f>
+        <v>ē</v>
+      </c>
+      <c r="R17" s="301" t="str">
+        <f>IFERROR( _xlfn.CONCAT(S$3, IF([1]【調】韻母標調!$E17="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!$E17,4))))), "")</f>
+        <v>ō</v>
+      </c>
+      <c r="S17" s="301" t="str">
+        <f>IFERROR( _xlfn.CONCAT(T$3, IF([1]【調】韻母標調!$E17="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!$E17,4))))), "")</f>
+        <v>m̄</v>
+      </c>
+      <c r="T17" s="301" t="str">
+        <f>IFERROR( _xlfn.CONCAT(U$3, IF([1]【調】韻母標調!$E17="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!$E17,4))))), "")</f>
+        <v>n̄</v>
+      </c>
+      <c r="W17" s="292" t="str">
+        <f xml:space="preserve"> IFERROR( _xlfn.CONCAT("l", "u", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!$O7,4))), "n"), "")</f>
+        <v>lǔn</v>
+      </c>
+      <c r="X17" s="292" t="str">
+        <f xml:space="preserve"> IFERROR( _xlfn.CONCAT("n", "g", "o", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!$O7,4))), "o"), "")</f>
+        <v>ngǒo</v>
+      </c>
+    </row>
+    <row r="18" spans="13:24" ht="30">
+      <c r="M18" s="292">
+        <v>2</v>
+      </c>
+      <c r="N18" s="301" t="str">
+        <f>IFERROR( _xlfn.CONCAT(O$3, IF([1]【調】韻母標調!$E18="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!$E18,4))))), "")</f>
+        <v>á</v>
+      </c>
+      <c r="O18" s="301" t="str">
+        <f>IFERROR( _xlfn.CONCAT(P$3, IF([1]【調】韻母標調!$E18="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!$E18,4))))), "")</f>
+        <v>í</v>
+      </c>
+      <c r="P18" s="301" t="str">
+        <f>IFERROR( _xlfn.CONCAT(Q$3, IF([1]【調】韻母標調!$E18="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!$E18,4))))), "")</f>
+        <v>ú</v>
+      </c>
+      <c r="Q18" s="301" t="str">
+        <f>IFERROR( _xlfn.CONCAT(R$3, IF([1]【調】韻母標調!$E18="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!$E18,4))))), "")</f>
+        <v>é</v>
+      </c>
+      <c r="R18" s="301" t="str">
+        <f>IFERROR( _xlfn.CONCAT(S$3, IF([1]【調】韻母標調!$E18="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!$E18,4))))), "")</f>
+        <v>ó</v>
+      </c>
+      <c r="S18" s="301" t="str">
+        <f>IFERROR( _xlfn.CONCAT(T$3, IF([1]【調】韻母標調!$E18="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!$E18,4))))), "")</f>
+        <v>ḿ</v>
+      </c>
+      <c r="T18" s="301" t="str">
+        <f>IFERROR( _xlfn.CONCAT(U$3, IF([1]【調】韻母標調!$E18="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!$E18,4))))), "")</f>
+        <v>ń</v>
+      </c>
+      <c r="W18" s="292" t="str">
+        <f xml:space="preserve"> IFERROR( _xlfn.CONCAT("l", "u", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!$O6,4))), "n"), "")</f>
+        <v>lùn</v>
+      </c>
+      <c r="X18" s="292" t="str">
+        <f xml:space="preserve"> IFERROR( _xlfn.CONCAT("n", "g", "o", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!$O6,4))), "o"), "")</f>
+        <v>ngòo</v>
+      </c>
+    </row>
+    <row r="19" spans="13:24" ht="30">
+      <c r="M19" s="292">
+        <v>3</v>
+      </c>
+      <c r="N19" s="301" t="str">
+        <f>IFERROR( _xlfn.CONCAT(O$3, IF([1]【調】韻母標調!$E19="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!$E19,4))))), "")</f>
+        <v>ǎ</v>
+      </c>
+      <c r="O19" s="301" t="str">
+        <f>IFERROR( _xlfn.CONCAT(P$3, IF([1]【調】韻母標調!$E19="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!$E19,4))))), "")</f>
+        <v>ǐ</v>
+      </c>
+      <c r="P19" s="301" t="str">
+        <f>IFERROR( _xlfn.CONCAT(Q$3, IF([1]【調】韻母標調!$E19="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!$E19,4))))), "")</f>
+        <v>ǔ</v>
+      </c>
+      <c r="Q19" s="301" t="str">
+        <f>IFERROR( _xlfn.CONCAT(R$3, IF([1]【調】韻母標調!$E19="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!$E19,4))))), "")</f>
+        <v>ě</v>
+      </c>
+      <c r="R19" s="301" t="str">
+        <f>IFERROR( _xlfn.CONCAT(S$3, IF([1]【調】韻母標調!$E19="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!$E19,4))))), "")</f>
+        <v>ǒ</v>
+      </c>
+      <c r="S19" s="301" t="str">
+        <f>IFERROR( _xlfn.CONCAT(T$3, IF([1]【調】韻母標調!$E19="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!$E19,4))))), "")</f>
+        <v>m̌</v>
+      </c>
+      <c r="T19" s="301" t="str">
+        <f>IFERROR( _xlfn.CONCAT(U$3, IF([1]【調】韻母標調!$E19="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!$E19,4))))), "")</f>
+        <v>ň</v>
+      </c>
+      <c r="W19" s="292" t="str">
+        <f xml:space="preserve"> IFERROR( _xlfn.CONCAT("l", "u", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!$O9,4))), "n"), "")</f>
+        <v>lūn</v>
+      </c>
+      <c r="X19" s="292" t="str">
+        <f xml:space="preserve"> IFERROR( _xlfn.CONCAT("n", "g", "o", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!$O9,4))), "o"), "")</f>
+        <v>ngōo</v>
+      </c>
+    </row>
+    <row r="20" spans="13:24" ht="30">
+      <c r="M20" s="292">
+        <v>4</v>
+      </c>
+      <c r="N20" s="301" t="str">
+        <f>IFERROR( _xlfn.CONCAT(O$3, IF([1]【調】韻母標調!$E20="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!$E20,4))))), "")</f>
+        <v>ǎ</v>
+      </c>
+      <c r="O20" s="301" t="str">
+        <f>IFERROR( _xlfn.CONCAT(P$3, IF([1]【調】韻母標調!$E20="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!$E20,4))))), "")</f>
+        <v>ǐ</v>
+      </c>
+      <c r="P20" s="301" t="str">
+        <f>IFERROR( _xlfn.CONCAT(Q$3, IF([1]【調】韻母標調!$E20="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!$E20,4))))), "")</f>
+        <v>ǔ</v>
+      </c>
+      <c r="Q20" s="301" t="str">
+        <f>IFERROR( _xlfn.CONCAT(R$3, IF([1]【調】韻母標調!$E20="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!$E20,4))))), "")</f>
+        <v>ě</v>
+      </c>
+      <c r="R20" s="301" t="str">
+        <f>IFERROR( _xlfn.CONCAT(S$3, IF([1]【調】韻母標調!$E20="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!$E20,4))))), "")</f>
+        <v>ǒ</v>
+      </c>
+      <c r="S20" s="301" t="str">
+        <f>IFERROR( _xlfn.CONCAT(T$3, IF([1]【調】韻母標調!$E20="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!$E20,4))))), "")</f>
+        <v>m̌</v>
+      </c>
+      <c r="T20" s="301" t="str">
+        <f>IFERROR( _xlfn.CONCAT(U$3, IF([1]【調】韻母標調!$E20="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!$E20,4))))), "")</f>
+        <v>ň</v>
+      </c>
+      <c r="W20" s="292" t="str">
+        <f xml:space="preserve"> IFERROR( _xlfn.CONCAT("l", "u", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!$O8,4))), "n"), "")</f>
+        <v>lún</v>
+      </c>
+      <c r="X20" s="292" t="str">
+        <f xml:space="preserve"> IFERROR( _xlfn.CONCAT("n", "g", "o", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!$O8,4))), "o"), "")</f>
+        <v>ngóo</v>
+      </c>
+    </row>
+    <row r="21" spans="13:24" ht="30">
+      <c r="M21" s="292">
+        <v>5</v>
+      </c>
+      <c r="N21" s="301" t="str">
+        <f>IFERROR( _xlfn.CONCAT(O$3, IF([1]【調】韻母標調!$E21="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!$E21,4))))), "")</f>
+        <v>à</v>
+      </c>
+      <c r="O21" s="301" t="str">
+        <f>IFERROR( _xlfn.CONCAT(P$3, IF([1]【調】韻母標調!$E21="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!$E21,4))))), "")</f>
+        <v>ì</v>
+      </c>
+      <c r="P21" s="301" t="str">
+        <f>IFERROR( _xlfn.CONCAT(Q$3, IF([1]【調】韻母標調!$E21="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!$E21,4))))), "")</f>
+        <v>ù</v>
+      </c>
+      <c r="Q21" s="301" t="str">
+        <f>IFERROR( _xlfn.CONCAT(R$3, IF([1]【調】韻母標調!$E21="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!$E21,4))))), "")</f>
+        <v>è</v>
+      </c>
+      <c r="R21" s="301" t="str">
+        <f>IFERROR( _xlfn.CONCAT(S$3, IF([1]【調】韻母標調!$E21="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!$E21,4))))), "")</f>
+        <v>ò</v>
+      </c>
+      <c r="S21" s="301" t="str">
+        <f>IFERROR( _xlfn.CONCAT(T$3, IF([1]【調】韻母標調!$E21="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!$E21,4))))), "")</f>
+        <v>m̀</v>
+      </c>
+      <c r="T21" s="301" t="str">
+        <f>IFERROR( _xlfn.CONCAT(U$3, IF([1]【調】韻母標調!$E21="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!$E21,4))))), "")</f>
+        <v>ǹ</v>
+      </c>
+      <c r="W21" s="292" t="str">
+        <f xml:space="preserve"> IFERROR( _xlfn.CONCAT("l", "u", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!$O11,4))), "n"), "")</f>
+        <v>lǔn</v>
+      </c>
+      <c r="X21" s="292" t="str">
+        <f xml:space="preserve"> IFERROR( _xlfn.CONCAT("n", "g", "o", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!$O11,4))), "o"), "")</f>
+        <v>ngǒo</v>
+      </c>
+    </row>
+    <row r="22" spans="13:24" ht="30">
+      <c r="M22" s="292">
+        <v>6</v>
+      </c>
+      <c r="N22" s="301" t="str">
+        <f>IFERROR( _xlfn.CONCAT(O$3, IF([1]【調】韻母標調!$E22="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!$E22,4))))), "")</f>
+        <v>â</v>
+      </c>
+      <c r="O22" s="301" t="str">
+        <f>IFERROR( _xlfn.CONCAT(P$3, IF([1]【調】韻母標調!$E22="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!$E22,4))))), "")</f>
+        <v>î</v>
+      </c>
+      <c r="P22" s="301" t="str">
+        <f>IFERROR( _xlfn.CONCAT(Q$3, IF([1]【調】韻母標調!$E22="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!$E22,4))))), "")</f>
+        <v>û</v>
+      </c>
+      <c r="Q22" s="301" t="str">
+        <f>IFERROR( _xlfn.CONCAT(R$3, IF([1]【調】韻母標調!$E22="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!$E22,4))))), "")</f>
+        <v>ê</v>
+      </c>
+      <c r="R22" s="301" t="str">
+        <f>IFERROR( _xlfn.CONCAT(S$3, IF([1]【調】韻母標調!$E22="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!$E22,4))))), "")</f>
+        <v>ô</v>
+      </c>
+      <c r="S22" s="301" t="str">
+        <f>IFERROR( _xlfn.CONCAT(T$3, IF([1]【調】韻母標調!$E22="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!$E22,4))))), "")</f>
+        <v>m̂</v>
+      </c>
+      <c r="T22" s="301" t="str">
+        <f>IFERROR( _xlfn.CONCAT(U$3, IF([1]【調】韻母標調!$E22="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!$E22,4))))), "")</f>
+        <v>n̂</v>
+      </c>
+      <c r="W22" s="292" t="str">
+        <f xml:space="preserve"> IFERROR( _xlfn.CONCAT("l", "u", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!$O5,4))), "n"), "")</f>
+        <v>lûn</v>
+      </c>
+      <c r="X22" s="292" t="str">
+        <f xml:space="preserve"> IFERROR( _xlfn.CONCAT("n", "g", "o", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!$O5,4))), "o"), "")</f>
+        <v>ngôo</v>
+      </c>
+    </row>
+    <row r="23" spans="13:24" ht="30">
+      <c r="M23" s="292">
+        <v>7</v>
+      </c>
+      <c r="N23" s="301" t="str">
+        <f>IFERROR( _xlfn.CONCAT(O$3, IF([1]【調】韻母標調!$E23="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!$E23,4))))), "")</f>
+        <v>ā</v>
+      </c>
+      <c r="O23" s="301" t="str">
+        <f>IFERROR( _xlfn.CONCAT(P$3, IF([1]【調】韻母標調!$E23="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!$E23,4))))), "")</f>
+        <v>ī</v>
+      </c>
+      <c r="P23" s="301" t="str">
+        <f>IFERROR( _xlfn.CONCAT(Q$3, IF([1]【調】韻母標調!$E23="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!$E23,4))))), "")</f>
+        <v>ū</v>
+      </c>
+      <c r="Q23" s="301" t="str">
+        <f>IFERROR( _xlfn.CONCAT(R$3, IF([1]【調】韻母標調!$E23="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!$E23,4))))), "")</f>
+        <v>ē</v>
+      </c>
+      <c r="R23" s="301" t="str">
+        <f>IFERROR( _xlfn.CONCAT(S$3, IF([1]【調】韻母標調!$E23="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!$E23,4))))), "")</f>
+        <v>ō</v>
+      </c>
+      <c r="S23" s="301" t="str">
+        <f>IFERROR( _xlfn.CONCAT(T$3, IF([1]【調】韻母標調!$E23="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!$E23,4))))), "")</f>
+        <v>m̄</v>
+      </c>
+      <c r="T23" s="301" t="str">
+        <f>IFERROR( _xlfn.CONCAT(U$3, IF([1]【調】韻母標調!$E23="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!$E23,4))))), "")</f>
+        <v>n̄</v>
+      </c>
+      <c r="W23" s="292" t="str">
+        <f xml:space="preserve"> IFERROR( _xlfn.CONCAT("l", "u", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!$O10,4))), "n"), "")</f>
+        <v>lún</v>
+      </c>
+      <c r="X23" s="292" t="str">
+        <f xml:space="preserve"> IFERROR( _xlfn.CONCAT("n", "g", "o", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!$O10,4))), "o"), "")</f>
+        <v>ngóo</v>
+      </c>
+    </row>
+    <row r="24" spans="13:24" ht="30">
+      <c r="M24" s="292">
+        <v>8</v>
+      </c>
+      <c r="N24" s="301" t="str">
+        <f>IFERROR( _xlfn.CONCAT(O$3, IF([1]【調】韻母標調!$E24="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!$E24,4))))), "")</f>
+        <v>á</v>
+      </c>
+      <c r="O24" s="301" t="str">
+        <f>IFERROR( _xlfn.CONCAT(P$3, IF([1]【調】韻母標調!$E24="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!$E24,4))))), "")</f>
+        <v>í</v>
+      </c>
+      <c r="P24" s="301" t="str">
+        <f>IFERROR( _xlfn.CONCAT(Q$3, IF([1]【調】韻母標調!$E24="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!$E24,4))))), "")</f>
+        <v>ú</v>
+      </c>
+      <c r="Q24" s="301" t="str">
+        <f>IFERROR( _xlfn.CONCAT(R$3, IF([1]【調】韻母標調!$E24="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!$E24,4))))), "")</f>
+        <v>é</v>
+      </c>
+      <c r="R24" s="301" t="str">
+        <f>IFERROR( _xlfn.CONCAT(S$3, IF([1]【調】韻母標調!$E24="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!$E24,4))))), "")</f>
+        <v>ó</v>
+      </c>
+      <c r="S24" s="301" t="str">
+        <f>IFERROR( _xlfn.CONCAT(T$3, IF([1]【調】韻母標調!$E24="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!$E24,4))))), "")</f>
+        <v>ḿ</v>
+      </c>
+      <c r="T24" s="301" t="str">
+        <f>IFERROR( _xlfn.CONCAT(U$3, IF([1]【調】韻母標調!$E24="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!$E24,4))))), "")</f>
+        <v>ń</v>
+      </c>
+    </row>
+    <row r="29" spans="13:24">
+      <c r="N29" s="299" t="s">
+        <v>580</v>
+      </c>
+      <c r="O29" s="299" t="s">
+        <v>581</v>
+      </c>
+      <c r="P29" s="299" t="s">
+        <v>582</v>
+      </c>
+      <c r="Q29" s="299" t="s">
+        <v>583</v>
+      </c>
+      <c r="R29" s="299" t="s">
+        <v>584</v>
+      </c>
+      <c r="S29" s="299" t="s">
+        <v>585</v>
+      </c>
+      <c r="T29" s="299" t="s">
+        <v>586</v>
+      </c>
+      <c r="W29" s="292" t="s">
+        <v>584</v>
+      </c>
+      <c r="X29" s="292" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="30" spans="13:24" ht="30">
+      <c r="M30" s="292">
+        <v>1</v>
+      </c>
+      <c r="N30" s="301" t="str">
+        <f>IFERROR( _xlfn.CONCAT(O$3, IF([1]【調】韻母標調!$E28="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!$E28,4))))), "")</f>
+        <v>a</v>
+      </c>
+      <c r="O30" s="301" t="str">
+        <f>IFERROR( _xlfn.CONCAT(P$3, IF([1]【調】韻母標調!$E28="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!$E28,4))))), "")</f>
+        <v>i</v>
+      </c>
+      <c r="P30" s="301" t="str">
+        <f>IFERROR( _xlfn.CONCAT(Q$3, IF([1]【調】韻母標調!$E28="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!$E28,4))))), "")</f>
+        <v>u</v>
+      </c>
+      <c r="Q30" s="301" t="str">
+        <f>IFERROR( _xlfn.CONCAT(R$3, IF([1]【調】韻母標調!$E28="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!$E28,4))))), "")</f>
+        <v>e</v>
+      </c>
+      <c r="R30" s="301" t="str">
+        <f>IFERROR( _xlfn.CONCAT(S$3, IF([1]【調】韻母標調!$E28="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!$E28,4))))), "")</f>
+        <v>o</v>
+      </c>
+      <c r="S30" s="301" t="str">
+        <f>IFERROR( _xlfn.CONCAT(T$3, IF([1]【調】韻母標調!$E28="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!$E28,4))))), "")</f>
+        <v>m</v>
+      </c>
+      <c r="T30" s="301" t="str">
+        <f>IFERROR( _xlfn.CONCAT(U$3, IF([1]【調】韻母標調!$E28="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!$E28,4))))), "")</f>
+        <v>n</v>
+      </c>
+      <c r="W30" s="307" t="str">
+        <f>IFERROR( _xlfn.CONCAT("l", "o", IF([1]【調】韻母標調!$M4="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!$M4,4))))), "")</f>
+        <v>lo</v>
+      </c>
+      <c r="X30" s="307" t="str">
+        <f>IFERROR( _xlfn.CONCAT("l", "o", IF([1]【調】韻母標調!$M4="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!$M4,4)))), "r", IF(OR(M30=4, M30=8), "k", "")), "")</f>
+        <v>lor</v>
+      </c>
+    </row>
+    <row r="31" spans="13:24" ht="30">
+      <c r="M31" s="292">
+        <v>2</v>
+      </c>
+      <c r="N31" s="301" t="str">
+        <f>IFERROR( _xlfn.CONCAT(O$3, IF([1]【調】韻母標調!$M3="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!$M3,4))))), "")</f>
+        <v/>
+      </c>
+      <c r="O31" s="301" t="str">
+        <f>IFERROR( _xlfn.CONCAT(P$3, IF([1]【調】韻母標調!$M3="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!$M3,4))))), "")</f>
+        <v/>
+      </c>
+      <c r="P31" s="301" t="str">
+        <f>IFERROR( _xlfn.CONCAT(Q$3, IF([1]【調】韻母標調!$M3="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!$M3,4))))), "")</f>
+        <v/>
+      </c>
+      <c r="Q31" s="301" t="str">
+        <f>IFERROR( _xlfn.CONCAT(R$3, IF([1]【調】韻母標調!$M3="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!$M3,4))))), "")</f>
+        <v/>
+      </c>
+      <c r="R31" s="301" t="str">
+        <f>IFERROR( _xlfn.CONCAT(S$3, IF([1]【調】韻母標調!$M3="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!$M3,4))))), "")</f>
+        <v/>
+      </c>
+      <c r="S31" s="301" t="str">
+        <f>IFERROR( _xlfn.CONCAT(T$3, IF([1]【調】韻母標調!$M3="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!$M3,4))))), "")</f>
+        <v/>
+      </c>
+      <c r="T31" s="301" t="str">
+        <f>IFERROR( _xlfn.CONCAT(U$3, IF([1]【調】韻母標調!$M3="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!$M3,4))))), "")</f>
+        <v/>
+      </c>
+      <c r="W31" s="307" t="str">
+        <f>IFERROR( _xlfn.CONCAT("l", "o", IF([1]【調】韻母標調!$M6="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!$M6,4))))), "")</f>
+        <v>ló</v>
+      </c>
+      <c r="X31" s="307" t="str">
+        <f>IFERROR( _xlfn.CONCAT("l", "o", IF([1]【調】韻母標調!$M6="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!$M6,4)))), "r", IF(OR(M31=4, M31=8), "k", "")), "")</f>
+        <v>lór</v>
+      </c>
+    </row>
+    <row r="32" spans="13:24" ht="30">
+      <c r="M32" s="292">
+        <v>3</v>
+      </c>
+      <c r="N32" s="301" t="str">
+        <f>IFERROR( _xlfn.CONCAT(O$3, IF([1]【調】韻母標調!$M4="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!$M4,4))))), "")</f>
+        <v>a</v>
+      </c>
+      <c r="O32" s="301" t="str">
+        <f>IFERROR( _xlfn.CONCAT(P$3, IF([1]【調】韻母標調!$M4="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!$M4,4))))), "")</f>
+        <v>i</v>
+      </c>
+      <c r="P32" s="301" t="str">
+        <f>IFERROR( _xlfn.CONCAT(Q$3, IF([1]【調】韻母標調!$M4="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!$M4,4))))), "")</f>
+        <v>u</v>
+      </c>
+      <c r="Q32" s="301" t="str">
+        <f>IFERROR( _xlfn.CONCAT(R$3, IF([1]【調】韻母標調!$M4="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!$M4,4))))), "")</f>
+        <v>e</v>
+      </c>
+      <c r="R32" s="301" t="str">
+        <f>IFERROR( _xlfn.CONCAT(S$3, IF([1]【調】韻母標調!$M4="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!$M4,4))))), "")</f>
+        <v>o</v>
+      </c>
+      <c r="S32" s="301" t="str">
+        <f>IFERROR( _xlfn.CONCAT(T$3, IF([1]【調】韻母標調!$M4="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!$M4,4))))), "")</f>
+        <v>m</v>
+      </c>
+      <c r="T32" s="301" t="str">
+        <f>IFERROR( _xlfn.CONCAT(U$3, IF([1]【調】韻母標調!$M4="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!$M4,4))))), "")</f>
+        <v>n</v>
+      </c>
+      <c r="W32" s="307" t="str">
+        <f>IFERROR( _xlfn.CONCAT("l", "o", IF([1]【調】韻母標調!$M7="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!$M7,4))))), "")</f>
+        <v>lò</v>
+      </c>
+      <c r="X32" s="307" t="str">
+        <f>IFERROR( _xlfn.CONCAT("l", "o", IF([1]【調】韻母標調!$M7="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!$M7,4)))), "r", IF(OR(M32=4, M32=8), "k", "")), "")</f>
+        <v>lòr</v>
+      </c>
+    </row>
+    <row r="33" spans="13:24" ht="30">
+      <c r="M33" s="292">
+        <v>4</v>
+      </c>
+      <c r="N33" s="301" t="str">
+        <f>IFERROR( _xlfn.CONCAT(O$3, IF([1]【調】韻母標調!$M6="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!$M6,4))))), "")</f>
+        <v>á</v>
+      </c>
+      <c r="O33" s="301" t="str">
+        <f>IFERROR( _xlfn.CONCAT(P$3, IF([1]【調】韻母標調!$M6="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!$M6,4))))), "")</f>
+        <v>í</v>
+      </c>
+      <c r="P33" s="301" t="str">
+        <f>IFERROR( _xlfn.CONCAT(Q$3, IF([1]【調】韻母標調!$M6="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!$M6,4))))), "")</f>
+        <v>ú</v>
+      </c>
+      <c r="Q33" s="301" t="str">
+        <f>IFERROR( _xlfn.CONCAT(R$3, IF([1]【調】韻母標調!$M6="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!$M6,4))))), "")</f>
+        <v>é</v>
+      </c>
+      <c r="R33" s="301" t="str">
+        <f>IFERROR( _xlfn.CONCAT(S$3, IF([1]【調】韻母標調!$M6="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!$M6,4))))), "")</f>
+        <v>ó</v>
+      </c>
+      <c r="S33" s="301" t="str">
+        <f>IFERROR( _xlfn.CONCAT(T$3, IF([1]【調】韻母標調!$M6="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!$M6,4))))), "")</f>
+        <v>ḿ</v>
+      </c>
+      <c r="T33" s="301" t="str">
+        <f>IFERROR( _xlfn.CONCAT(U$3, IF([1]【調】韻母標調!$M6="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!$M6,4))))), "")</f>
+        <v>ń</v>
+      </c>
+      <c r="W33" s="307" t="str">
+        <f>IFERROR( _xlfn.CONCAT("l", "o", IF([1]【調】韻母標調!$M8="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!$M8,4)))), "k"), "")</f>
+        <v>lók</v>
+      </c>
+      <c r="X33" s="307" t="str">
+        <f>IFERROR( _xlfn.CONCAT("l", "o", IF([1]【調】韻母標調!$M8="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!$M8,4)))), "r", IF(OR(M33=4, M33=8), "k", "")), "")</f>
+        <v>lórk</v>
+      </c>
+    </row>
+    <row r="34" spans="13:24" ht="30">
+      <c r="M34" s="292">
+        <v>5</v>
+      </c>
+      <c r="N34" s="301" t="str">
+        <f>IFERROR( _xlfn.CONCAT(O$3, IF([1]【調】韻母標調!$M7="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!$M7,4))))), "")</f>
+        <v>à</v>
+      </c>
+      <c r="O34" s="301" t="str">
+        <f>IFERROR( _xlfn.CONCAT(P$3, IF([1]【調】韻母標調!$M7="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!$M7,4))))), "")</f>
+        <v>ì</v>
+      </c>
+      <c r="P34" s="301" t="str">
+        <f>IFERROR( _xlfn.CONCAT(Q$3, IF([1]【調】韻母標調!$M7="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!$M7,4))))), "")</f>
+        <v>ù</v>
+      </c>
+      <c r="Q34" s="301" t="str">
+        <f>IFERROR( _xlfn.CONCAT(R$3, IF([1]【調】韻母標調!$M7="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!$M7,4))))), "")</f>
+        <v>è</v>
+      </c>
+      <c r="R34" s="301" t="str">
+        <f>IFERROR( _xlfn.CONCAT(S$3, IF([1]【調】韻母標調!$M7="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!$M7,4))))), "")</f>
+        <v>ò</v>
+      </c>
+      <c r="S34" s="301" t="str">
+        <f>IFERROR( _xlfn.CONCAT(T$3, IF([1]【調】韻母標調!$M7="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!$M7,4))))), "")</f>
+        <v>m̀</v>
+      </c>
+      <c r="T34" s="301" t="str">
+        <f>IFERROR( _xlfn.CONCAT(U$3, IF([1]【調】韻母標調!$M7="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!$M7,4))))), "")</f>
+        <v>ǹ</v>
+      </c>
+      <c r="W34" s="307" t="str">
+        <f>IFERROR( _xlfn.CONCAT("l", "o", IF([1]【調】韻母標調!$M9="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!$M9,4))))), "")</f>
+        <v>lǒ</v>
+      </c>
+      <c r="X34" s="307" t="str">
+        <f>IFERROR( _xlfn.CONCAT("l", "o", IF([1]【調】韻母標調!$M9="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!$M9,4)))), "r", IF(OR(M34=4, M34=8), "k", "")), "")</f>
+        <v>lǒr</v>
+      </c>
+    </row>
+    <row r="35" spans="13:24" ht="30">
+      <c r="M35" s="292">
+        <v>6</v>
+      </c>
+      <c r="N35" s="301" t="str">
+        <f>IFERROR( _xlfn.CONCAT(O$3, IF([1]【調】韻母標調!$M8="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!$M8,4))))), "")</f>
+        <v>á</v>
+      </c>
+      <c r="O35" s="301" t="str">
+        <f>IFERROR( _xlfn.CONCAT(P$3, IF([1]【調】韻母標調!$M8="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!$M8,4))))), "")</f>
+        <v>í</v>
+      </c>
+      <c r="P35" s="301" t="str">
+        <f>IFERROR( _xlfn.CONCAT(Q$3, IF([1]【調】韻母標調!$M8="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!$M8,4))))), "")</f>
+        <v>ú</v>
+      </c>
+      <c r="Q35" s="301" t="str">
+        <f>IFERROR( _xlfn.CONCAT(R$3, IF([1]【調】韻母標調!$M8="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!$M8,4))))), "")</f>
+        <v>é</v>
+      </c>
+      <c r="R35" s="301" t="str">
+        <f>IFERROR( _xlfn.CONCAT(S$3, IF([1]【調】韻母標調!$M8="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!$M8,4))))), "")</f>
+        <v>ó</v>
+      </c>
+      <c r="S35" s="301" t="str">
+        <f>IFERROR( _xlfn.CONCAT(T$3, IF([1]【調】韻母標調!$M8="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!$M8,4))))), "")</f>
+        <v>ḿ</v>
+      </c>
+      <c r="T35" s="301" t="str">
+        <f>IFERROR( _xlfn.CONCAT(U$3, IF([1]【調】韻母標調!$M8="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!$M8,4))))), "")</f>
+        <v>ń</v>
+      </c>
+      <c r="W35" s="307" t="str">
+        <f>IFERROR( _xlfn.CONCAT("l", "o", IF([1]【調】韻母標調!$M11="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!$M11,4))))), "")</f>
+        <v>ló</v>
+      </c>
+      <c r="X35" s="307" t="str">
+        <f>IFERROR( _xlfn.CONCAT("l", "o", IF([1]【調】韻母標調!$M11="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!$M11,4)))), "r", IF(OR(M35=4, M35=8), "k", "")), "")</f>
+        <v>lór</v>
+      </c>
+    </row>
+    <row r="36" spans="13:24" ht="30">
+      <c r="M36" s="292">
+        <v>7</v>
+      </c>
+      <c r="N36" s="301" t="str">
+        <f>IFERROR( _xlfn.CONCAT(O$3, IF([1]【調】韻母標調!$M9="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!$M9,4))))), "")</f>
+        <v>ǎ</v>
+      </c>
+      <c r="O36" s="301" t="str">
+        <f>IFERROR( _xlfn.CONCAT(P$3, IF([1]【調】韻母標調!$M9="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!$M9,4))))), "")</f>
+        <v>ǐ</v>
+      </c>
+      <c r="P36" s="301" t="str">
+        <f>IFERROR( _xlfn.CONCAT(Q$3, IF([1]【調】韻母標調!$M9="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!$M9,4))))), "")</f>
+        <v>ǔ</v>
+      </c>
+      <c r="Q36" s="301" t="str">
+        <f>IFERROR( _xlfn.CONCAT(R$3, IF([1]【調】韻母標調!$M9="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!$M9,4))))), "")</f>
+        <v>ě</v>
+      </c>
+      <c r="R36" s="301" t="str">
+        <f>IFERROR( _xlfn.CONCAT(S$3, IF([1]【調】韻母標調!$M9="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!$M9,4))))), "")</f>
+        <v>ǒ</v>
+      </c>
+      <c r="S36" s="301" t="str">
+        <f>IFERROR( _xlfn.CONCAT(T$3, IF([1]【調】韻母標調!$M9="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!$M9,4))))), "")</f>
+        <v>m̌</v>
+      </c>
+      <c r="T36" s="301" t="str">
+        <f>IFERROR( _xlfn.CONCAT(U$3, IF([1]【調】韻母標調!$M9="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!$M9,4))))), "")</f>
+        <v>ň</v>
+      </c>
+      <c r="W36" s="307" t="str">
+        <f>IFERROR( _xlfn.CONCAT("l", "o", IF([1]【調】韻母標調!$M5="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!$M5,4))))), "")</f>
+        <v>lō</v>
+      </c>
+      <c r="X36" s="307" t="str">
+        <f>IFERROR( _xlfn.CONCAT("l", "o", IF([1]【調】韻母標調!$M5="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!$M5,4)))), "r", IF(OR(M36=4, M36=8), "k", "")), "")</f>
+        <v>lōr</v>
+      </c>
+    </row>
+    <row r="37" spans="13:24" ht="30">
+      <c r="M37" s="292">
+        <v>8</v>
+      </c>
+      <c r="N37" s="301" t="str">
+        <f>IFERROR( _xlfn.CONCAT(O$3, IF([1]【調】韻母標調!$M11="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!$M11,4))))), "")</f>
+        <v>á</v>
+      </c>
+      <c r="O37" s="301" t="str">
+        <f>IFERROR( _xlfn.CONCAT(P$3, IF([1]【調】韻母標調!$M11="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!$M11,4))))), "")</f>
+        <v>í</v>
+      </c>
+      <c r="P37" s="301" t="str">
+        <f>IFERROR( _xlfn.CONCAT(Q$3, IF([1]【調】韻母標調!$M11="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!$M11,4))))), "")</f>
+        <v>ú</v>
+      </c>
+      <c r="Q37" s="301" t="str">
+        <f>IFERROR( _xlfn.CONCAT(R$3, IF([1]【調】韻母標調!$M11="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!$M11,4))))), "")</f>
+        <v>é</v>
+      </c>
+      <c r="R37" s="301" t="str">
+        <f>IFERROR( _xlfn.CONCAT(S$3, IF([1]【調】韻母標調!$M11="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!$M11,4))))), "")</f>
+        <v>ó</v>
+      </c>
+      <c r="S37" s="301" t="str">
+        <f>IFERROR( _xlfn.CONCAT(T$3, IF([1]【調】韻母標調!$M11="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!$M11,4))))), "")</f>
+        <v>ḿ</v>
+      </c>
+      <c r="T37" s="301" t="str">
+        <f>IFERROR( _xlfn.CONCAT(U$3, IF([1]【調】韻母標調!$M11="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!$M11,4))))), "")</f>
+        <v>ń</v>
+      </c>
+      <c r="W37" s="307" t="str">
+        <f>IFERROR( _xlfn.CONCAT("l", "o", IF([1]【調】韻母標調!$M10="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!$M10,4)))), "k"), "")</f>
+        <v>lo̍k</v>
+      </c>
+      <c r="X37" s="307" t="str">
+        <f>IFERROR( _xlfn.CONCAT("l", "o", IF([1]【調】韻母標調!$M10="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT([1]【調】韻母標調!$M10,4)))), "r", IF(OR(M37=4, M37=8), "k", "")), "")</f>
+        <v>lo̍rk</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/docs/301_鍵盤設計規格_方音符號輸入_台語音標編碼.xlsx
+++ b/docs/301_鍵盤設計規格_方音符號輸入_台語音標編碼.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AlanJui\work\rime-tlpa\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7A1ED8A-909C-4A5E-A316-CDE7EABA905A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECE1D091-2009-4495-A3D8-C2CD6CF230BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="38640" windowHeight="15720" tabRatio="763" activeTab="10" xr2:uid="{6D6F034E-466E-416C-B3CC-1F7937B8DE3D}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="38640" windowHeight="15720" tabRatio="763" activeTab="9" xr2:uid="{6D6F034E-466E-416C-B3CC-1F7937B8DE3D}"/>
   </bookViews>
   <sheets>
     <sheet name="xlit對映工具" sheetId="1" r:id="rId1"/>
@@ -118,7 +118,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2699" uniqueCount="699">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2716" uniqueCount="713">
   <si>
     <t>algebra:</t>
     <phoneticPr fontId="4" type="noConversion"/>
@@ -2202,7 +2202,7 @@
         <sz val="28"/>
         <color rgb="FF000000"/>
         <rFont val="Microsoft JhengHei"/>
-        <charset val="136"/>
+        <family val="2"/>
       </rPr>
       <t>ㆦ˫</t>
     </r>
@@ -2912,6 +2912,58 @@
   <si>
     <t>閩拼方案</t>
   </si>
+  <si>
+    <t>U+02EB</t>
+    <phoneticPr fontId="143" type="noConversion"/>
+  </si>
+  <si>
+    <t>U+02EA</t>
+    <phoneticPr fontId="143" type="noConversion"/>
+  </si>
+  <si>
+    <t>U+02CB</t>
+    <phoneticPr fontId="143" type="noConversion"/>
+  </si>
+  <si>
+    <t>U+02CA</t>
+    <phoneticPr fontId="143" type="noConversion"/>
+  </si>
+  <si>
+    <t>U+0307</t>
+    <phoneticPr fontId="143" type="noConversion"/>
+  </si>
+  <si>
+    <t>陰平</t>
+  </si>
+  <si>
+    <t>陰上</t>
+  </si>
+  <si>
+    <t>陰入</t>
+  </si>
+  <si>
+    <t>陽入</t>
+  </si>
+  <si>
+    <t>八音調名</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>10進制編碼</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Unicode編碼</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>方音調符</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>方音調名</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -2920,7 +2972,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="General;;"/>
   </numFmts>
-  <fonts count="158">
+  <fonts count="164">
     <font>
       <sz val="16"/>
       <color rgb="FF000000"/>
@@ -3724,7 +3776,7 @@
       <sz val="28"/>
       <color rgb="FF000000"/>
       <name val="Microsoft JhengHei"/>
-      <charset val="136"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="12"/>
@@ -3978,8 +4030,53 @@
       <color theme="0" tint="-0.14999847407452621"/>
       <name val="Charis SIL"/>
     </font>
+    <font>
+      <u/>
+      <sz val="16"/>
+      <color theme="10"/>
+      <name val="新細明體"/>
+      <family val="1"/>
+      <charset val="136"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="18"/>
+      <color theme="1"/>
+      <name val="霞鶩文楷等寬 TC Medium"/>
+      <family val="3"/>
+      <charset val="136"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="12"/>
+      <color theme="10"/>
+      <name val="Noto Sans TC Medium"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Noto Sans TC"/>
+      <family val="2"/>
+      <charset val="136"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF0C0301"/>
+      <name val="Noto Sans TC Medium"/>
+      <family val="2"/>
+      <charset val="136"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FFFFFF00"/>
+      <name val="Noto Sans HK"/>
+      <family val="2"/>
+      <charset val="136"/>
+    </font>
   </fonts>
-  <fills count="36">
+  <fills count="37">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -4188,6 +4285,12 @@
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor theme="4" tint="0.59999389629810485"/>
       </patternFill>
     </fill>
   </fills>
@@ -4554,7 +4657,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="7">
+  <cellStyleXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
@@ -4568,8 +4671,12 @@
     <xf numFmtId="0" fontId="132" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="158" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="161" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="352">
+  <cellXfs count="360">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -5482,15 +5589,6 @@
     <xf numFmtId="0" fontId="132" fillId="0" borderId="30" xfId="6" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="108" fillId="29" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="108" fillId="29" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="108" fillId="29" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="107" fillId="30" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -5518,8 +5616,41 @@
     <xf numFmtId="0" fontId="107" fillId="30" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="108" fillId="29" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="108" fillId="29" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="108" fillId="29" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="159" fillId="36" borderId="1" xfId="8" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="159" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="160" fillId="33" borderId="1" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="151" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="162" fillId="33" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="163" fillId="25" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="7">
+  <cellStyles count="9">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
     <cellStyle name="一般 2" xfId="3" xr:uid="{82C09742-F2A0-488F-B715-51F74F221E36}"/>
     <cellStyle name="一般 3" xfId="4" xr:uid="{1FCE98B0-77F0-4309-B3C4-64F2D8A54DE8}"/>
@@ -5527,6 +5658,8 @@
     <cellStyle name="一般 3 3" xfId="6" xr:uid="{171DC839-6999-4A26-BE2F-2CEC8387EFEB}"/>
     <cellStyle name="一般 4" xfId="2" xr:uid="{FCDA43F1-3668-4A20-A0B6-816AA98335F1}"/>
     <cellStyle name="一般 4 2" xfId="5" xr:uid="{143C506F-73C5-41F0-B07E-06D8EE70262A}"/>
+    <cellStyle name="一般 5" xfId="8" xr:uid="{102A3EB5-55C0-4102-B61B-69989119AE4E}"/>
+    <cellStyle name="超連結" xfId="7" builtinId="8"/>
   </cellStyles>
   <dxfs count="23">
     <dxf>
@@ -21055,16 +21188,19 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF721241-4F3B-4D82-A21D-D937A9B2FB8A}">
-  <dimension ref="B1:M39"/>
+  <dimension ref="B1:Q39"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="8.796875" style="267"/>
     <col min="2" max="5" width="10.59765625" style="267" customWidth="1"/>
     <col min="6" max="6" width="16.3984375" style="267" customWidth="1"/>
-    <col min="7" max="16384" width="8.796875" style="267"/>
+    <col min="7" max="11" width="8.796875" style="267"/>
+    <col min="12" max="15" width="9.3984375" style="267" customWidth="1"/>
+    <col min="16" max="16" width="14.5" style="267" customWidth="1"/>
+    <col min="17" max="16384" width="8.796875" style="267"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:13" ht="29.25">
+    <row r="1" spans="2:17" ht="29.25">
       <c r="C1" s="267" t="s">
         <v>600</v>
       </c>
@@ -21080,7 +21216,7 @@
       <c r="L1" s="294"/>
       <c r="M1" s="294"/>
     </row>
-    <row r="2" spans="2:13" ht="20.25">
+    <row r="2" spans="2:17" ht="21">
       <c r="B2" s="295" t="s">
         <v>602</v>
       </c>
@@ -21096,8 +21232,23 @@
       <c r="F2" s="295" t="s">
         <v>606</v>
       </c>
+      <c r="L2" s="359" t="s">
+        <v>708</v>
+      </c>
+      <c r="M2" s="359" t="s">
+        <v>710</v>
+      </c>
+      <c r="N2" s="359" t="s">
+        <v>709</v>
+      </c>
+      <c r="O2" s="359" t="s">
+        <v>711</v>
+      </c>
+      <c r="P2" s="359" t="s">
+        <v>712</v>
+      </c>
     </row>
-    <row r="3" spans="2:13" ht="29.25">
+    <row r="3" spans="2:17" ht="29.25">
       <c r="B3" s="297" t="s">
         <v>607</v>
       </c>
@@ -21125,8 +21276,22 @@
         <v>608</v>
       </c>
       <c r="J3" s="293"/>
+      <c r="L3" s="354" t="s">
+        <v>704</v>
+      </c>
+      <c r="M3" s="355"/>
+      <c r="N3" s="356"/>
+      <c r="O3" s="353" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT("ㄚ")</f>
+        <v>ㄚ</v>
+      </c>
+      <c r="P3" s="353" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT( LEFT(L3,2), " ", O3,)</f>
+        <v>陰平 ㄚ</v>
+      </c>
+      <c r="Q3" s="352"/>
     </row>
-    <row r="4" spans="2:13" ht="29.25">
+    <row r="4" spans="2:17" ht="30">
       <c r="B4" s="297" t="s">
         <v>609</v>
       </c>
@@ -21154,8 +21319,27 @@
         <v>610</v>
       </c>
       <c r="J4" s="293"/>
+      <c r="L4" s="354" t="s">
+        <v>52</v>
+      </c>
+      <c r="M4" s="355" t="s">
+        <v>699</v>
+      </c>
+      <c r="N4" s="357">
+        <f t="shared" ref="N4:N9" si="4" xml:space="preserve"> IFERROR( HEX2DEC(RIGHT(M4,4)), "")</f>
+        <v>747</v>
+      </c>
+      <c r="O4" s="353" t="str">
+        <f xml:space="preserve"> IFERROR( _xlfn.CONCAT("ㄚ", _xlfn.UNICHAR(HEX2DEC(RIGHT(M4,4)))), "")</f>
+        <v>ㄚ˫</v>
+      </c>
+      <c r="P4" s="353" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT( LEFT(L4,2), " ", O4,)</f>
+        <v>陽去 ㄚ˫</v>
+      </c>
+      <c r="Q4" s="352"/>
     </row>
-    <row r="5" spans="2:13" ht="29.25">
+    <row r="5" spans="2:17" ht="30">
       <c r="B5" s="297" t="s">
         <v>611</v>
       </c>
@@ -21183,8 +21367,27 @@
         <v>612</v>
       </c>
       <c r="J5" s="293"/>
+      <c r="L5" s="354" t="s">
+        <v>48</v>
+      </c>
+      <c r="M5" s="355" t="s">
+        <v>700</v>
+      </c>
+      <c r="N5" s="357">
+        <f t="shared" si="4"/>
+        <v>746</v>
+      </c>
+      <c r="O5" s="353" t="str">
+        <f t="shared" ref="O5:O7" si="5" xml:space="preserve"> IFERROR( _xlfn.CONCAT("ㄚ", _xlfn.UNICHAR(HEX2DEC(RIGHT(M5,4)))), "")</f>
+        <v>ㄚ˪</v>
+      </c>
+      <c r="P5" s="353" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT( LEFT(L5,2), " ", O5,)</f>
+        <v>陰去 ㄚ˪</v>
+      </c>
+      <c r="Q5" s="352"/>
     </row>
-    <row r="6" spans="2:13" ht="29.25">
+    <row r="6" spans="2:17" ht="30">
       <c r="B6" s="297" t="s">
         <v>613</v>
       </c>
@@ -21212,8 +21415,27 @@
         <v>106</v>
       </c>
       <c r="J6" s="293"/>
+      <c r="L6" s="354" t="s">
+        <v>705</v>
+      </c>
+      <c r="M6" s="358" t="s">
+        <v>701</v>
+      </c>
+      <c r="N6" s="357">
+        <f t="shared" si="4"/>
+        <v>715</v>
+      </c>
+      <c r="O6" s="353" t="str">
+        <f t="shared" si="5"/>
+        <v>ㄚˋ</v>
+      </c>
+      <c r="P6" s="353" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT( LEFT(L6,2), " ", O6,)</f>
+        <v>陰上 ㄚˋ</v>
+      </c>
+      <c r="Q6" s="352"/>
     </row>
-    <row r="7" spans="2:13" ht="29.25">
+    <row r="7" spans="2:17" ht="30">
       <c r="B7" s="297" t="s">
         <v>614</v>
       </c>
@@ -21241,8 +21463,27 @@
         <v>182</v>
       </c>
       <c r="J7" s="293"/>
+      <c r="L7" s="354" t="s">
+        <v>54</v>
+      </c>
+      <c r="M7" s="355" t="s">
+        <v>702</v>
+      </c>
+      <c r="N7" s="357">
+        <f t="shared" si="4"/>
+        <v>714</v>
+      </c>
+      <c r="O7" s="353" t="str">
+        <f t="shared" si="5"/>
+        <v>ㄚˊ</v>
+      </c>
+      <c r="P7" s="353" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT( LEFT(L7,2), " ", O7,)</f>
+        <v>陽平 ㄚˊ</v>
+      </c>
+      <c r="Q7" s="352"/>
     </row>
-    <row r="8" spans="2:13" ht="29.25">
+    <row r="8" spans="2:17" ht="30">
       <c r="B8" s="297" t="s">
         <v>615</v>
       </c>
@@ -21270,8 +21511,25 @@
         <v>616</v>
       </c>
       <c r="J8" s="293"/>
+      <c r="L8" s="354" t="s">
+        <v>706</v>
+      </c>
+      <c r="M8" s="355"/>
+      <c r="N8" s="357">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="O8" s="353" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT("ㄚ", "ㆷ")</f>
+        <v>ㄚㆷ</v>
+      </c>
+      <c r="P8" s="353" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT( LEFT(L8,2), " ", O8,)</f>
+        <v>陰入 ㄚㆷ</v>
+      </c>
+      <c r="Q8" s="352"/>
     </row>
-    <row r="9" spans="2:13" ht="29.25">
+    <row r="9" spans="2:17" ht="30">
       <c r="B9" s="297" t="s">
         <v>617</v>
       </c>
@@ -21299,8 +21557,27 @@
         <v>618</v>
       </c>
       <c r="J9" s="293"/>
+      <c r="L9" s="354" t="s">
+        <v>707</v>
+      </c>
+      <c r="M9" s="355" t="s">
+        <v>703</v>
+      </c>
+      <c r="N9" s="357">
+        <f t="shared" si="4"/>
+        <v>775</v>
+      </c>
+      <c r="O9" s="353" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT("ㄚ", "ㆷ", _xlfn.UNICHAR(HEX2DEC(RIGHT(M9,4))))</f>
+        <v>ㄚㆷ̇</v>
+      </c>
+      <c r="P9" s="353" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT( LEFT(L9,2), " ", O9,)</f>
+        <v>陽入 ㄚㆷ̇</v>
+      </c>
+      <c r="Q9" s="352"/>
     </row>
-    <row r="10" spans="2:13" ht="29.25">
+    <row r="10" spans="2:17" ht="29.25">
       <c r="B10" s="297" t="s">
         <v>619</v>
       </c>
@@ -21322,7 +21599,7 @@
       </c>
       <c r="G10" s="293"/>
       <c r="H10" s="293" t="str">
-        <f t="shared" ref="H10:H12" si="4">LEFT(B10,2)</f>
+        <f t="shared" ref="H10:H12" si="6">LEFT(B10,2)</f>
         <v>io</v>
       </c>
       <c r="I10" s="298" t="s">
@@ -21330,7 +21607,7 @@
       </c>
       <c r="J10" s="293"/>
     </row>
-    <row r="11" spans="2:13" ht="29.25">
+    <row r="11" spans="2:17" ht="29.25">
       <c r="B11" s="297" t="s">
         <v>621</v>
       </c>
@@ -21352,7 +21629,7 @@
       </c>
       <c r="G11" s="293"/>
       <c r="H11" s="293" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>iu</v>
       </c>
       <c r="I11" s="293" t="s">
@@ -21360,7 +21637,7 @@
       </c>
       <c r="J11" s="293"/>
     </row>
-    <row r="12" spans="2:13" ht="29.25">
+    <row r="12" spans="2:17" ht="29.25">
       <c r="B12" s="297" t="s">
         <v>623</v>
       </c>
@@ -21382,7 +21659,7 @@
       </c>
       <c r="G12" s="293"/>
       <c r="H12" s="293" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>ia</v>
       </c>
       <c r="I12" s="293" t="s">
@@ -21390,12 +21667,12 @@
       </c>
       <c r="J12" s="293"/>
     </row>
-    <row r="13" spans="2:13" ht="29.25">
+    <row r="13" spans="2:17" ht="29.25">
       <c r="B13" s="297" t="s">
         <v>625</v>
       </c>
       <c r="C13" s="297" t="str">
-        <f t="shared" ref="C13" si="5" xml:space="preserve"> _xlfn.CONCAT("ㄧ",C9)</f>
+        <f t="shared" ref="C13" si="7" xml:space="preserve"> _xlfn.CONCAT("ㄧ",C9)</f>
         <v>ㄧㆯ</v>
       </c>
       <c r="D13" s="297" t="str">
@@ -21420,7 +21697,7 @@
       </c>
       <c r="J13" s="293"/>
     </row>
-    <row r="14" spans="2:13" ht="29.25">
+    <row r="14" spans="2:17" ht="29.25">
       <c r="B14" s="297" t="s">
         <v>627</v>
       </c>
@@ -21450,7 +21727,7 @@
       </c>
       <c r="J14" s="293"/>
     </row>
-    <row r="15" spans="2:13" ht="29.25">
+    <row r="15" spans="2:17" ht="29.25">
       <c r="B15" s="297" t="s">
         <v>629</v>
       </c>
@@ -21480,7 +21757,7 @@
       </c>
       <c r="J15" s="293"/>
     </row>
-    <row r="16" spans="2:13" ht="29.25">
+    <row r="16" spans="2:17" ht="29.25">
       <c r="B16" s="293"/>
       <c r="C16" s="293"/>
       <c r="D16" s="293"/>
@@ -21516,11 +21793,11 @@
         <v>135</v>
       </c>
       <c r="D18" s="293" t="str">
-        <f t="shared" ref="D18:E19" si="6" xml:space="preserve"> _xlfn.CONCAT(B18, $I$3)</f>
+        <f t="shared" ref="D18:E19" si="8" xml:space="preserve"> _xlfn.CONCAT(B18, $I$3)</f>
         <v>ㄘㄧ</v>
       </c>
       <c r="E18" s="293" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>ㄑㄧ</v>
       </c>
       <c r="F18" s="293"/>
@@ -21535,11 +21812,11 @@
         <v>174</v>
       </c>
       <c r="D19" s="293" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>ㄙㄧ</v>
       </c>
       <c r="E19" s="293" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>ㄒㄧ</v>
       </c>
       <c r="F19" s="293"/>
@@ -21648,6 +21925,12 @@
     </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="M4" r:id="rId1" display="https://zi-hi.com/sp/uni/0301" xr:uid="{8E09843C-9E3B-4BD1-A60F-176F601F5502}"/>
+    <hyperlink ref="M7" r:id="rId2" display="https://zi-hi.com/sp/uni/0300" xr:uid="{6DC62E69-6013-4B8C-B6B7-3551176CF13D}"/>
+    <hyperlink ref="M5" r:id="rId3" display="https://zi-hi.com/sp/uni/0304" xr:uid="{86E30BA4-CB54-47D4-B865-DE2E6F34A888}"/>
+    <hyperlink ref="M9" r:id="rId4" display="https://zi-hi.com/sp/uni/030D" xr:uid="{D88B0A2F-0E15-472F-9026-FDC168ECBC1B}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -39163,25 +39446,25 @@
   <sheetData>
     <row r="1" spans="2:19" ht="21.75" thickBot="1"/>
     <row r="2" spans="2:19" ht="24" thickBot="1">
-      <c r="B2" s="343" t="s">
+      <c r="B2" s="340" t="s">
         <v>332</v>
       </c>
-      <c r="C2" s="345" t="s">
+      <c r="C2" s="342" t="s">
         <v>333</v>
       </c>
-      <c r="D2" s="346"/>
-      <c r="E2" s="349" t="s">
+      <c r="D2" s="343"/>
+      <c r="E2" s="346" t="s">
         <v>334</v>
       </c>
-      <c r="F2" s="350"/>
-      <c r="G2" s="351"/>
-      <c r="H2" s="349" t="s">
+      <c r="F2" s="347"/>
+      <c r="G2" s="348"/>
+      <c r="H2" s="346" t="s">
         <v>335</v>
       </c>
-      <c r="I2" s="350"/>
-      <c r="J2" s="350"/>
-      <c r="K2" s="350"/>
-      <c r="L2" s="351"/>
+      <c r="I2" s="347"/>
+      <c r="J2" s="347"/>
+      <c r="K2" s="347"/>
+      <c r="L2" s="348"/>
       <c r="O2" s="236" t="s">
         <v>484</v>
       </c>
@@ -39196,9 +39479,9 @@
       </c>
     </row>
     <row r="3" spans="2:19" ht="24" thickBot="1">
-      <c r="B3" s="344"/>
-      <c r="C3" s="347"/>
-      <c r="D3" s="348"/>
+      <c r="B3" s="341"/>
+      <c r="C3" s="344"/>
+      <c r="D3" s="345"/>
       <c r="E3" s="234" t="s">
         <v>336</v>
       </c>
@@ -39217,10 +39500,10 @@
       <c r="J3" s="234" t="s">
         <v>341</v>
       </c>
-      <c r="K3" s="349" t="s">
+      <c r="K3" s="346" t="s">
         <v>342</v>
       </c>
-      <c r="L3" s="351"/>
+      <c r="L3" s="348"/>
       <c r="O3" s="236" t="s">
         <v>278</v>
       </c>
@@ -40112,57 +40395,57 @@
       <c r="B27" s="234" t="s">
         <v>447</v>
       </c>
-      <c r="C27" s="340" t="s">
+      <c r="C27" s="349" t="s">
         <v>192</v>
       </c>
-      <c r="D27" s="341"/>
-      <c r="E27" s="340" t="s">
+      <c r="D27" s="350"/>
+      <c r="E27" s="349" t="s">
         <v>448</v>
       </c>
-      <c r="F27" s="342"/>
-      <c r="G27" s="342"/>
-      <c r="H27" s="342"/>
-      <c r="I27" s="342"/>
-      <c r="J27" s="341"/>
-      <c r="K27" s="340" t="s">
+      <c r="F27" s="351"/>
+      <c r="G27" s="351"/>
+      <c r="H27" s="351"/>
+      <c r="I27" s="351"/>
+      <c r="J27" s="350"/>
+      <c r="K27" s="349" t="s">
         <v>449</v>
       </c>
-      <c r="L27" s="341"/>
+      <c r="L27" s="350"/>
     </row>
     <row r="28" spans="2:20" ht="24" thickBot="1">
       <c r="B28" s="234" t="s">
         <v>450</v>
       </c>
-      <c r="C28" s="340" t="s">
+      <c r="C28" s="349" t="s">
         <v>451</v>
       </c>
-      <c r="D28" s="341"/>
-      <c r="E28" s="340" t="s">
+      <c r="D28" s="350"/>
+      <c r="E28" s="349" t="s">
         <v>448</v>
       </c>
-      <c r="F28" s="342"/>
-      <c r="G28" s="342"/>
-      <c r="H28" s="342"/>
-      <c r="I28" s="342"/>
-      <c r="J28" s="341"/>
-      <c r="K28" s="340" t="s">
+      <c r="F28" s="351"/>
+      <c r="G28" s="351"/>
+      <c r="H28" s="351"/>
+      <c r="I28" s="351"/>
+      <c r="J28" s="350"/>
+      <c r="K28" s="349" t="s">
         <v>452</v>
       </c>
-      <c r="L28" s="341"/>
+      <c r="L28" s="350"/>
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="C2:D3"/>
-    <mergeCell ref="E2:G2"/>
-    <mergeCell ref="H2:L2"/>
-    <mergeCell ref="K3:L3"/>
     <mergeCell ref="C27:D27"/>
     <mergeCell ref="E27:J27"/>
     <mergeCell ref="K27:L27"/>
     <mergeCell ref="C28:D28"/>
     <mergeCell ref="E28:J28"/>
     <mergeCell ref="K28:L28"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="C2:D3"/>
+    <mergeCell ref="E2:G2"/>
+    <mergeCell ref="H2:L2"/>
+    <mergeCell ref="K3:L3"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -40184,30 +40467,30 @@
   <sheetData>
     <row r="1" spans="2:20" ht="21.75" thickBot="1"/>
     <row r="2" spans="2:20" ht="24" thickBot="1">
-      <c r="B2" s="343" t="s">
+      <c r="B2" s="340" t="s">
         <v>332</v>
       </c>
-      <c r="C2" s="345" t="s">
+      <c r="C2" s="342" t="s">
         <v>333</v>
       </c>
-      <c r="D2" s="346"/>
-      <c r="E2" s="349" t="s">
+      <c r="D2" s="343"/>
+      <c r="E2" s="346" t="s">
         <v>334</v>
       </c>
-      <c r="F2" s="350"/>
-      <c r="G2" s="351"/>
-      <c r="H2" s="349" t="s">
+      <c r="F2" s="347"/>
+      <c r="G2" s="348"/>
+      <c r="H2" s="346" t="s">
         <v>335</v>
       </c>
-      <c r="I2" s="350"/>
-      <c r="J2" s="350"/>
-      <c r="K2" s="350"/>
-      <c r="L2" s="351"/>
+      <c r="I2" s="347"/>
+      <c r="J2" s="347"/>
+      <c r="K2" s="347"/>
+      <c r="L2" s="348"/>
     </row>
     <row r="3" spans="2:20" ht="24" thickBot="1">
-      <c r="B3" s="344"/>
-      <c r="C3" s="347"/>
-      <c r="D3" s="348"/>
+      <c r="B3" s="341"/>
+      <c r="C3" s="344"/>
+      <c r="D3" s="345"/>
       <c r="E3" s="234" t="s">
         <v>336</v>
       </c>
@@ -40226,10 +40509,10 @@
       <c r="J3" s="234" t="s">
         <v>341</v>
       </c>
-      <c r="K3" s="349" t="s">
+      <c r="K3" s="346" t="s">
         <v>342</v>
       </c>
-      <c r="L3" s="351"/>
+      <c r="L3" s="348"/>
       <c r="N3" s="240" t="s">
         <v>509</v>
       </c>
@@ -41262,43 +41545,43 @@
       <c r="B27" s="234" t="s">
         <v>447</v>
       </c>
-      <c r="C27" s="340" t="s">
+      <c r="C27" s="349" t="s">
         <v>192</v>
       </c>
-      <c r="D27" s="341"/>
-      <c r="E27" s="340" t="s">
+      <c r="D27" s="350"/>
+      <c r="E27" s="349" t="s">
         <v>448</v>
       </c>
-      <c r="F27" s="342"/>
-      <c r="G27" s="342"/>
-      <c r="H27" s="342"/>
-      <c r="I27" s="342"/>
-      <c r="J27" s="341"/>
-      <c r="K27" s="340" t="s">
+      <c r="F27" s="351"/>
+      <c r="G27" s="351"/>
+      <c r="H27" s="351"/>
+      <c r="I27" s="351"/>
+      <c r="J27" s="350"/>
+      <c r="K27" s="349" t="s">
         <v>449</v>
       </c>
-      <c r="L27" s="341"/>
+      <c r="L27" s="350"/>
     </row>
     <row r="28" spans="2:21" ht="24" thickBot="1">
       <c r="B28" s="234" t="s">
         <v>450</v>
       </c>
-      <c r="C28" s="340" t="s">
+      <c r="C28" s="349" t="s">
         <v>451</v>
       </c>
-      <c r="D28" s="341"/>
-      <c r="E28" s="340" t="s">
+      <c r="D28" s="350"/>
+      <c r="E28" s="349" t="s">
         <v>448</v>
       </c>
-      <c r="F28" s="342"/>
-      <c r="G28" s="342"/>
-      <c r="H28" s="342"/>
-      <c r="I28" s="342"/>
-      <c r="J28" s="341"/>
-      <c r="K28" s="340" t="s">
+      <c r="F28" s="351"/>
+      <c r="G28" s="351"/>
+      <c r="H28" s="351"/>
+      <c r="I28" s="351"/>
+      <c r="J28" s="350"/>
+      <c r="K28" s="349" t="s">
         <v>452</v>
       </c>
-      <c r="L28" s="341"/>
+      <c r="L28" s="350"/>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="N4:T20">
@@ -41337,25 +41620,25 @@
   <sheetData>
     <row r="1" spans="2:18" ht="21.75" thickBot="1"/>
     <row r="2" spans="2:18" ht="24" thickBot="1">
-      <c r="B2" s="343" t="s">
+      <c r="B2" s="340" t="s">
         <v>332</v>
       </c>
-      <c r="C2" s="345" t="s">
+      <c r="C2" s="342" t="s">
         <v>333</v>
       </c>
-      <c r="D2" s="346"/>
-      <c r="E2" s="349" t="s">
+      <c r="D2" s="343"/>
+      <c r="E2" s="346" t="s">
         <v>334</v>
       </c>
-      <c r="F2" s="350"/>
-      <c r="G2" s="351"/>
-      <c r="H2" s="349" t="s">
+      <c r="F2" s="347"/>
+      <c r="G2" s="348"/>
+      <c r="H2" s="346" t="s">
         <v>335</v>
       </c>
-      <c r="I2" s="350"/>
-      <c r="J2" s="350"/>
-      <c r="K2" s="350"/>
-      <c r="L2" s="351"/>
+      <c r="I2" s="347"/>
+      <c r="J2" s="347"/>
+      <c r="K2" s="347"/>
+      <c r="L2" s="348"/>
       <c r="P2" s="236" t="str">
         <f xml:space="preserve"> "([48])"</f>
         <v>([48])</v>
@@ -41365,9 +41648,9 @@
       </c>
     </row>
     <row r="3" spans="2:18" ht="24" thickBot="1">
-      <c r="B3" s="344"/>
-      <c r="C3" s="347"/>
-      <c r="D3" s="348"/>
+      <c r="B3" s="341"/>
+      <c r="C3" s="344"/>
+      <c r="D3" s="345"/>
       <c r="E3" s="234" t="s">
         <v>336</v>
       </c>
@@ -41386,10 +41669,10 @@
       <c r="J3" s="234" t="s">
         <v>341</v>
       </c>
-      <c r="K3" s="349" t="s">
+      <c r="K3" s="346" t="s">
         <v>342</v>
       </c>
-      <c r="L3" s="351"/>
+      <c r="L3" s="348"/>
       <c r="N3" s="236" t="s">
         <v>454</v>
       </c>
@@ -42281,43 +42564,43 @@
       <c r="B27" s="234" t="s">
         <v>447</v>
       </c>
-      <c r="C27" s="340" t="s">
+      <c r="C27" s="349" t="s">
         <v>192</v>
       </c>
-      <c r="D27" s="341"/>
-      <c r="E27" s="340" t="s">
+      <c r="D27" s="350"/>
+      <c r="E27" s="349" t="s">
         <v>448</v>
       </c>
-      <c r="F27" s="342"/>
-      <c r="G27" s="342"/>
-      <c r="H27" s="342"/>
-      <c r="I27" s="342"/>
-      <c r="J27" s="341"/>
-      <c r="K27" s="340" t="s">
+      <c r="F27" s="351"/>
+      <c r="G27" s="351"/>
+      <c r="H27" s="351"/>
+      <c r="I27" s="351"/>
+      <c r="J27" s="350"/>
+      <c r="K27" s="349" t="s">
         <v>449</v>
       </c>
-      <c r="L27" s="341"/>
+      <c r="L27" s="350"/>
     </row>
     <row r="28" spans="2:19" ht="24" thickBot="1">
       <c r="B28" s="234" t="s">
         <v>450</v>
       </c>
-      <c r="C28" s="340" t="s">
+      <c r="C28" s="349" t="s">
         <v>451</v>
       </c>
-      <c r="D28" s="341"/>
-      <c r="E28" s="340" t="s">
+      <c r="D28" s="350"/>
+      <c r="E28" s="349" t="s">
         <v>448</v>
       </c>
-      <c r="F28" s="342"/>
-      <c r="G28" s="342"/>
-      <c r="H28" s="342"/>
-      <c r="I28" s="342"/>
-      <c r="J28" s="341"/>
-      <c r="K28" s="340" t="s">
+      <c r="F28" s="351"/>
+      <c r="G28" s="351"/>
+      <c r="H28" s="351"/>
+      <c r="I28" s="351"/>
+      <c r="J28" s="350"/>
+      <c r="K28" s="349" t="s">
         <v>452</v>
       </c>
-      <c r="L28" s="341"/>
+      <c r="L28" s="350"/>
     </row>
   </sheetData>
   <mergeCells count="11">
